--- a/spec/SLAM Build Spec.xlsx
+++ b/spec/SLAM Build Spec.xlsx
@@ -31,8 +31,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open questions" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Rules'!$A$3:$K$188</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Fields'!$A$2:$V$265</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Rules'!$A$3:$K$190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Fields'!$A$2:$V$267</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Feature details'!$A$2:$I$122</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Tags and layers'!$A$2:$C$29</definedName>
   </definedNames>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Grouped into left (where am I), middle (5 tabs), right (7 tools)</t>
+          <t>Grouped into left (where am I), middle (5 tabs), right (8 tools)</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -15240,7 +15240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K188"/>
+  <dimension ref="A1:K190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -16594,7 +16594,7 @@
       </c>
       <c r="D30" s="32" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Coast FI retirement age</t>
         </is>
       </c>
       <c r="E30" s="32" t="inlineStr">
@@ -16604,14 +16604,14 @@
       </c>
       <c r="F30" s="32" t="inlineStr">
         <is>
-          <t>A 'These are big deals' card shows the FI date under each preset side by side, so the client sees how much one assumption moves it</t>
+          <t>Uses the FI target age if set; otherwise 60, editable in Plan &gt; Goals as 'Retire by'</t>
         </is>
       </c>
       <c r="G30" s="32" t="n"/>
       <c r="H30" s="32" t="n"/>
       <c r="I30" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 28)</t>
+          <t>Decided (Oct 28, from Claude Code's question)</t>
         </is>
       </c>
       <c r="J30" s="32" t="n"/>
@@ -16639,24 +16639,24 @@
       </c>
       <c r="D31" s="32" t="inlineStr">
         <is>
-          <t>Goals</t>
+          <t>FI date investing</t>
         </is>
       </c>
       <c r="E31" s="32" t="inlineStr">
         <is>
-          <t>No pace picked</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F31" s="32" t="inlineStr">
         <is>
-          <t>Likely (the default presets); Optimistic and Pessimistic use the 8% and 6% presets</t>
+          <t>Monthly surplus counts as invested until an investing split is entered</t>
         </is>
       </c>
       <c r="G31" s="32" t="n"/>
       <c r="H31" s="32" t="n"/>
       <c r="I31" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 28, replaces Optimistic default)</t>
+          <t>Decided (Oct 28, from Claude Code's question)</t>
         </is>
       </c>
       <c r="J31" s="32" t="n"/>
@@ -16684,28 +16684,24 @@
       </c>
       <c r="D32" s="32" t="inlineStr">
         <is>
-          <t>Goals</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="E32" s="32" t="inlineStr">
         <is>
-          <t>No life expectancy</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F32" s="32" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>A 'These are big deals' card shows the FI date under each preset side by side, so the client sees how much one assumption moves it</t>
         </is>
       </c>
       <c r="G32" s="32" t="n"/>
-      <c r="H32" s="32" t="inlineStr">
-        <is>
-          <t>ProjectionLab uses 85</t>
-        </is>
-      </c>
+      <c r="H32" s="32" t="n"/>
       <c r="I32" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (Oct 28)</t>
         </is>
       </c>
       <c r="J32" s="32" t="n"/>
@@ -16738,19 +16734,19 @@
       </c>
       <c r="E33" s="32" t="inlineStr">
         <is>
-          <t>No retirement spending</t>
+          <t>No pace picked</t>
         </is>
       </c>
       <c r="F33" s="32" t="inlineStr">
         <is>
-          <t>Equals current spending</t>
+          <t>Likely (the default presets); Optimistic and Pessimistic use the 8% and 6% presets</t>
         </is>
       </c>
       <c r="G33" s="32" t="n"/>
       <c r="H33" s="32" t="n"/>
       <c r="I33" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (Oct 28, replaces Optimistic default)</t>
         </is>
       </c>
       <c r="J33" s="32" t="n"/>
@@ -16783,19 +16779,23 @@
       </c>
       <c r="E34" s="32" t="inlineStr">
         <is>
-          <t>Social Security not set</t>
+          <t>No life expectancy</t>
         </is>
       </c>
       <c r="F34" s="32" t="inlineStr">
         <is>
-          <t>Full scheduled benefit (likely case), never zero by default</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G34" s="32" t="n"/>
-      <c r="H34" s="32" t="n"/>
+      <c r="H34" s="32" t="inlineStr">
+        <is>
+          <t>ProjectionLab uses 85</t>
+        </is>
+      </c>
       <c r="I34" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 2)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J34" s="32" t="n"/>
@@ -16823,24 +16823,24 @@
       </c>
       <c r="D35" s="32" t="inlineStr">
         <is>
-          <t>Engine</t>
+          <t>Goals</t>
         </is>
       </c>
       <c r="E35" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>No retirement spending</t>
         </is>
       </c>
       <c r="F35" s="32" t="inlineStr">
         <is>
-          <t>Real (today's) dollars; nominal is a toggle</t>
+          <t>Equals current spending</t>
         </is>
       </c>
       <c r="G35" s="32" t="n"/>
       <c r="H35" s="32" t="n"/>
       <c r="I35" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 2)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J35" s="32" t="n"/>
@@ -16868,28 +16868,24 @@
       </c>
       <c r="D36" s="32" t="inlineStr">
         <is>
-          <t>Split by</t>
+          <t>Goals</t>
         </is>
       </c>
       <c r="E36" s="32" t="inlineStr">
         <is>
-          <t>Roommates entered</t>
+          <t>Social Security not set</t>
         </is>
       </c>
       <c r="F36" s="32" t="inlineStr">
         <is>
-          <t>Every shared Needs line defaults to split by roommates + 1</t>
-        </is>
-      </c>
-      <c r="G36" s="32" t="inlineStr">
-        <is>
-          <t>Client can override per line or just type 'my share'</t>
-        </is>
-      </c>
+          <t>Full scheduled benefit (likely case), never zero by default</t>
+        </is>
+      </c>
+      <c r="G36" s="32" t="n"/>
       <c r="H36" s="32" t="n"/>
       <c r="I36" s="32" t="inlineStr">
         <is>
-          <t>Decided (your Fields comment)</t>
+          <t>Decided (Oct 2)</t>
         </is>
       </c>
       <c r="J36" s="32" t="n"/>
@@ -16917,24 +16913,24 @@
       </c>
       <c r="D37" s="32" t="inlineStr">
         <is>
-          <t>Housing = Family</t>
+          <t>Engine</t>
         </is>
       </c>
       <c r="E37" s="32" t="inlineStr">
         <is>
-          <t>Housing line</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F37" s="32" t="inlineStr">
         <is>
-          <t>Defaults to 'Covered by someone' with Covered by = Parents</t>
+          <t>Real (today's) dollars; nominal is a toggle</t>
         </is>
       </c>
       <c r="G37" s="32" t="n"/>
       <c r="H37" s="32" t="n"/>
       <c r="I37" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (Oct 2)</t>
         </is>
       </c>
       <c r="J37" s="32" t="n"/>
@@ -16962,28 +16958,28 @@
       </c>
       <c r="D38" s="32" t="inlineStr">
         <is>
-          <t>APR = Not sure</t>
+          <t>Split by</t>
         </is>
       </c>
       <c r="E38" s="32" t="inlineStr">
         <is>
-          <t>Debt row</t>
+          <t>Roommates entered</t>
         </is>
       </c>
       <c r="F38" s="32" t="inlineStr">
         <is>
-          <t>Fills a typical rate for that debt type, status Roughly</t>
-        </is>
-      </c>
-      <c r="G38" s="32" t="n"/>
-      <c r="H38" s="32" t="inlineStr">
-        <is>
-          <t>Credit card 24%, personal loan 12%, car 7% (rates to confirm in the Math pass)</t>
-        </is>
-      </c>
+          <t>Every shared Needs line defaults to split by roommates + 1</t>
+        </is>
+      </c>
+      <c r="G38" s="32" t="inlineStr">
+        <is>
+          <t>Client can override per line or just type 'my share'</t>
+        </is>
+      </c>
+      <c r="H38" s="32" t="n"/>
       <c r="I38" s="32" t="inlineStr">
         <is>
-          <t>Decided (screen review)</t>
+          <t>Decided (your Fields comment)</t>
         </is>
       </c>
       <c r="J38" s="32" t="n"/>
@@ -17011,24 +17007,24 @@
       </c>
       <c r="D39" s="32" t="inlineStr">
         <is>
-          <t>Min payment</t>
+          <t>Housing = Family</t>
         </is>
       </c>
       <c r="E39" s="32" t="inlineStr">
         <is>
-          <t>Credit card balance and APR exist</t>
+          <t>Housing line</t>
         </is>
       </c>
       <c r="F39" s="32" t="inlineStr">
         <is>
-          <t>Minimum is computed and shown in Primary; client can overwrite with the statement number</t>
+          <t>Defaults to 'Covered by someone' with Covered by = Parents</t>
         </is>
       </c>
       <c r="G39" s="32" t="n"/>
       <c r="H39" s="32" t="n"/>
       <c r="I39" s="32" t="inlineStr">
         <is>
-          <t>Decided (your Mockup comment)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J39" s="32" t="n"/>
@@ -17056,24 +17052,28 @@
       </c>
       <c r="D40" s="32" t="inlineStr">
         <is>
-          <t>Credit card payment</t>
+          <t>APR = Not sure</t>
         </is>
       </c>
       <c r="E40" s="32" t="inlineStr">
         <is>
-          <t>No choice made</t>
+          <t>Debt row</t>
         </is>
       </c>
       <c r="F40" s="32" t="inlineStr">
         <is>
-          <t>Minimum</t>
+          <t>Fills the typical rate for that debt type from Reference data (Federal Reserve G.19), labeled Guess</t>
         </is>
       </c>
       <c r="G40" s="32" t="n"/>
-      <c r="H40" s="32" t="n"/>
+      <c r="H40" s="32" t="inlineStr">
+        <is>
+          <t>Credit card 22.15%, personal loan 11.86%, car 7.14%</t>
+        </is>
+      </c>
       <c r="I40" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (Oct 28; Guess wins over Roughly here)</t>
         </is>
       </c>
       <c r="J40" s="32" t="n"/>
@@ -17101,24 +17101,24 @@
       </c>
       <c r="D41" s="32" t="inlineStr">
         <is>
-          <t>Tax set-aside</t>
+          <t>Min payment</t>
         </is>
       </c>
       <c r="E41" s="32" t="inlineStr">
         <is>
-          <t>Self-employed, no % entered</t>
+          <t>Credit card balance and APR exist</t>
         </is>
       </c>
       <c r="F41" s="32" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>Minimum is computed and shown in Primary; client can overwrite with the statement number</t>
         </is>
       </c>
       <c r="G41" s="32" t="n"/>
       <c r="H41" s="32" t="n"/>
       <c r="I41" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (your Mockup comment)</t>
         </is>
       </c>
       <c r="J41" s="32" t="n"/>
@@ -17146,17 +17146,17 @@
       </c>
       <c r="D42" s="32" t="inlineStr">
         <is>
-          <t>Session length</t>
+          <t>Credit card payment</t>
         </is>
       </c>
       <c r="E42" s="32" t="inlineStr">
         <is>
-          <t>Not set</t>
+          <t>No choice made</t>
         </is>
       </c>
       <c r="F42" s="32" t="inlineStr">
         <is>
-          <t>60 minutes</t>
+          <t>Minimum</t>
         </is>
       </c>
       <c r="G42" s="32" t="n"/>
@@ -17191,17 +17191,17 @@
       </c>
       <c r="D43" s="32" t="inlineStr">
         <is>
-          <t>Low balance line</t>
+          <t>Tax set-aside</t>
         </is>
       </c>
       <c r="E43" s="32" t="inlineStr">
         <is>
-          <t>Not set</t>
+          <t>Self-employed, no % entered</t>
         </is>
       </c>
       <c r="F43" s="32" t="inlineStr">
         <is>
-          <t>$500</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G43" s="32" t="n"/>
@@ -17236,24 +17236,20 @@
       </c>
       <c r="D44" s="32" t="inlineStr">
         <is>
-          <t>Filing status</t>
+          <t>Session length</t>
         </is>
       </c>
       <c r="E44" s="32" t="inlineStr">
         <is>
-          <t>Solo, not set</t>
+          <t>Not set</t>
         </is>
       </c>
       <c r="F44" s="32" t="inlineStr">
         <is>
-          <t>Single (marked Coach infers)</t>
-        </is>
-      </c>
-      <c r="G44" s="32" t="inlineStr">
-        <is>
-          <t>Couple: Married filing jointly (marked Coach infers)</t>
-        </is>
-      </c>
+          <t>60 minutes</t>
+        </is>
+      </c>
+      <c r="G44" s="32" t="n"/>
       <c r="H44" s="32" t="n"/>
       <c r="I44" s="32" t="inlineStr">
         <is>
@@ -17285,24 +17281,24 @@
       </c>
       <c r="D45" s="32" t="inlineStr">
         <is>
-          <t>Period selector</t>
+          <t>Low balance line</t>
         </is>
       </c>
       <c r="E45" s="32" t="inlineStr">
         <is>
-          <t>Spending opened</t>
+          <t>Not set</t>
         </is>
       </c>
       <c r="F45" s="32" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>$500</t>
         </is>
       </c>
       <c r="G45" s="32" t="n"/>
       <c r="H45" s="32" t="n"/>
       <c r="I45" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 22: monthly default)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J45" s="32" t="n"/>
@@ -17325,35 +17321,39 @@
       </c>
       <c r="C46" s="32" t="inlineStr">
         <is>
-          <t>Entry</t>
+          <t>Default</t>
         </is>
       </c>
       <c r="D46" s="32" t="inlineStr">
         <is>
-          <t>Any amount with a 'per' picker</t>
+          <t>Filing status</t>
         </is>
       </c>
       <c r="E46" s="32" t="inlineStr">
         <is>
-          <t>Amount entered per paycheck, week, month or year</t>
+          <t>Solo, not set</t>
         </is>
       </c>
       <c r="F46" s="32" t="inlineStr">
         <is>
-          <t>Stored as monthly; shown back in the unit it was entered</t>
-        </is>
-      </c>
-      <c r="G46" s="32" t="n"/>
+          <t>Single (marked Coach infers)</t>
+        </is>
+      </c>
+      <c r="G46" s="32" t="inlineStr">
+        <is>
+          <t>Couple: Married filing jointly (marked Coach infers)</t>
+        </is>
+      </c>
       <c r="H46" s="32" t="n"/>
       <c r="I46" s="32" t="inlineStr">
         <is>
-          <t>Decided (Sept 23: any way a number can be given)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J46" s="32" t="n"/>
       <c r="K46" s="33" t="inlineStr">
         <is>
-          <t>3-6</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -17370,39 +17370,35 @@
       </c>
       <c r="C47" s="32" t="inlineStr">
         <is>
-          <t>Entry</t>
+          <t>Default</t>
         </is>
       </c>
       <c r="D47" s="32" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Period selector</t>
         </is>
       </c>
       <c r="E47" s="32" t="inlineStr">
         <is>
-          <t>Only take-home entered</t>
+          <t>Spending opened</t>
         </is>
       </c>
       <c r="F47" s="32" t="inlineStr">
         <is>
-          <t>Gross is solved and marked Computed</t>
-        </is>
-      </c>
-      <c r="G47" s="32" t="inlineStr">
-        <is>
-          <t>Only gross entered: take-home solved. Both: both kept, difference flagged if they don't reconcile</t>
-        </is>
-      </c>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="G47" s="32" t="n"/>
       <c r="H47" s="32" t="n"/>
       <c r="I47" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 2)</t>
+          <t>Decided (Oct 22: monthly default)</t>
         </is>
       </c>
       <c r="J47" s="32" t="n"/>
       <c r="K47" s="33" t="inlineStr">
         <is>
-          <t>3-6</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -17424,24 +17420,24 @@
       </c>
       <c r="D48" s="32" t="inlineStr">
         <is>
-          <t>Pickers</t>
+          <t>Any amount with a 'per' picker</t>
         </is>
       </c>
       <c r="E48" s="32" t="inlineStr">
         <is>
-          <t>Typing</t>
+          <t>Amount entered per paycheck, week, month or year</t>
         </is>
       </c>
       <c r="F48" s="32" t="inlineStr">
         <is>
-          <t>Matches start after 1 letter; Enter picks the top match; free text allowed as 'Other'</t>
+          <t>Stored as monthly; shown back in the unit it was entered</t>
         </is>
       </c>
       <c r="G48" s="32" t="n"/>
       <c r="H48" s="32" t="n"/>
       <c r="I48" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 27: type a little and pick)</t>
+          <t>Decided (Sept 23: any way a number can be given)</t>
         </is>
       </c>
       <c r="J48" s="32" t="n"/>
@@ -17469,24 +17465,28 @@
       </c>
       <c r="D49" s="32" t="inlineStr">
         <is>
-          <t>Every section</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="E49" s="32" t="inlineStr">
         <is>
-          <t>Client has something not on the list</t>
+          <t>Only take-home entered</t>
         </is>
       </c>
       <c r="F49" s="32" t="inlineStr">
         <is>
-          <t>'Other' row with name, amount, type is always available</t>
-        </is>
-      </c>
-      <c r="G49" s="32" t="n"/>
+          <t>Gross is solved and marked Computed</t>
+        </is>
+      </c>
+      <c r="G49" s="32" t="inlineStr">
+        <is>
+          <t>Only gross entered: take-home solved. Both: both kept, difference flagged if they don't reconcile</t>
+        </is>
+      </c>
       <c r="H49" s="32" t="n"/>
       <c r="I49" s="32" t="inlineStr">
         <is>
-          <t>Decided (session gaps)</t>
+          <t>Decided (Oct 2)</t>
         </is>
       </c>
       <c r="J49" s="32" t="n"/>
@@ -17514,24 +17514,24 @@
       </c>
       <c r="D50" s="32" t="inlineStr">
         <is>
-          <t>Car loan / mortgage</t>
+          <t>Pickers</t>
         </is>
       </c>
       <c r="E50" s="32" t="inlineStr">
         <is>
-          <t>Entered on either the asset or the debt</t>
+          <t>Typing</t>
         </is>
       </c>
       <c r="F50" s="32" t="inlineStr">
         <is>
-          <t>Same record shows in both places; editing one edits the other</t>
+          <t>Matches start after 1 letter; Enter picks the top match; free text allowed as 'Other'</t>
         </is>
       </c>
       <c r="G50" s="32" t="n"/>
       <c r="H50" s="32" t="n"/>
       <c r="I50" s="32" t="inlineStr">
         <is>
-          <t>Decided (screen review)</t>
+          <t>Decided (Oct 27: type a little and pick)</t>
         </is>
       </c>
       <c r="J50" s="32" t="n"/>
@@ -17559,24 +17559,24 @@
       </c>
       <c r="D51" s="32" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Every section</t>
         </is>
       </c>
       <c r="E51" s="32" t="inlineStr">
         <is>
-          <t>Credit card or loan has a due day</t>
+          <t>Client has something not on the list</t>
         </is>
       </c>
       <c r="F51" s="32" t="inlineStr">
         <is>
-          <t>Payment appears on the calendar automatically, repeating monthly</t>
+          <t>'Other' row with name, amount, type is always available</t>
         </is>
       </c>
       <c r="G51" s="32" t="n"/>
       <c r="H51" s="32" t="n"/>
       <c r="I51" s="32" t="inlineStr">
         <is>
-          <t>Decided (screen review)</t>
+          <t>Decided (session gaps)</t>
         </is>
       </c>
       <c r="J51" s="32" t="n"/>
@@ -17604,24 +17604,24 @@
       </c>
       <c r="D52" s="32" t="inlineStr">
         <is>
-          <t>Irregular costs</t>
+          <t>Car loan / mortgage</t>
         </is>
       </c>
       <c r="E52" s="32" t="inlineStr">
         <is>
-          <t>Yearly cost and month entered</t>
+          <t>Entered on either the asset or the debt</t>
         </is>
       </c>
       <c r="F52" s="32" t="inlineStr">
         <is>
-          <t>Lands on the calendar in that month and creates a monthly set-aside</t>
+          <t>Same record shows in both places; editing one edits the other</t>
         </is>
       </c>
       <c r="G52" s="32" t="n"/>
       <c r="H52" s="32" t="n"/>
       <c r="I52" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (screen review)</t>
         </is>
       </c>
       <c r="J52" s="32" t="n"/>
@@ -17649,24 +17649,24 @@
       </c>
       <c r="D53" s="32" t="inlineStr">
         <is>
-          <t>Budget actuals</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E53" s="32" t="inlineStr">
         <is>
-          <t>Calendar entries marked Got it / Paid</t>
+          <t>Credit card or loan has a due day</t>
         </is>
       </c>
       <c r="F53" s="32" t="inlineStr">
         <is>
-          <t>Feed the budget line's Actual</t>
+          <t>Payment appears on the calendar automatically, repeating monthly</t>
         </is>
       </c>
       <c r="G53" s="32" t="n"/>
       <c r="H53" s="32" t="n"/>
       <c r="I53" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 16 ice cream sandwich)</t>
+          <t>Decided (screen review)</t>
         </is>
       </c>
       <c r="J53" s="32" t="n"/>
@@ -17694,17 +17694,17 @@
       </c>
       <c r="D54" s="32" t="inlineStr">
         <is>
-          <t>Parking lot</t>
+          <t>Irregular costs</t>
         </is>
       </c>
       <c r="E54" s="32" t="inlineStr">
         <is>
-          <t>Note converted to a field</t>
+          <t>Yearly cost and month entered</t>
         </is>
       </c>
       <c r="F54" s="32" t="inlineStr">
         <is>
-          <t>Note is struck through and links to that field</t>
+          <t>Lands on the calendar in that month and creates a monthly set-aside</t>
         </is>
       </c>
       <c r="G54" s="32" t="n"/>
@@ -17734,35 +17734,35 @@
       </c>
       <c r="C55" s="32" t="inlineStr">
         <is>
-          <t>Status and confidence</t>
+          <t>Entry</t>
         </is>
       </c>
       <c r="D55" s="32" t="inlineStr">
         <is>
-          <t>Every input</t>
+          <t>Budget actuals</t>
         </is>
       </c>
       <c r="E55" s="32" t="inlineStr">
         <is>
-          <t>Value typed</t>
+          <t>Calendar entries marked Got it / Paid</t>
         </is>
       </c>
       <c r="F55" s="32" t="inlineStr">
         <is>
-          <t>Status = Know it unless changed</t>
+          <t>Feed the budget line's Actual</t>
         </is>
       </c>
       <c r="G55" s="32" t="n"/>
       <c r="H55" s="32" t="n"/>
       <c r="I55" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (Oct 16 ice cream sandwich)</t>
         </is>
       </c>
       <c r="J55" s="32" t="n"/>
       <c r="K55" s="33" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>3-6</t>
         </is>
       </c>
     </row>
@@ -17779,35 +17779,35 @@
       </c>
       <c r="C56" s="32" t="inlineStr">
         <is>
-          <t>Status and confidence</t>
+          <t>Entry</t>
         </is>
       </c>
       <c r="D56" s="32" t="inlineStr">
         <is>
-          <t>Every input</t>
+          <t>Parking lot</t>
         </is>
       </c>
       <c r="E56" s="32" t="inlineStr">
         <is>
-          <t>Status picked</t>
+          <t>Note converted to a field</t>
         </is>
       </c>
       <c r="F56" s="32" t="inlineStr">
         <is>
-          <t>One of: Know it, Roughly, Not sure, Will email, Not now, Not for me, Computed</t>
+          <t>Note is struck through and links to that field</t>
         </is>
       </c>
       <c r="G56" s="32" t="n"/>
       <c r="H56" s="32" t="n"/>
       <c r="I56" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 27, list pending your final OK)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J56" s="32" t="n"/>
       <c r="K56" s="33" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>3-6</t>
         </is>
       </c>
     </row>
@@ -17829,24 +17829,24 @@
       </c>
       <c r="D57" s="32" t="inlineStr">
         <is>
-          <t>Status = Roughly</t>
+          <t>Every input</t>
         </is>
       </c>
       <c r="E57" s="32" t="inlineStr">
         <is>
-          <t>Any field</t>
+          <t>Value typed</t>
         </is>
       </c>
       <c r="F57" s="32" t="inlineStr">
         <is>
-          <t>Counts as done, shows ≈, gets a next check date</t>
+          <t>Status = Know it unless changed</t>
         </is>
       </c>
       <c r="G57" s="32" t="n"/>
       <c r="H57" s="32" t="n"/>
       <c r="I57" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 27)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J57" s="32" t="n"/>
@@ -17874,24 +17874,24 @@
       </c>
       <c r="D58" s="32" t="inlineStr">
         <is>
-          <t>Status = Not sure</t>
+          <t>Every input</t>
         </is>
       </c>
       <c r="E58" s="32" t="inlineStr">
         <is>
-          <t>Any field</t>
+          <t>Status picked</t>
         </is>
       </c>
       <c r="F58" s="32" t="inlineStr">
         <is>
-          <t>App fills a typical value labeled Guess. Different from Roughly: Roughly is the client's own ballpark, Guess is the app's number. Counts toward core but flagged</t>
+          <t>One of: Know it, Roughly, Not sure, Will email, Not now, Not for me, Computed</t>
         </is>
       </c>
       <c r="G58" s="32" t="n"/>
       <c r="H58" s="32" t="n"/>
       <c r="I58" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (Oct 27, list pending your final OK)</t>
         </is>
       </c>
       <c r="J58" s="32" t="n"/>
@@ -17919,7 +17919,7 @@
       </c>
       <c r="D59" s="32" t="inlineStr">
         <is>
-          <t>Status = Will email</t>
+          <t>Status = Roughly</t>
         </is>
       </c>
       <c r="E59" s="32" t="inlineStr">
@@ -17929,14 +17929,14 @@
       </c>
       <c r="F59" s="32" t="inlineStr">
         <is>
-          <t>Added to homework list with the field name; counts as not done</t>
+          <t>Counts as done, shows ≈, gets a next check date</t>
         </is>
       </c>
       <c r="G59" s="32" t="n"/>
       <c r="H59" s="32" t="n"/>
       <c r="I59" s="32" t="inlineStr">
         <is>
-          <t>Decided (homework)</t>
+          <t>Decided (Oct 27)</t>
         </is>
       </c>
       <c r="J59" s="32" t="n"/>
@@ -17964,7 +17964,7 @@
       </c>
       <c r="D60" s="32" t="inlineStr">
         <is>
-          <t>Status = Not now</t>
+          <t>Status = Not sure</t>
         </is>
       </c>
       <c r="E60" s="32" t="inlineStr">
@@ -17974,14 +17974,14 @@
       </c>
       <c r="F60" s="32" t="inlineStr">
         <is>
-          <t>Parked; stays on the revisit list; not done</t>
+          <t>App fills a typical value labeled Guess. Different from Roughly: Roughly is the client's own ballpark, Guess is the app's number. Counts toward core but flagged</t>
         </is>
       </c>
       <c r="G60" s="32" t="n"/>
       <c r="H60" s="32" t="n"/>
       <c r="I60" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 27)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J60" s="32" t="n"/>
@@ -18009,24 +18009,24 @@
       </c>
       <c r="D61" s="32" t="inlineStr">
         <is>
-          <t>Status = Not for me / N/A</t>
+          <t>Status = Will email</t>
         </is>
       </c>
       <c r="E61" s="32" t="inlineStr">
         <is>
-          <t>Any field or line</t>
+          <t>Any field</t>
         </is>
       </c>
       <c r="F61" s="32" t="inlineStr">
         <is>
-          <t>Counts as done; value treated as zero</t>
+          <t>Added to homework list with the field name; counts as not done</t>
         </is>
       </c>
       <c r="G61" s="32" t="n"/>
       <c r="H61" s="32" t="n"/>
       <c r="I61" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 27)</t>
+          <t>Decided (homework)</t>
         </is>
       </c>
       <c r="J61" s="32" t="n"/>
@@ -18054,24 +18054,24 @@
       </c>
       <c r="D62" s="32" t="inlineStr">
         <is>
-          <t>Row status</t>
+          <t>Status = Not now</t>
         </is>
       </c>
       <c r="E62" s="32" t="inlineStr">
         <is>
-          <t>Row-level status set</t>
+          <t>Any field</t>
         </is>
       </c>
       <c r="F62" s="32" t="inlineStr">
         <is>
-          <t>Applies to every field in the row unless a field has its own</t>
+          <t>Parked; stays on the revisit list; not done</t>
         </is>
       </c>
       <c r="G62" s="32" t="n"/>
       <c r="H62" s="32" t="n"/>
       <c r="I62" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (Oct 27)</t>
         </is>
       </c>
       <c r="J62" s="32" t="n"/>
@@ -18099,24 +18099,24 @@
       </c>
       <c r="D63" s="32" t="inlineStr">
         <is>
-          <t>Computed fields</t>
+          <t>Status = Not for me / N/A</t>
         </is>
       </c>
       <c r="E63" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Any field or line</t>
         </is>
       </c>
       <c r="F63" s="32" t="inlineStr">
         <is>
-          <t>Can't be typed over except min payment (statement number) and gross/take-home; an overwrite turns status to Know it and shows a reset-to-computed icon</t>
+          <t>Counts as done; value treated as zero</t>
         </is>
       </c>
       <c r="G63" s="32" t="n"/>
       <c r="H63" s="32" t="n"/>
       <c r="I63" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (Oct 27)</t>
         </is>
       </c>
       <c r="J63" s="32" t="n"/>
@@ -18144,17 +18144,17 @@
       </c>
       <c r="D64" s="32" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Row status</t>
         </is>
       </c>
       <c r="E64" s="32" t="inlineStr">
         <is>
-          <t>Roughly number older than 30 days, or any number older than 90 days</t>
+          <t>Row-level status set</t>
         </is>
       </c>
       <c r="F64" s="32" t="inlineStr">
         <is>
-          <t>Shows on revisit list and 'Due for a check' on Home</t>
+          <t>Applies to every field in the row unless a field has its own</t>
         </is>
       </c>
       <c r="G64" s="32" t="n"/>
@@ -18189,24 +18189,24 @@
       </c>
       <c r="D65" s="32" t="inlineStr">
         <is>
-          <t>Stress rating</t>
+          <t>Computed fields</t>
         </is>
       </c>
       <c r="E65" s="32" t="inlineStr">
         <is>
-          <t>Debts and accounts</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F65" s="32" t="inlineStr">
         <is>
-          <t>1 to 5, blank allowed; blank is ignored by the stress payoff order</t>
+          <t>Can't be typed over except min payment (statement number) and gross/take-home; an overwrite turns status to Know it and shows a reset-to-computed icon</t>
         </is>
       </c>
       <c r="G65" s="32" t="n"/>
       <c r="H65" s="32" t="n"/>
       <c r="I65" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 2)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J65" s="32" t="n"/>
@@ -18229,35 +18229,35 @@
       </c>
       <c r="C66" s="32" t="inlineStr">
         <is>
-          <t>Completion</t>
+          <t>Status and confidence</t>
         </is>
       </c>
       <c r="D66" s="32" t="inlineStr">
         <is>
-          <t>Section bars</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="E66" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Roughly number older than 30 days, or any number older than 90 days</t>
         </is>
       </c>
       <c r="F66" s="32" t="inlineStr">
         <is>
-          <t>Two bars per section: core (Primary fields) and full detail (all fields that apply)</t>
+          <t>Shows on revisit list and 'Due for a check' on Home</t>
         </is>
       </c>
       <c r="G66" s="32" t="n"/>
       <c r="H66" s="32" t="n"/>
       <c r="I66" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 27)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J66" s="32" t="n"/>
       <c r="K66" s="33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1-3</t>
         </is>
       </c>
     </row>
@@ -18274,35 +18274,35 @@
       </c>
       <c r="C67" s="32" t="inlineStr">
         <is>
-          <t>Completion</t>
+          <t>Status and confidence</t>
         </is>
       </c>
       <c r="D67" s="32" t="inlineStr">
         <is>
-          <t>Counting</t>
+          <t>Stress rating</t>
         </is>
       </c>
       <c r="E67" s="32" t="inlineStr">
         <is>
-          <t>Field is gated out</t>
+          <t>Debts and accounts</t>
         </is>
       </c>
       <c r="F67" s="32" t="inlineStr">
         <is>
-          <t>Not counted at all</t>
+          <t>1 to 5, blank allowed; blank is ignored by the stress payoff order</t>
         </is>
       </c>
       <c r="G67" s="32" t="n"/>
       <c r="H67" s="32" t="n"/>
       <c r="I67" s="32" t="inlineStr">
         <is>
-          <t>Decided</t>
+          <t>Decided (Oct 2)</t>
         </is>
       </c>
       <c r="J67" s="32" t="n"/>
       <c r="K67" s="33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1-3</t>
         </is>
       </c>
     </row>
@@ -18324,28 +18324,24 @@
       </c>
       <c r="D68" s="32" t="inlineStr">
         <is>
-          <t>Counting</t>
+          <t>Section bars</t>
         </is>
       </c>
       <c r="E68" s="32" t="inlineStr">
         <is>
-          <t>Know it, Roughly, Not for me, Computed</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F68" s="32" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G68" s="32" t="inlineStr">
-        <is>
-          <t>Not sure counts for core only; Will email and Not now are not done</t>
-        </is>
-      </c>
+          <t>Two bars per section: core (Primary fields) and full detail (all fields that apply)</t>
+        </is>
+      </c>
+      <c r="G68" s="32" t="n"/>
       <c r="H68" s="32" t="n"/>
       <c r="I68" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (Oct 27)</t>
         </is>
       </c>
       <c r="J68" s="32" t="n"/>
@@ -18373,24 +18369,24 @@
       </c>
       <c r="D69" s="32" t="inlineStr">
         <is>
-          <t>Fast Track</t>
+          <t>Counting</t>
         </is>
       </c>
       <c r="E69" s="32" t="inlineStr">
         <is>
-          <t>All Fast Track fields done</t>
+          <t>Field is gated out</t>
         </is>
       </c>
       <c r="F69" s="32" t="inlineStr">
         <is>
-          <t>Every lens turns on (net worth, savings rate, DRAFTT, FI date)</t>
+          <t>Not counted at all</t>
         </is>
       </c>
       <c r="G69" s="32" t="n"/>
       <c r="H69" s="32" t="n"/>
       <c r="I69" s="32" t="inlineStr">
         <is>
-          <t>Decided (your comment: enough to turn on every lens)</t>
+          <t>Decided</t>
         </is>
       </c>
       <c r="J69" s="32" t="n"/>
@@ -18418,24 +18414,28 @@
       </c>
       <c r="D70" s="32" t="inlineStr">
         <is>
-          <t>Fast Track accuracy</t>
+          <t>Counting</t>
         </is>
       </c>
       <c r="E70" s="32" t="inlineStr">
         <is>
-          <t>Fast Track result vs full-detail result</t>
+          <t>Know it, Roughly, Not for me, Computed</t>
         </is>
       </c>
       <c r="F70" s="32" t="inlineStr">
         <is>
-          <t>Target: within $100/month of the full answer. Track the gap after each full session</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>Not sure counts for core only; Will email and Not now are not done</t>
+        </is>
+      </c>
       <c r="H70" s="32" t="n"/>
       <c r="I70" s="32" t="inlineStr">
         <is>
-          <t>Decided (your comment)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J70" s="32" t="n"/>
@@ -18463,24 +18463,24 @@
       </c>
       <c r="D71" s="32" t="inlineStr">
         <is>
-          <t>Metrics</t>
+          <t>Fast Track</t>
         </is>
       </c>
       <c r="E71" s="32" t="inlineStr">
         <is>
-          <t>Inputs missing</t>
+          <t>All Fast Track fields done</t>
         </is>
       </c>
       <c r="F71" s="32" t="inlineStr">
         <is>
-          <t>Metric card shows 'Locked: needs 2 numbers' and jumps to them</t>
+          <t>Every lens turns on (net worth, savings rate, DRAFTT, FI date)</t>
         </is>
       </c>
       <c r="G71" s="32" t="n"/>
       <c r="H71" s="32" t="n"/>
       <c r="I71" s="32" t="inlineStr">
         <is>
-          <t>Decided (metrics unlocked)</t>
+          <t>Decided (your comment: enough to turn on every lens)</t>
         </is>
       </c>
       <c r="J71" s="32" t="n"/>
@@ -18503,35 +18503,35 @@
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
-          <t>Order and priority</t>
+          <t>Completion</t>
         </is>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
-          <t>Next 3 numbers</t>
+          <t>Fast Track accuracy</t>
         </is>
       </c>
       <c r="E72" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Fast Track result vs full-detail result</t>
         </is>
       </c>
       <c r="F72" s="32" t="inlineStr">
         <is>
-          <t>Rank empty, Not sure and Not now fields by how much they move FI date and core metrics; ignore gated-out fields</t>
+          <t>Target: within $100/month of the full answer. Track the gap after each full session</t>
         </is>
       </c>
       <c r="G72" s="32" t="n"/>
       <c r="H72" s="32" t="n"/>
       <c r="I72" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 7 dependency ranking)</t>
+          <t>Decided (your comment)</t>
         </is>
       </c>
       <c r="J72" s="32" t="n"/>
       <c r="K72" s="33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -18548,35 +18548,35 @@
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
-          <t>Order and priority</t>
+          <t>Completion</t>
         </is>
       </c>
       <c r="D73" s="32" t="inlineStr">
         <is>
-          <t>Next 3 numbers</t>
+          <t>Metrics</t>
         </is>
       </c>
       <c r="E73" s="32" t="inlineStr">
         <is>
-          <t>Two fields tie</t>
+          <t>Inputs missing</t>
         </is>
       </c>
       <c r="F73" s="32" t="inlineStr">
         <is>
-          <t>Primary before Secondary, then the order the field appears on screen</t>
+          <t>Metric card shows 'Locked: needs 2 numbers' and jumps to them</t>
         </is>
       </c>
       <c r="G73" s="32" t="n"/>
       <c r="H73" s="32" t="n"/>
       <c r="I73" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (metrics unlocked)</t>
         </is>
       </c>
       <c r="J73" s="32" t="n"/>
       <c r="K73" s="33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -18598,24 +18598,24 @@
       </c>
       <c r="D74" s="32" t="inlineStr">
         <is>
-          <t>Materiality</t>
+          <t>Next 3 numbers</t>
         </is>
       </c>
       <c r="E74" s="32" t="inlineStr">
         <is>
-          <t>A field's effect is under $100/year</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F74" s="32" t="inlineStr">
         <is>
-          <t>Never in Next 3; goes to the Small wins tab</t>
+          <t>Rank empty, Not sure and Not now fields by how much they move FI date and core metrics; ignore gated-out fields</t>
         </is>
       </c>
       <c r="G74" s="32" t="n"/>
       <c r="H74" s="32" t="n"/>
       <c r="I74" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 2)</t>
+          <t>Decided (Oct 7 dependency ranking)</t>
         </is>
       </c>
       <c r="J74" s="32" t="n"/>
@@ -18643,28 +18643,24 @@
       </c>
       <c r="D75" s="32" t="inlineStr">
         <is>
-          <t>Debt payoff order</t>
+          <t>Next 3 numbers</t>
         </is>
       </c>
       <c r="E75" s="32" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Two fields tie</t>
         </is>
       </c>
       <c r="F75" s="32" t="inlineStr">
         <is>
-          <t>Highest APR first</t>
-        </is>
-      </c>
-      <c r="G75" s="32" t="inlineStr">
-        <is>
-          <t>Snowball: smallest balance first. Stress: highest stress first, ties by APR</t>
-        </is>
-      </c>
+          <t>Primary before Secondary, then the order the field appears on screen</t>
+        </is>
+      </c>
+      <c r="G75" s="32" t="n"/>
       <c r="H75" s="32" t="n"/>
       <c r="I75" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 2)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J75" s="32" t="n"/>
@@ -18692,24 +18688,24 @@
       </c>
       <c r="D76" s="32" t="inlineStr">
         <is>
-          <t>Promo rates</t>
+          <t>Materiality</t>
         </is>
       </c>
       <c r="E76" s="32" t="inlineStr">
         <is>
-          <t>0% promo ends within 60 days</t>
+          <t>A field's effect is under $100/year</t>
         </is>
       </c>
       <c r="F76" s="32" t="inlineStr">
         <is>
-          <t>Card jumps to the top of payoff order and shows a warning</t>
+          <t>Never in Next 3; goes to the Small wins tab</t>
         </is>
       </c>
       <c r="G76" s="32" t="n"/>
       <c r="H76" s="32" t="n"/>
       <c r="I76" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (Oct 2)</t>
         </is>
       </c>
       <c r="J76" s="32" t="n"/>
@@ -18737,24 +18733,28 @@
       </c>
       <c r="D77" s="32" t="inlineStr">
         <is>
-          <t>Guide me</t>
+          <t>Debt payoff order</t>
         </is>
       </c>
       <c r="E77" s="32" t="inlineStr">
         <is>
-          <t>Turned on</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="F77" s="32" t="inlineStr">
         <is>
-          <t>Follows the session 1 curriculum order; skips gated-out and done fields</t>
-        </is>
-      </c>
-      <c r="G77" s="32" t="n"/>
+          <t>Highest APR first</t>
+        </is>
+      </c>
+      <c r="G77" s="32" t="inlineStr">
+        <is>
+          <t>Snowball: smallest balance first. Stress: highest stress first, ties by APR</t>
+        </is>
+      </c>
       <c r="H77" s="32" t="n"/>
       <c r="I77" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 7)</t>
+          <t>Decided (Oct 2)</t>
         </is>
       </c>
       <c r="J77" s="32" t="n"/>
@@ -18777,35 +18777,35 @@
       </c>
       <c r="C78" s="32" t="inlineStr">
         <is>
-          <t>Visibility</t>
+          <t>Order and priority</t>
         </is>
       </c>
       <c r="D78" s="32" t="inlineStr">
         <is>
-          <t>Client view</t>
+          <t>Promo rates</t>
         </is>
       </c>
       <c r="E78" s="32" t="inlineStr">
         <is>
-          <t>On</t>
+          <t>0% promo ends within 60 days</t>
         </is>
       </c>
       <c r="F78" s="32" t="inlineStr">
         <is>
-          <t>Hides private notes, stress ratings, coach-only fields, the gear, other clients' names; text 15% bigger</t>
+          <t>Card jumps to the top of payoff order and shows a warning</t>
         </is>
       </c>
       <c r="G78" s="32" t="n"/>
       <c r="H78" s="32" t="n"/>
       <c r="I78" s="32" t="inlineStr">
         <is>
-          <t>Decided (session gaps)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J78" s="32" t="n"/>
       <c r="K78" s="33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -18822,35 +18822,35 @@
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
-          <t>Visibility</t>
+          <t>Order and priority</t>
         </is>
       </c>
       <c r="D79" s="32" t="inlineStr">
         <is>
-          <t>Coach tools</t>
+          <t>Guide me</t>
         </is>
       </c>
       <c r="E79" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Turned on</t>
         </is>
       </c>
       <c r="F79" s="32" t="inlineStr">
         <is>
-          <t>Behind the gear, never on a main tab</t>
+          <t>Follows the session 1 curriculum order; skips gated-out and done fields</t>
         </is>
       </c>
       <c r="G79" s="32" t="n"/>
       <c r="H79" s="32" t="n"/>
       <c r="I79" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 27)</t>
+          <t>Decided (Oct 7)</t>
         </is>
       </c>
       <c r="J79" s="32" t="n"/>
       <c r="K79" s="33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -18872,17 +18872,17 @@
       </c>
       <c r="D80" s="32" t="inlineStr">
         <is>
-          <t>Private notes</t>
+          <t>Client view</t>
         </is>
       </c>
       <c r="E80" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>On</t>
         </is>
       </c>
       <c r="F80" s="32" t="inlineStr">
         <is>
-          <t>Never shown in client view, the one-pager, exports to the client or the pre-call form</t>
+          <t>Hides private notes, stress ratings, coach-only fields, the gear, other clients' names; text 15% bigger</t>
         </is>
       </c>
       <c r="G80" s="32" t="n"/>
@@ -18917,24 +18917,24 @@
       </c>
       <c r="D81" s="32" t="inlineStr">
         <is>
-          <t>Colors</t>
+          <t>Coach tools</t>
         </is>
       </c>
       <c r="E81" s="32" t="inlineStr">
         <is>
-          <t>Any difference or warning</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F81" s="32" t="inlineStr">
         <is>
-          <t>Never red; use neutral and calm tones</t>
+          <t>Behind the gear, never on a main tab</t>
         </is>
       </c>
       <c r="G81" s="32" t="n"/>
       <c r="H81" s="32" t="n"/>
       <c r="I81" s="32" t="inlineStr">
         <is>
-          <t>Decided (nine tiles never red)</t>
+          <t>Decided (Oct 27)</t>
         </is>
       </c>
       <c r="J81" s="32" t="n"/>
@@ -18962,24 +18962,24 @@
       </c>
       <c r="D82" s="32" t="inlineStr">
         <is>
-          <t>Pre-call form</t>
+          <t>Private notes</t>
         </is>
       </c>
       <c r="E82" s="32" t="inlineStr">
         <is>
-          <t>Start of the client program</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F82" s="32" t="inlineStr">
         <is>
-          <t>You fill Level 1 yourself in session 1; the client-facing link is built later with the same questions</t>
+          <t>Never shown in client view, the one-pager, exports to the client or the pre-call form</t>
         </is>
       </c>
       <c r="G82" s="32" t="n"/>
       <c r="H82" s="32" t="n"/>
       <c r="I82" s="32" t="inlineStr">
         <is>
-          <t>Decided (your comment: I'll be filling it out to start)</t>
+          <t>Decided (session gaps)</t>
         </is>
       </c>
       <c r="J82" s="32" t="n"/>
@@ -19002,35 +19002,35 @@
       </c>
       <c r="C83" s="32" t="inlineStr">
         <is>
-          <t>Data safety</t>
+          <t>Visibility</t>
         </is>
       </c>
       <c r="D83" s="32" t="inlineStr">
         <is>
-          <t>Delete row</t>
+          <t>Colors</t>
         </is>
       </c>
       <c r="E83" s="32" t="inlineStr">
         <is>
-          <t>Clicked</t>
+          <t>Any difference or warning</t>
         </is>
       </c>
       <c r="F83" s="32" t="inlineStr">
         <is>
-          <t>Row removed, 'Undo' toast for 10 seconds</t>
+          <t>Never red; use neutral and calm tones</t>
         </is>
       </c>
       <c r="G83" s="32" t="n"/>
       <c r="H83" s="32" t="n"/>
       <c r="I83" s="32" t="inlineStr">
         <is>
-          <t>Decided (screen review)</t>
+          <t>Decided (nine tiles never red)</t>
         </is>
       </c>
       <c r="J83" s="32" t="n"/>
       <c r="K83" s="33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -19047,35 +19047,35 @@
       </c>
       <c r="C84" s="32" t="inlineStr">
         <is>
-          <t>Data safety</t>
+          <t>Visibility</t>
         </is>
       </c>
       <c r="D84" s="32" t="inlineStr">
         <is>
-          <t>Reset row</t>
+          <t>Pre-call form</t>
         </is>
       </c>
       <c r="E84" s="32" t="inlineStr">
         <is>
-          <t>Clicked</t>
+          <t>Start of the client program</t>
         </is>
       </c>
       <c r="F84" s="32" t="inlineStr">
         <is>
-          <t>All fields blank, status cleared, row kept; Undo toast</t>
+          <t>You fill Level 1 yourself in session 1; the client-facing link is built later with the same questions</t>
         </is>
       </c>
       <c r="G84" s="32" t="n"/>
       <c r="H84" s="32" t="n"/>
       <c r="I84" s="32" t="inlineStr">
         <is>
-          <t>Decided</t>
+          <t>Decided (your comment: I'll be filling it out to start)</t>
         </is>
       </c>
       <c r="J84" s="32" t="n"/>
       <c r="K84" s="33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -19097,7 +19097,7 @@
       </c>
       <c r="D85" s="32" t="inlineStr">
         <is>
-          <t>Reset section</t>
+          <t>Delete row</t>
         </is>
       </c>
       <c r="E85" s="32" t="inlineStr">
@@ -19107,14 +19107,14 @@
       </c>
       <c r="F85" s="32" t="inlineStr">
         <is>
-          <t>Confirm dialog naming the section; Undo toast</t>
+          <t>Row removed, 'Undo' toast for 10 seconds</t>
         </is>
       </c>
       <c r="G85" s="32" t="n"/>
       <c r="H85" s="32" t="n"/>
       <c r="I85" s="32" t="inlineStr">
         <is>
-          <t>Decided</t>
+          <t>Decided (screen review)</t>
         </is>
       </c>
       <c r="J85" s="32" t="n"/>
@@ -19142,7 +19142,7 @@
       </c>
       <c r="D86" s="32" t="inlineStr">
         <is>
-          <t>Reset client</t>
+          <t>Reset row</t>
         </is>
       </c>
       <c r="E86" s="32" t="inlineStr">
@@ -19152,7 +19152,7 @@
       </c>
       <c r="F86" s="32" t="inlineStr">
         <is>
-          <t>Must type the client's name; snapshot taken first</t>
+          <t>All fields blank, status cleared, row kept; Undo toast</t>
         </is>
       </c>
       <c r="G86" s="32" t="n"/>
@@ -19187,24 +19187,24 @@
       </c>
       <c r="D87" s="32" t="inlineStr">
         <is>
-          <t>Autosave</t>
+          <t>Reset section</t>
         </is>
       </c>
       <c r="E87" s="32" t="inlineStr">
         <is>
-          <t>Any change</t>
+          <t>Clicked</t>
         </is>
       </c>
       <c r="F87" s="32" t="inlineStr">
         <is>
-          <t>Saved within 1 second; 'Unsaved' shown if it fails; warning before closing the tab</t>
+          <t>Confirm dialog naming the section; Undo toast</t>
         </is>
       </c>
       <c r="G87" s="32" t="n"/>
       <c r="H87" s="32" t="n"/>
       <c r="I87" s="32" t="inlineStr">
         <is>
-          <t>Decided (session gaps)</t>
+          <t>Decided</t>
         </is>
       </c>
       <c r="J87" s="32" t="n"/>
@@ -19232,24 +19232,24 @@
       </c>
       <c r="D88" s="32" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Reset client</t>
         </is>
       </c>
       <c r="E88" s="32" t="inlineStr">
         <is>
-          <t>File imported</t>
+          <t>Clicked</t>
         </is>
       </c>
       <c r="F88" s="32" t="inlineStr">
         <is>
-          <t>Snapshot taken first so it can be undone</t>
+          <t>Must type the client's name; snapshot taken first</t>
         </is>
       </c>
       <c r="G88" s="32" t="n"/>
       <c r="H88" s="32" t="n"/>
       <c r="I88" s="32" t="inlineStr">
         <is>
-          <t>Decided (Sept export/import)</t>
+          <t>Decided</t>
         </is>
       </c>
       <c r="J88" s="32" t="n"/>
@@ -19277,24 +19277,24 @@
       </c>
       <c r="D89" s="32" t="inlineStr">
         <is>
-          <t>Undo / redo</t>
+          <t>Autosave</t>
         </is>
       </c>
       <c r="E89" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Any change</t>
         </is>
       </c>
       <c r="F89" s="32" t="inlineStr">
         <is>
-          <t>Covers every change on every screen, including deletes and resets</t>
+          <t>Saved within 1 second; 'Unsaved' shown if it fails; warning before closing the tab</t>
         </is>
       </c>
       <c r="G89" s="32" t="n"/>
       <c r="H89" s="32" t="n"/>
       <c r="I89" s="32" t="inlineStr">
         <is>
-          <t>Decided (Sept)</t>
+          <t>Decided (session gaps)</t>
         </is>
       </c>
       <c r="J89" s="32" t="n"/>
@@ -19322,24 +19322,24 @@
       </c>
       <c r="D90" s="32" t="inlineStr">
         <is>
-          <t>Linked records</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="E90" s="32" t="inlineStr">
         <is>
-          <t>A debt linked to an asset is deleted</t>
+          <t>File imported</t>
         </is>
       </c>
       <c r="F90" s="32" t="inlineStr">
         <is>
-          <t>Ask: delete the loan only, or the asset too</t>
+          <t>Snapshot taken first so it can be undone</t>
         </is>
       </c>
       <c r="G90" s="32" t="n"/>
       <c r="H90" s="32" t="n"/>
       <c r="I90" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (Sept export/import)</t>
         </is>
       </c>
       <c r="J90" s="32" t="n"/>
@@ -19362,12 +19362,12 @@
       </c>
       <c r="C91" s="32" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Data safety</t>
         </is>
       </c>
       <c r="D91" s="32" t="inlineStr">
         <is>
-          <t>Maybe entries</t>
+          <t>Undo / redo</t>
         </is>
       </c>
       <c r="E91" s="32" t="inlineStr">
@@ -19377,20 +19377,20 @@
       </c>
       <c r="F91" s="32" t="inlineStr">
         <is>
-          <t>Dashed chip; left out of the running balance unless 'Count maybe' is on</t>
+          <t>Covers every change on every screen, including deletes and resets</t>
         </is>
       </c>
       <c r="G91" s="32" t="n"/>
       <c r="H91" s="32" t="n"/>
       <c r="I91" s="32" t="inlineStr">
         <is>
-          <t>Decided (your comment)</t>
+          <t>Decided (Sept)</t>
         </is>
       </c>
       <c r="J91" s="32" t="n"/>
       <c r="K91" s="33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -19407,35 +19407,35 @@
       </c>
       <c r="C92" s="32" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Data safety</t>
         </is>
       </c>
       <c r="D92" s="32" t="inlineStr">
         <is>
-          <t>Got it / Paid</t>
+          <t>Linked records</t>
         </is>
       </c>
       <c r="E92" s="32" t="inlineStr">
         <is>
-          <t>Clicked</t>
+          <t>A debt linked to an asset is deleted</t>
         </is>
       </c>
       <c r="F92" s="32" t="inlineStr">
         <is>
-          <t>Planned or maybe becomes actual on the real date and amount</t>
+          <t>Ask: delete the loan only, or the asset too</t>
         </is>
       </c>
       <c r="G92" s="32" t="n"/>
       <c r="H92" s="32" t="n"/>
       <c r="I92" s="32" t="inlineStr">
         <is>
-          <t>Decided (your comment)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J92" s="32" t="n"/>
       <c r="K92" s="33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -19457,7 +19457,7 @@
       </c>
       <c r="D93" s="32" t="inlineStr">
         <is>
-          <t>Entry status</t>
+          <t>Maybe entries</t>
         </is>
       </c>
       <c r="E93" s="32" t="inlineStr">
@@ -19467,14 +19467,14 @@
       </c>
       <c r="F93" s="32" t="inlineStr">
         <is>
-          <t>Each calendar entry is Planned, Partial, Got it / Paid, Didn't happen, or Moved</t>
+          <t>Dashed chip; left out of the running balance unless 'Count maybe' is on</t>
         </is>
       </c>
       <c r="G93" s="32" t="n"/>
       <c r="H93" s="32" t="n"/>
       <c r="I93" s="32" t="inlineStr">
         <is>
-          <t>Decided (your comment on R048)</t>
+          <t>Decided (your comment)</t>
         </is>
       </c>
       <c r="J93" s="32" t="n"/>
@@ -19502,24 +19502,24 @@
       </c>
       <c r="D94" s="32" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Got it / Paid</t>
         </is>
       </c>
       <c r="E94" s="32" t="inlineStr">
         <is>
-          <t>Some of the money came or was paid</t>
+          <t>Clicked</t>
         </is>
       </c>
       <c r="F94" s="32" t="inlineStr">
         <is>
-          <t>Enter the amount so far; the rest stays Planned on the same entry. Update it later instead of starting over</t>
+          <t>Planned or maybe becomes actual on the real date and amount</t>
         </is>
       </c>
       <c r="G94" s="32" t="n"/>
       <c r="H94" s="32" t="n"/>
       <c r="I94" s="32" t="inlineStr">
         <is>
-          <t>Decided (your comment on R048)</t>
+          <t>Decided (your comment)</t>
         </is>
       </c>
       <c r="J94" s="32" t="n"/>
@@ -19547,28 +19547,24 @@
       </c>
       <c r="D95" s="32" t="inlineStr">
         <is>
-          <t>Didn't happen</t>
+          <t>Entry status</t>
         </is>
       </c>
       <c r="E95" s="32" t="inlineStr">
         <is>
-          <t>Clicked</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F95" s="32" t="inlineStr">
         <is>
-          <t>Entry kept, greyed, counted as $0 actual so the miss shows in month-end close</t>
-        </is>
-      </c>
-      <c r="G95" s="32" t="inlineStr">
-        <is>
-          <t>Moved: pick a new date, original date keeps a faint marker</t>
-        </is>
-      </c>
+          <t>Each calendar entry is Planned, Partial, Got it / Paid, Didn't happen, or Moved</t>
+        </is>
+      </c>
+      <c r="G95" s="32" t="n"/>
       <c r="H95" s="32" t="n"/>
       <c r="I95" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (your comment on R048)</t>
         </is>
       </c>
       <c r="J95" s="32" t="n"/>
@@ -19596,24 +19592,24 @@
       </c>
       <c r="D96" s="32" t="inlineStr">
         <is>
-          <t>Wins</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E96" s="32" t="inlineStr">
         <is>
-          <t>A payoff date, milestone or FI step is reached in the projection</t>
+          <t>Some of the money came or was paid</t>
         </is>
       </c>
       <c r="F96" s="32" t="inlineStr">
         <is>
-          <t>Win chip appears on that date automatically</t>
+          <t>Enter the amount so far; the rest stays Planned on the same entry. Update it later instead of starting over</t>
         </is>
       </c>
       <c r="G96" s="32" t="n"/>
       <c r="H96" s="32" t="n"/>
       <c r="I96" s="32" t="inlineStr">
         <is>
-          <t>Decided (your comment)</t>
+          <t>Decided (your comment on R048)</t>
         </is>
       </c>
       <c r="J96" s="32" t="n"/>
@@ -19641,20 +19637,24 @@
       </c>
       <c r="D97" s="32" t="inlineStr">
         <is>
-          <t>Low balance</t>
+          <t>Didn't happen</t>
         </is>
       </c>
       <c r="E97" s="32" t="inlineStr">
         <is>
-          <t>End-of-day balance below the line</t>
+          <t>Clicked</t>
         </is>
       </c>
       <c r="F97" s="32" t="inlineStr">
         <is>
-          <t>Day shows ⚠ and Home shows the first such day</t>
-        </is>
-      </c>
-      <c r="G97" s="32" t="n"/>
+          <t>Entry kept, greyed, counted as $0 actual so the miss shows in month-end close</t>
+        </is>
+      </c>
+      <c r="G97" s="32" t="inlineStr">
+        <is>
+          <t>Moved: pick a new date, original date keeps a faint marker</t>
+        </is>
+      </c>
       <c r="H97" s="32" t="n"/>
       <c r="I97" s="32" t="inlineStr">
         <is>
@@ -19686,24 +19686,24 @@
       </c>
       <c r="D98" s="32" t="inlineStr">
         <is>
-          <t>Repeats</t>
+          <t>Wins</t>
         </is>
       </c>
       <c r="E98" s="32" t="inlineStr">
         <is>
-          <t>Twice a month</t>
+          <t>A payoff date, milestone or FI step is reached in the projection</t>
         </is>
       </c>
       <c r="F98" s="32" t="inlineStr">
         <is>
-          <t>1st and 15th unless days are set</t>
+          <t>Win chip appears on that date automatically</t>
         </is>
       </c>
       <c r="G98" s="32" t="n"/>
       <c r="H98" s="32" t="n"/>
       <c r="I98" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (your comment)</t>
         </is>
       </c>
       <c r="J98" s="32" t="n"/>
@@ -19731,24 +19731,24 @@
       </c>
       <c r="D99" s="32" t="inlineStr">
         <is>
-          <t>Paychecks</t>
+          <t>Low balance</t>
         </is>
       </c>
       <c r="E99" s="32" t="inlineStr">
         <is>
-          <t>Every-2-weeks pay lands 3 times in a month</t>
+          <t>End-of-day balance below the line</t>
         </is>
       </c>
       <c r="F99" s="32" t="inlineStr">
         <is>
-          <t>Month marked 'bonus paycheck month'</t>
+          <t>Day shows ⚠ and Home shows the first such day</t>
         </is>
       </c>
       <c r="G99" s="32" t="n"/>
       <c r="H99" s="32" t="n"/>
       <c r="I99" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 22)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J99" s="32" t="n"/>
@@ -19771,29 +19771,29 @@
       </c>
       <c r="C100" s="32" t="inlineStr">
         <is>
-          <t>Paid with (bill to card)</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="D100" s="32" t="inlineStr">
         <is>
-          <t>Needs lines, calendar entries, irregular costs</t>
+          <t>Repeats</t>
         </is>
       </c>
       <c r="E100" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Twice a month</t>
         </is>
       </c>
       <c r="F100" s="32" t="inlineStr">
         <is>
-          <t>Every bill can carry 'Paid with ▾': checking, savings, or any credit card on file. Tertiary by default</t>
+          <t>1st and 15th unless days are set</t>
         </is>
       </c>
       <c r="G100" s="32" t="n"/>
       <c r="H100" s="32" t="n"/>
       <c r="I100" s="32" t="inlineStr">
         <is>
-          <t>Decided (your message: link a bill to a credit card, tertiary)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J100" s="32" t="n"/>
@@ -19816,29 +19816,29 @@
       </c>
       <c r="C101" s="32" t="inlineStr">
         <is>
-          <t>Paid with (bill to card)</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="D101" s="32" t="inlineStr">
         <is>
-          <t>Where it lives</t>
+          <t>Paychecks</t>
         </is>
       </c>
       <c r="E101" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Every-2-weeks pay lands 3 times in a month</t>
         </is>
       </c>
       <c r="F101" s="32" t="inlineStr">
         <is>
-          <t>Paid with sits at the top of the row's More ▸ area, so it's 3 clicks from any bill</t>
+          <t>Month marked 'bonus paycheck month'</t>
         </is>
       </c>
       <c r="G101" s="32" t="n"/>
       <c r="H101" s="32" t="n"/>
       <c r="I101" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 28)</t>
+          <t>Decided (Oct 22)</t>
         </is>
       </c>
       <c r="J101" s="32" t="n"/>
@@ -19866,24 +19866,24 @@
       </c>
       <c r="D102" s="32" t="inlineStr">
         <is>
-          <t>Paid with = a credit card</t>
+          <t>Needs lines, calendar entries, irregular costs</t>
         </is>
       </c>
       <c r="E102" s="32" t="inlineStr">
         <is>
-          <t>Bill linked</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F102" s="32" t="inlineStr">
         <is>
-          <t>The charge adds to that card's expected balance on its date; the calendar shows it on the card, not on checking; the card's payment day pulls the total</t>
+          <t>Every bill can carry 'Paid with ▾': checking, savings, or any credit card on file. Tertiary by default</t>
         </is>
       </c>
       <c r="G102" s="32" t="n"/>
       <c r="H102" s="32" t="n"/>
       <c r="I102" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (your message: link a bill to a credit card, tertiary)</t>
         </is>
       </c>
       <c r="J102" s="32" t="n"/>
@@ -19911,28 +19911,24 @@
       </c>
       <c r="D103" s="32" t="inlineStr">
         <is>
-          <t>Promote to Secondary</t>
+          <t>Where it lives</t>
         </is>
       </c>
       <c r="E103" s="32" t="inlineStr">
         <is>
-          <t>Client says most spending goes on cards (Profile toggle)</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F103" s="32" t="inlineStr">
         <is>
-          <t>'Paid with' moves up to Secondary on every line</t>
-        </is>
-      </c>
-      <c r="G103" s="32" t="inlineStr">
-        <is>
-          <t>Stays Tertiary</t>
-        </is>
-      </c>
+          <t>Paid with sits at the top of the row's More ▸ area, so it's 3 clicks from any bill</t>
+        </is>
+      </c>
+      <c r="G103" s="32" t="n"/>
       <c r="H103" s="32" t="n"/>
       <c r="I103" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (Oct 28)</t>
         </is>
       </c>
       <c r="J103" s="32" t="n"/>
@@ -19960,17 +19956,17 @@
       </c>
       <c r="D104" s="32" t="inlineStr">
         <is>
-          <t>Card row</t>
+          <t>Paid with = a credit card</t>
         </is>
       </c>
       <c r="E104" s="32" t="inlineStr">
         <is>
-          <t>Bills are linked to the card</t>
+          <t>Bill linked</t>
         </is>
       </c>
       <c r="F104" s="32" t="inlineStr">
         <is>
-          <t>Card's Secondary shows 'Bills on this card: 6, $412/mo' with a list</t>
+          <t>The charge adds to that card's expected balance on its date; the calendar shows it on the card, not on checking; the card's payment day pulls the total</t>
         </is>
       </c>
       <c r="G104" s="32" t="n"/>
@@ -20005,22 +20001,22 @@
       </c>
       <c r="D105" s="32" t="inlineStr">
         <is>
-          <t>Card paid in full monthly</t>
+          <t>Promote to Secondary</t>
         </is>
       </c>
       <c r="E105" s="32" t="inlineStr">
         <is>
-          <t>Pay = In full</t>
+          <t>Client says most spending goes on cards (Profile toggle)</t>
         </is>
       </c>
       <c r="F105" s="32" t="inlineStr">
         <is>
-          <t>Linked bills count as spending, not debt; no interest</t>
+          <t>'Paid with' moves up to Secondary on every line</t>
         </is>
       </c>
       <c r="G105" s="32" t="inlineStr">
         <is>
-          <t>Carrying a balance: linked bills add to the payoff projection</t>
+          <t>Stays Tertiary</t>
         </is>
       </c>
       <c r="H105" s="32" t="n"/>
@@ -20049,35 +20045,35 @@
       </c>
       <c r="C106" s="32" t="inlineStr">
         <is>
-          <t>Staples (same everywhere)</t>
+          <t>Paid with (bill to card)</t>
         </is>
       </c>
       <c r="D106" s="32" t="inlineStr">
         <is>
-          <t>Every section</t>
+          <t>Card row</t>
         </is>
       </c>
       <c r="E106" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Bills are linked to the card</t>
         </is>
       </c>
       <c r="F106" s="32" t="inlineStr">
         <is>
-          <t>One '+ Add [thing]' button in the same spot (bottom left of the section), same look</t>
+          <t>Card's Secondary shows 'Bills on this card: 6, $412/mo' with a list</t>
         </is>
       </c>
       <c r="G106" s="32" t="n"/>
       <c r="H106" s="32" t="n"/>
       <c r="I106" s="32" t="inlineStr">
         <is>
-          <t>Decided (your message: uniform staples)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J106" s="32" t="n"/>
       <c r="K106" s="33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -20094,35 +20090,39 @@
       </c>
       <c r="C107" s="32" t="inlineStr">
         <is>
-          <t>Staples (same everywhere)</t>
+          <t>Paid with (bill to card)</t>
         </is>
       </c>
       <c r="D107" s="32" t="inlineStr">
         <is>
-          <t>Every add picker</t>
+          <t>Card paid in full monthly</t>
         </is>
       </c>
       <c r="E107" s="32" t="inlineStr">
         <is>
-          <t>Clicked</t>
+          <t>Pay = In full</t>
         </is>
       </c>
       <c r="F107" s="32" t="inlineStr">
         <is>
-          <t>Top 4 types as big buttons, Other opens the rest with search, 'Name your own' at the end</t>
-        </is>
-      </c>
-      <c r="G107" s="32" t="n"/>
+          <t>Linked bills count as spending, not debt; no interest</t>
+        </is>
+      </c>
+      <c r="G107" s="32" t="inlineStr">
+        <is>
+          <t>Carrying a balance: linked bills add to the payoff projection</t>
+        </is>
+      </c>
       <c r="H107" s="32" t="n"/>
       <c r="I107" s="32" t="inlineStr">
         <is>
-          <t>Decided (your Mockup comment, made universal)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J107" s="32" t="n"/>
       <c r="K107" s="33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -20144,7 +20144,7 @@
       </c>
       <c r="D108" s="32" t="inlineStr">
         <is>
-          <t>Every row</t>
+          <t>Every section</t>
         </is>
       </c>
       <c r="E108" s="32" t="inlineStr">
@@ -20154,14 +20154,14 @@
       </c>
       <c r="F108" s="32" t="inlineStr">
         <is>
-          <t>Same anatomy left to right: type/name, amount, per, owner (couples), status, ⧉ ↺ 🗑, ▸ More</t>
+          <t>One '+ Add [thing]' button in the same spot (bottom left of the section), same look</t>
         </is>
       </c>
       <c r="G108" s="32" t="n"/>
       <c r="H108" s="32" t="n"/>
       <c r="I108" s="32" t="inlineStr">
         <is>
-          <t>Decided</t>
+          <t>Decided (your message: uniform staples)</t>
         </is>
       </c>
       <c r="J108" s="32" t="n"/>
@@ -20189,24 +20189,24 @@
       </c>
       <c r="D109" s="32" t="inlineStr">
         <is>
-          <t>Quick add</t>
+          <t>Every add picker</t>
         </is>
       </c>
       <c r="E109" s="32" t="inlineStr">
         <is>
-          <t>Top bar</t>
+          <t>Clicked</t>
         </is>
       </c>
       <c r="F109" s="32" t="inlineStr">
         <is>
-          <t>'+ Add anything' box: type 'Netflix 15.99 monthly' or 'Chase card 3200 at 24%' and it picks the type and section; you confirm</t>
+          <t>Top 4 types as big buttons, Other opens the rest with search, 'Name your own' at the end</t>
         </is>
       </c>
       <c r="G109" s="32" t="n"/>
       <c r="H109" s="32" t="n"/>
       <c r="I109" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (your Mockup comment, made universal)</t>
         </is>
       </c>
       <c r="J109" s="32" t="n"/>
@@ -20234,24 +20234,24 @@
       </c>
       <c r="D110" s="32" t="inlineStr">
         <is>
-          <t>Add from anywhere</t>
+          <t>Every row</t>
         </is>
       </c>
       <c r="E110" s="32" t="inlineStr">
         <is>
-          <t>Adding from Home, calendar or a chart</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F110" s="32" t="inlineStr">
         <is>
-          <t>Opens the same add picker and drops the row in its home section; no screen switch</t>
+          <t>Same anatomy left to right: type/name, amount, per, owner (couples), status, ⧉ ↺ 🗑, ▸ More</t>
         </is>
       </c>
       <c r="G110" s="32" t="n"/>
       <c r="H110" s="32" t="n"/>
       <c r="I110" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided</t>
         </is>
       </c>
       <c r="J110" s="32" t="n"/>
@@ -20279,17 +20279,17 @@
       </c>
       <c r="D111" s="32" t="inlineStr">
         <is>
-          <t>Every section footer</t>
+          <t>Quick add</t>
         </is>
       </c>
       <c r="E111" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Top bar</t>
         </is>
       </c>
       <c r="F111" s="32" t="inlineStr">
         <is>
-          <t>Total, count, completion bar in the same spot</t>
+          <t>'+ Add anything' box: type 'Netflix 15.99 monthly' or 'Chase card 3200 at 24%' and it picks the type and section; you confirm</t>
         </is>
       </c>
       <c r="G111" s="32" t="n"/>
@@ -20319,29 +20319,29 @@
       </c>
       <c r="C112" s="32" t="inlineStr">
         <is>
-          <t>Bulk select</t>
+          <t>Staples (same everywhere)</t>
         </is>
       </c>
       <c r="D112" s="32" t="inlineStr">
         <is>
-          <t>Every multi-item list</t>
+          <t>Add from anywhere</t>
         </is>
       </c>
       <c r="E112" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Adding from Home, calendar or a chart</t>
         </is>
       </c>
       <c r="F112" s="32" t="inlineStr">
         <is>
-          <t>Each row has a checkbox on the far left; the list header has 'Select all'</t>
+          <t>Opens the same add picker and drops the row in its home section; no screen switch</t>
         </is>
       </c>
       <c r="G112" s="32" t="n"/>
       <c r="H112" s="32" t="n"/>
       <c r="I112" s="32" t="inlineStr">
         <is>
-          <t>Decided (your message: multi-select like bills)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J112" s="32" t="n"/>
@@ -20364,12 +20364,12 @@
       </c>
       <c r="C113" s="32" t="inlineStr">
         <is>
-          <t>Bulk select</t>
+          <t>Staples (same everywhere)</t>
         </is>
       </c>
       <c r="D113" s="32" t="inlineStr">
         <is>
-          <t>One or more rows checked</t>
+          <t>Every section footer</t>
         </is>
       </c>
       <c r="E113" s="32" t="inlineStr">
@@ -20379,18 +20379,14 @@
       </c>
       <c r="F113" s="32" t="inlineStr">
         <is>
-          <t>A slim bar appears at the top of the list: Duplicate, Delete, Reset, Set status, Link to card, Clear selection</t>
-        </is>
-      </c>
-      <c r="G113" s="32" t="inlineStr">
-        <is>
-          <t>Bar disappears when nothing is checked</t>
-        </is>
-      </c>
+          <t>Total, count, completion bar in the same spot</t>
+        </is>
+      </c>
+      <c r="G113" s="32" t="n"/>
       <c r="H113" s="32" t="n"/>
       <c r="I113" s="32" t="inlineStr">
         <is>
-          <t>Decided</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J113" s="32" t="n"/>
@@ -20418,24 +20414,24 @@
       </c>
       <c r="D114" s="32" t="inlineStr">
         <is>
-          <t>Bulk delete or reset</t>
+          <t>Every multi-item list</t>
         </is>
       </c>
       <c r="E114" s="32" t="inlineStr">
         <is>
-          <t>Clicked</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F114" s="32" t="inlineStr">
         <is>
-          <t>One undo toast covers all of them ('Deleted 5. Undo')</t>
+          <t>Each row has a checkbox on the far left; the list header has 'Select all'</t>
         </is>
       </c>
       <c r="G114" s="32" t="n"/>
       <c r="H114" s="32" t="n"/>
       <c r="I114" s="32" t="inlineStr">
         <is>
-          <t>Decided</t>
+          <t>Decided (your message: multi-select like bills)</t>
         </is>
       </c>
       <c r="J114" s="32" t="n"/>
@@ -20463,24 +20459,28 @@
       </c>
       <c r="D115" s="32" t="inlineStr">
         <is>
-          <t>Link to card (bulk or row)</t>
+          <t>One or more rows checked</t>
         </is>
       </c>
       <c r="E115" s="32" t="inlineStr">
         <is>
-          <t>Clicked</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F115" s="32" t="inlineStr">
         <is>
-          <t>Shows the client's cards as buttons if there are 4 or fewer; a picker with search if more. One click links every selected bill</t>
-        </is>
-      </c>
-      <c r="G115" s="32" t="n"/>
+          <t>A slim bar appears at the top of the list: Duplicate, Delete, Reset, Set status, Link to card, Clear selection</t>
+        </is>
+      </c>
+      <c r="G115" s="32" t="inlineStr">
+        <is>
+          <t>Bar disappears when nothing is checked</t>
+        </is>
+      </c>
       <c r="H115" s="32" t="n"/>
       <c r="I115" s="32" t="inlineStr">
         <is>
-          <t>Decided (your message: easier with a couple of cards)</t>
+          <t>Decided</t>
         </is>
       </c>
       <c r="J115" s="32" t="n"/>
@@ -20508,24 +20508,24 @@
       </c>
       <c r="D116" s="32" t="inlineStr">
         <is>
-          <t>Link to card (single row)</t>
+          <t>Bulk delete or reset</t>
         </is>
       </c>
       <c r="E116" s="32" t="inlineStr">
         <is>
-          <t>More ▸ on the row</t>
+          <t>Clicked</t>
         </is>
       </c>
       <c r="F116" s="32" t="inlineStr">
         <is>
-          <t>Paid with shows the card buttons, so it's 3 clicks: More ▸ › Paid with › card name</t>
+          <t>One undo toast covers all of them ('Deleted 5. Undo')</t>
         </is>
       </c>
       <c r="G116" s="32" t="n"/>
       <c r="H116" s="32" t="n"/>
       <c r="I116" s="32" t="inlineStr">
         <is>
-          <t>Decided (your message: about three links away; no ⋯ menu)</t>
+          <t>Decided</t>
         </is>
       </c>
       <c r="J116" s="32" t="n"/>
@@ -20553,7 +20553,7 @@
       </c>
       <c r="D117" s="32" t="inlineStr">
         <is>
-          <t>Set status (bulk)</t>
+          <t>Link to card (bulk or row)</t>
         </is>
       </c>
       <c r="E117" s="32" t="inlineStr">
@@ -20563,14 +20563,14 @@
       </c>
       <c r="F117" s="32" t="inlineStr">
         <is>
-          <t>Applies one status (Roughly, Will email, etc.) to every selected row</t>
+          <t>Shows the client's cards as buttons if there are 4 or fewer; a picker with search if more. One click links every selected bill</t>
         </is>
       </c>
       <c r="G117" s="32" t="n"/>
       <c r="H117" s="32" t="n"/>
       <c r="I117" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (your message: easier with a couple of cards)</t>
         </is>
       </c>
       <c r="J117" s="32" t="n"/>
@@ -20593,35 +20593,35 @@
       </c>
       <c r="C118" s="32" t="inlineStr">
         <is>
-          <t>Data and timing</t>
+          <t>Bulk select</t>
         </is>
       </c>
       <c r="D118" s="32" t="inlineStr">
         <is>
-          <t>Every record</t>
+          <t>Link to card (single row)</t>
         </is>
       </c>
       <c r="E118" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>More ▸ on the row</t>
         </is>
       </c>
       <c r="F118" s="32" t="inlineStr">
         <is>
-          <t>One record type for bills, paychecks, debt payments, yearly costs: name, amount, how often, owner, status, paid with, linked to, source, covers period. Budget, calendar, card row and Needs are views of these records</t>
+          <t>Paid with shows the card buttons, so it's 3 clicks: More ▸ › Paid with › card name</t>
         </is>
       </c>
       <c r="G118" s="32" t="n"/>
       <c r="H118" s="32" t="n"/>
       <c r="I118" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (your message: about three links away; no ⋯ menu)</t>
         </is>
       </c>
       <c r="J118" s="32" t="n"/>
       <c r="K118" s="33" t="inlineStr">
         <is>
-          <t>1-6</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -20638,35 +20638,35 @@
       </c>
       <c r="C119" s="32" t="inlineStr">
         <is>
-          <t>Data and timing</t>
+          <t>Bulk select</t>
         </is>
       </c>
       <c r="D119" s="32" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Set status (bulk)</t>
         </is>
       </c>
       <c r="E119" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Clicked</t>
         </is>
       </c>
       <c r="F119" s="32" t="inlineStr">
         <is>
-          <t>Every record notes where it came from: manual, statement, or bank (future)</t>
+          <t>Applies one status (Roughly, Will email, etc.) to every selected row</t>
         </is>
       </c>
       <c r="G119" s="32" t="n"/>
       <c r="H119" s="32" t="n"/>
       <c r="I119" s="32" t="inlineStr">
         <is>
-          <t>Decided (manual now, statements next, bank one day)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J119" s="32" t="n"/>
       <c r="K119" s="33" t="inlineStr">
         <is>
-          <t>1-6</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -20688,24 +20688,24 @@
       </c>
       <c r="D120" s="32" t="inlineStr">
         <is>
-          <t>Statement upload</t>
+          <t>Every record</t>
         </is>
       </c>
       <c r="E120" s="32" t="inlineStr">
         <is>
-          <t>Later (phase 4)</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F120" s="32" t="inlineStr">
         <is>
-          <t>Upload a statement as CSV or PDF; lines are read and matched to existing records. Matches update actuals, new lines are offered as new records, likely duplicates are flagged for you to confirm</t>
+          <t>One record type for bills, paychecks, debt payments, yearly costs: name, amount, how often, owner, status, paid with, linked to, source, covers period. Budget, calendar, card row and Needs are views of these records</t>
         </is>
       </c>
       <c r="G120" s="32" t="n"/>
       <c r="H120" s="32" t="n"/>
       <c r="I120" s="32" t="inlineStr">
         <is>
-          <t>Decided (you want statement upload and consolidation)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J120" s="32" t="n"/>
@@ -20733,24 +20733,24 @@
       </c>
       <c r="D121" s="32" t="inlineStr">
         <is>
-          <t>Bank connection</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="E121" s="32" t="inlineStr">
         <is>
-          <t>Not planned</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F121" s="32" t="inlineStr">
         <is>
-          <t>Not built; records keep a 'bank' source value so it can slot in later without redesign</t>
+          <t>Every record notes where it came from: manual, statement, or bank (future)</t>
         </is>
       </c>
       <c r="G121" s="32" t="n"/>
       <c r="H121" s="32" t="n"/>
       <c r="I121" s="32" t="inlineStr">
         <is>
-          <t>Decided (one day, not soon)</t>
+          <t>Decided (manual now, statements next, bank one day)</t>
         </is>
       </c>
       <c r="J121" s="32" t="n"/>
@@ -20778,24 +20778,24 @@
       </c>
       <c r="D122" s="32" t="inlineStr">
         <is>
-          <t>Paid in advance</t>
+          <t>Statement upload</t>
         </is>
       </c>
       <c r="E122" s="32" t="inlineStr">
         <is>
-          <t>A payment covers future months (yearly insurance, prepaid rent, annual subscription)</t>
+          <t>Later (phase 4)</t>
         </is>
       </c>
       <c r="F122" s="32" t="inlineStr">
         <is>
-          <t>Enter the amount, the date paid, and the months it covers</t>
+          <t>Upload a statement as CSV or PDF; lines are read and matched to existing records. Matches update actuals, new lines are offered as new records, likely duplicates are flagged for you to confirm</t>
         </is>
       </c>
       <c r="G122" s="32" t="n"/>
       <c r="H122" s="32" t="n"/>
       <c r="I122" s="32" t="inlineStr">
         <is>
-          <t>Decided (your 'paying in advance')</t>
+          <t>Decided (you want statement upload and consolidation)</t>
         </is>
       </c>
       <c r="J122" s="32" t="n"/>
@@ -20823,24 +20823,24 @@
       </c>
       <c r="D123" s="32" t="inlineStr">
         <is>
-          <t>Cash vs accrual</t>
+          <t>Bank connection</t>
         </is>
       </c>
       <c r="E123" s="32" t="inlineStr">
         <is>
-          <t>Paid-in-advance or yearly record</t>
+          <t>Not planned</t>
         </is>
       </c>
       <c r="F123" s="32" t="inlineStr">
         <is>
-          <t>Calendar always shows cash basis (the day money left). Budget has a Cash | Accrual toggle: accrual spreads the cost across the months it covers</t>
+          <t>Not built; records keep a 'bank' source value so it can slot in later without redesign</t>
         </is>
       </c>
       <c r="G123" s="32" t="n"/>
       <c r="H123" s="32" t="n"/>
       <c r="I123" s="32" t="inlineStr">
         <is>
-          <t>Decided (you want both views)</t>
+          <t>Decided (one day, not soon)</t>
         </is>
       </c>
       <c r="J123" s="32" t="n"/>
@@ -20868,28 +20868,24 @@
       </c>
       <c r="D124" s="32" t="inlineStr">
         <is>
-          <t>Budget default basis</t>
+          <t>Paid in advance</t>
         </is>
       </c>
       <c r="E124" s="32" t="inlineStr">
         <is>
-          <t>Spending opened</t>
+          <t>A payment covers future months (yearly insurance, prepaid rent, annual subscription)</t>
         </is>
       </c>
       <c r="F124" s="32" t="inlineStr">
         <is>
-          <t>Accrual (monthly equivalent), so a yearly bill doesn't wreck one month</t>
-        </is>
-      </c>
-      <c r="G124" s="32" t="inlineStr">
-        <is>
-          <t>Cash view shows the real month it hit</t>
-        </is>
-      </c>
+          <t>Enter the amount, the date paid, and the months it covers</t>
+        </is>
+      </c>
+      <c r="G124" s="32" t="n"/>
       <c r="H124" s="32" t="n"/>
       <c r="I124" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (your 'paying in advance')</t>
         </is>
       </c>
       <c r="J124" s="32" t="n"/>
@@ -20917,24 +20913,24 @@
       </c>
       <c r="D125" s="32" t="inlineStr">
         <is>
-          <t>Prepaid balance</t>
+          <t>Cash vs accrual</t>
         </is>
       </c>
       <c r="E125" s="32" t="inlineStr">
         <is>
-          <t>Paid in advance, accrual on</t>
+          <t>Paid-in-advance or yearly record</t>
         </is>
       </c>
       <c r="F125" s="32" t="inlineStr">
         <is>
-          <t>Unused portion shows as a small 'prepaid' asset that runs down each month</t>
+          <t>Calendar always shows cash basis (the day money left). Budget has a Cash | Accrual toggle: accrual spreads the cost across the months it covers</t>
         </is>
       </c>
       <c r="G125" s="32" t="n"/>
       <c r="H125" s="32" t="n"/>
       <c r="I125" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (you want both views)</t>
         </is>
       </c>
       <c r="J125" s="32" t="n"/>
@@ -20962,20 +20958,24 @@
       </c>
       <c r="D126" s="32" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Budget default basis</t>
         </is>
       </c>
       <c r="E126" s="32" t="inlineStr">
         <is>
-          <t>Any number changes</t>
+          <t>Spending opened</t>
         </is>
       </c>
       <c r="F126" s="32" t="inlineStr">
         <is>
-          <t>Old value is kept with its date (not overwritten). Snapshots sit on top for session comparisons</t>
-        </is>
-      </c>
-      <c r="G126" s="32" t="n"/>
+          <t>Accrual (monthly equivalent), so a yearly bill doesn't wreck one month</t>
+        </is>
+      </c>
+      <c r="G126" s="32" t="inlineStr">
+        <is>
+          <t>Cash view shows the real month it hit</t>
+        </is>
+      </c>
       <c r="H126" s="32" t="n"/>
       <c r="I126" s="32" t="inlineStr">
         <is>
@@ -21007,24 +21007,24 @@
       </c>
       <c r="D127" s="32" t="inlineStr">
         <is>
-          <t>Year in review (Wrapped)</t>
+          <t>Prepaid balance</t>
         </is>
       </c>
       <c r="E127" s="32" t="inlineStr">
         <is>
-          <t>12 months of history exist</t>
+          <t>Paid in advance, accrual on</t>
         </is>
       </c>
       <c r="F127" s="32" t="inlineStr">
         <is>
-          <t>Wrapped-style recap: biggest wins, debt paid, savings rate trend, top categories, estimate accuracy</t>
+          <t>Unused portion shows as a small 'prepaid' asset that runs down each month</t>
         </is>
       </c>
       <c r="G127" s="32" t="n"/>
       <c r="H127" s="32" t="n"/>
       <c r="I127" s="32" t="inlineStr">
         <is>
-          <t>Decided (you want Wrapped)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J127" s="32" t="n"/>
@@ -21052,24 +21052,24 @@
       </c>
       <c r="D128" s="32" t="inlineStr">
         <is>
-          <t>Household</t>
+          <t>History</t>
         </is>
       </c>
       <c r="E128" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Any number changes</t>
         </is>
       </c>
       <c r="F128" s="32" t="inlineStr">
         <is>
-          <t>One client file = one household; couples are two people inside one file</t>
+          <t>Old value is kept with its date (not overwritten). Snapshots sit on top for session comparisons</t>
         </is>
       </c>
       <c r="G128" s="32" t="n"/>
       <c r="H128" s="32" t="n"/>
       <c r="I128" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 28)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J128" s="32" t="n"/>
@@ -21097,24 +21097,24 @@
       </c>
       <c r="D129" s="32" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Year in review (Wrapped)</t>
         </is>
       </c>
       <c r="E129" s="32" t="inlineStr">
         <is>
-          <t>Now</t>
+          <t>12 months of history exist</t>
         </is>
       </c>
       <c r="F129" s="32" t="inlineStr">
         <is>
-          <t>Laptop only. If clients get access later, their view is built phone-first</t>
+          <t>Wrapped-style recap: biggest wins, debt paid, savings rate trend, top categories, estimate accuracy</t>
         </is>
       </c>
       <c r="G129" s="32" t="n"/>
       <c r="H129" s="32" t="n"/>
       <c r="I129" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 28)</t>
+          <t>Decided (you want Wrapped)</t>
         </is>
       </c>
       <c r="J129" s="32" t="n"/>
@@ -21142,17 +21142,17 @@
       </c>
       <c r="D130" s="32" t="inlineStr">
         <is>
-          <t>Client logging</t>
+          <t>Household</t>
         </is>
       </c>
       <c r="E130" s="32" t="inlineStr">
         <is>
-          <t>Now</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F130" s="32" t="inlineStr">
         <is>
-          <t>Only you edit. Client logging between sessions is a later phase</t>
+          <t>One client file = one household; couples are two people inside one file</t>
         </is>
       </c>
       <c r="G130" s="32" t="n"/>
@@ -21187,17 +21187,17 @@
       </c>
       <c r="D131" s="32" t="inlineStr">
         <is>
-          <t>Budget passes</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="E131" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Now</t>
         </is>
       </c>
       <c r="F131" s="32" t="inlineStr">
         <is>
-          <t>Five passes in order: Gut, Basics, Rough, Estimate, Actual</t>
+          <t>Laptop only. If clients get access later, their view is built phone-first</t>
         </is>
       </c>
       <c r="G131" s="32" t="n"/>
@@ -21232,17 +21232,17 @@
       </c>
       <c r="D132" s="32" t="inlineStr">
         <is>
-          <t>Pass: Gut</t>
+          <t>Client logging</t>
         </is>
       </c>
       <c r="E132" s="32" t="inlineStr">
         <is>
-          <t>First minutes</t>
+          <t>Now</t>
         </is>
       </c>
       <c r="F132" s="32" t="inlineStr">
         <is>
-          <t>One number: 'what do you think you spend?' A test, kept to compare later</t>
+          <t>Only you edit. Client logging between sessions is a later phase</t>
         </is>
       </c>
       <c r="G132" s="32" t="n"/>
@@ -21277,24 +21277,24 @@
       </c>
       <c r="D133" s="32" t="inlineStr">
         <is>
-          <t>Pass: Basics</t>
+          <t>Budget passes</t>
         </is>
       </c>
       <c r="E133" s="32" t="inlineStr">
         <is>
-          <t>Fast Track</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F133" s="32" t="inlineStr">
         <is>
-          <t>Sum totals by area, not line items</t>
+          <t>Five passes in order: Gut, Basics, Rough, Estimate, Actual</t>
         </is>
       </c>
       <c r="G133" s="32" t="n"/>
       <c r="H133" s="32" t="n"/>
       <c r="I133" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 28: Fast Track = Basics)</t>
+          <t>Decided (Oct 28)</t>
         </is>
       </c>
       <c r="J133" s="32" t="n"/>
@@ -21322,17 +21322,17 @@
       </c>
       <c r="D134" s="32" t="inlineStr">
         <is>
-          <t>Pass: Rough</t>
+          <t>Pass: Gut</t>
         </is>
       </c>
       <c r="E134" s="32" t="inlineStr">
         <is>
-          <t>Going through line items in session</t>
+          <t>First minutes</t>
         </is>
       </c>
       <c r="F134" s="32" t="inlineStr">
         <is>
-          <t>Temporary placeholders for what it usually is; meant to be replaced</t>
+          <t>One number: 'what do you think you spend?' A test, kept to compare later</t>
         </is>
       </c>
       <c r="G134" s="32" t="n"/>
@@ -21367,24 +21367,24 @@
       </c>
       <c r="D135" s="32" t="inlineStr">
         <is>
-          <t>Pass: Estimate</t>
+          <t>Pass: Basics</t>
         </is>
       </c>
       <c r="E135" s="32" t="inlineStr">
         <is>
-          <t>Planning the coming month</t>
+          <t>Fast Track</t>
         </is>
       </c>
       <c r="F135" s="32" t="inlineStr">
         <is>
-          <t>What we expect this month, including the known amounts (rent, subscriptions); a plan, not a placeholder</t>
+          <t>Sum totals by area, not line items</t>
         </is>
       </c>
       <c r="G135" s="32" t="n"/>
       <c r="H135" s="32" t="n"/>
       <c r="I135" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 28)</t>
+          <t>Decided (Oct 28: Fast Track = Basics)</t>
         </is>
       </c>
       <c r="J135" s="32" t="n"/>
@@ -21412,17 +21412,17 @@
       </c>
       <c r="D136" s="32" t="inlineStr">
         <is>
-          <t>Pass: Actual</t>
+          <t>Pass: Rough</t>
         </is>
       </c>
       <c r="E136" s="32" t="inlineStr">
         <is>
-          <t>Month closes</t>
+          <t>Going through line items in session</t>
         </is>
       </c>
       <c r="F136" s="32" t="inlineStr">
         <is>
-          <t>Confirms or changes each estimate; differences show at month-end close</t>
+          <t>Temporary placeholders for what it usually is; meant to be replaced</t>
         </is>
       </c>
       <c r="G136" s="32" t="n"/>
@@ -21457,24 +21457,24 @@
       </c>
       <c r="D137" s="32" t="inlineStr">
         <is>
-          <t>Rough vs Estimate</t>
+          <t>Pass: Estimate</t>
         </is>
       </c>
       <c r="E137" s="32" t="inlineStr">
         <is>
-          <t>A line has a Rough number when a month is planned</t>
+          <t>Planning the coming month</t>
         </is>
       </c>
       <c r="F137" s="32" t="inlineStr">
         <is>
-          <t>Rough carries over as the starting Estimate and is marked 'from Rough' until you confirm it</t>
+          <t>What we expect this month, including the known amounts (rent, subscriptions); a plan, not a placeholder</t>
         </is>
       </c>
       <c r="G137" s="32" t="n"/>
       <c r="H137" s="32" t="n"/>
       <c r="I137" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (Oct 28)</t>
         </is>
       </c>
       <c r="J137" s="32" t="n"/>
@@ -21497,30 +21497,26 @@
       </c>
       <c r="C138" s="32" t="inlineStr">
         <is>
-          <t>Fixed vs variable</t>
+          <t>Data and timing</t>
         </is>
       </c>
       <c r="D138" s="32" t="inlineStr">
         <is>
-          <t>Every spending line</t>
+          <t>Pass: Actual</t>
         </is>
       </c>
       <c r="E138" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Month closes</t>
         </is>
       </c>
       <c r="F138" s="32" t="inlineStr">
         <is>
-          <t>Tagged Fixed or Variable (default by category, editable)</t>
+          <t>Confirms or changes each estimate; differences show at month-end close</t>
         </is>
       </c>
       <c r="G138" s="32" t="n"/>
-      <c r="H138" s="32" t="inlineStr">
-        <is>
-          <t>Rent, subscriptions, insurance = Fixed. Food, lattes, gas = Variable</t>
-        </is>
-      </c>
+      <c r="H138" s="32" t="n"/>
       <c r="I138" s="32" t="inlineStr">
         <is>
           <t>Decided (Oct 28)</t>
@@ -21529,7 +21525,7 @@
       <c r="J138" s="32" t="n"/>
       <c r="K138" s="33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1-6</t>
         </is>
       </c>
     </row>
@@ -21546,35 +21542,35 @@
       </c>
       <c r="C139" s="32" t="inlineStr">
         <is>
-          <t>Fixed vs variable</t>
+          <t>Data and timing</t>
         </is>
       </c>
       <c r="D139" s="32" t="inlineStr">
         <is>
-          <t>Two tags, not three</t>
+          <t>Rough vs Estimate</t>
         </is>
       </c>
       <c r="E139" s="32" t="inlineStr">
         <is>
-          <t>Every spending line</t>
+          <t>A line has a Rough number when a month is planned</t>
         </is>
       </c>
       <c r="F139" s="32" t="inlineStr">
         <is>
-          <t>Amount: Fixed | Variable. Timing: Fixed date | Variable date. Electric = variable amount, fixed date</t>
+          <t>Rough carries over as the starting Estimate and is marked 'from Rough' until you confirm it</t>
         </is>
       </c>
       <c r="G139" s="32" t="n"/>
       <c r="H139" s="32" t="n"/>
       <c r="I139" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 28: amount and timing are separate)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J139" s="32" t="n"/>
       <c r="K139" s="33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1-6</t>
         </is>
       </c>
     </row>
@@ -21596,21 +21592,25 @@
       </c>
       <c r="D140" s="32" t="inlineStr">
         <is>
-          <t>Four kinds</t>
+          <t>Every spending line</t>
         </is>
       </c>
       <c r="E140" s="32" t="inlineStr">
         <is>
-          <t>Both tags set</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F140" s="32" t="inlineStr">
         <is>
-          <t>Fixed amount + fixed date (rent, subscriptions). Variable amount + fixed date (electric, phone overages). Fixed amount + variable date (haircut, oil change). Variable amount + variable date (groceries, lattes, gas)</t>
+          <t>Tagged Fixed or Variable (default by category, editable)</t>
         </is>
       </c>
       <c r="G140" s="32" t="n"/>
-      <c r="H140" s="32" t="n"/>
+      <c r="H140" s="32" t="inlineStr">
+        <is>
+          <t>Rent, subscriptions, insurance = Fixed. Food, lattes, gas = Variable</t>
+        </is>
+      </c>
       <c r="I140" s="32" t="inlineStr">
         <is>
           <t>Decided (Oct 28)</t>
@@ -21641,28 +21641,24 @@
       </c>
       <c r="D141" s="32" t="inlineStr">
         <is>
-          <t>Calendar placement</t>
+          <t>Two tags, not three</t>
         </is>
       </c>
       <c r="E141" s="32" t="inlineStr">
         <is>
-          <t>Timing = Fixed date</t>
+          <t>Every spending line</t>
         </is>
       </c>
       <c r="F141" s="32" t="inlineStr">
         <is>
-          <t>Placed on its exact day</t>
-        </is>
-      </c>
-      <c r="G141" s="32" t="inlineStr">
-        <is>
-          <t>Variable date: spread evenly (weekly or per visit) so the running balance stays realistic</t>
-        </is>
-      </c>
+          <t>Amount: Fixed | Variable. Timing: Fixed date | Variable date. Electric = variable amount, fixed date</t>
+        </is>
+      </c>
+      <c r="G141" s="32" t="n"/>
       <c r="H141" s="32" t="n"/>
       <c r="I141" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (Oct 28: amount and timing are separate)</t>
         </is>
       </c>
       <c r="J141" s="32" t="n"/>
@@ -21690,28 +21686,24 @@
       </c>
       <c r="D142" s="32" t="inlineStr">
         <is>
-          <t>Estimate accuracy</t>
+          <t>Four kinds</t>
         </is>
       </c>
       <c r="E142" s="32" t="inlineStr">
         <is>
-          <t>Amount = Variable</t>
+          <t>Both tags set</t>
         </is>
       </c>
       <c r="F142" s="32" t="inlineStr">
         <is>
-          <t>Tracked for how far off it runs; most attention at month-end close</t>
-        </is>
-      </c>
-      <c r="G142" s="32" t="inlineStr">
-        <is>
-          <t>Fixed amount: a change is flagged as 'price went up'</t>
-        </is>
-      </c>
+          <t>Fixed amount + fixed date (rent, subscriptions). Variable amount + fixed date (electric, phone overages). Fixed amount + variable date (haircut, oil change). Variable amount + variable date (groceries, lattes, gas)</t>
+        </is>
+      </c>
+      <c r="G142" s="32" t="n"/>
       <c r="H142" s="32" t="n"/>
       <c r="I142" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (Oct 28)</t>
         </is>
       </c>
       <c r="J142" s="32" t="n"/>
@@ -21739,20 +21731,24 @@
       </c>
       <c r="D143" s="32" t="inlineStr">
         <is>
-          <t>Timing risk</t>
+          <t>Calendar placement</t>
         </is>
       </c>
       <c r="E143" s="32" t="inlineStr">
         <is>
-          <t>Timing = Variable date and amount is large</t>
+          <t>Timing = Fixed date</t>
         </is>
       </c>
       <c r="F143" s="32" t="inlineStr">
         <is>
-          <t>Flagged as a cash-flow risk on the calendar</t>
-        </is>
-      </c>
-      <c r="G143" s="32" t="n"/>
+          <t>Placed on its exact day</t>
+        </is>
+      </c>
+      <c r="G143" s="32" t="inlineStr">
+        <is>
+          <t>Variable date: spread evenly (weekly or per visit) so the running balance stays realistic</t>
+        </is>
+      </c>
       <c r="H143" s="32" t="n"/>
       <c r="I143" s="32" t="inlineStr">
         <is>
@@ -21784,24 +21780,28 @@
       </c>
       <c r="D144" s="32" t="inlineStr">
         <is>
-          <t>Fixed line suggestions</t>
+          <t>Estimate accuracy</t>
         </is>
       </c>
       <c r="E144" s="32" t="inlineStr">
         <is>
-          <t>Looking for savings</t>
+          <t>Amount = Variable</t>
         </is>
       </c>
       <c r="F144" s="32" t="inlineStr">
         <is>
-          <t>Offer: keep, cancel, renegotiate, or switch (easy to eliminate, hard to lower)</t>
-        </is>
-      </c>
-      <c r="G144" s="32" t="n"/>
+          <t>Tracked for how far off it runs; most attention at month-end close</t>
+        </is>
+      </c>
+      <c r="G144" s="32" t="inlineStr">
+        <is>
+          <t>Fixed amount: a change is flagged as 'price went up'</t>
+        </is>
+      </c>
       <c r="H144" s="32" t="n"/>
       <c r="I144" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 28 reasoning)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J144" s="32" t="n"/>
@@ -21829,24 +21829,24 @@
       </c>
       <c r="D145" s="32" t="inlineStr">
         <is>
-          <t>Variable line suggestions</t>
+          <t>Timing risk</t>
         </is>
       </c>
       <c r="E145" s="32" t="inlineStr">
         <is>
-          <t>Looking for savings</t>
+          <t>Timing = Variable date and amount is large</t>
         </is>
       </c>
       <c r="F145" s="32" t="inlineStr">
         <is>
-          <t>Offer: set a lower target or a cap (easy to lower, hard to eliminate)</t>
+          <t>Flagged as a cash-flow risk on the calendar</t>
         </is>
       </c>
       <c r="G145" s="32" t="n"/>
       <c r="H145" s="32" t="n"/>
       <c r="I145" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 28 reasoning)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J145" s="32" t="n"/>
@@ -21874,24 +21874,24 @@
       </c>
       <c r="D146" s="32" t="inlineStr">
         <is>
-          <t>Focus</t>
+          <t>Fixed line suggestions</t>
         </is>
       </c>
       <c r="E146" s="32" t="inlineStr">
         <is>
-          <t>Estimate vs actual at month end</t>
+          <t>Looking for savings</t>
         </is>
       </c>
       <c r="F146" s="32" t="inlineStr">
         <is>
-          <t>Variable lines get more attention: their misses are listed first and they're tracked for how far off they usually are</t>
+          <t>Offer: keep, cancel, renegotiate, or switch (easy to eliminate, hard to lower)</t>
         </is>
       </c>
       <c r="G146" s="32" t="n"/>
       <c r="H146" s="32" t="n"/>
       <c r="I146" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 28: variable is higher risk)</t>
+          <t>Decided (Oct 28 reasoning)</t>
         </is>
       </c>
       <c r="J146" s="32" t="n"/>
@@ -21919,24 +21919,24 @@
       </c>
       <c r="D147" s="32" t="inlineStr">
         <is>
-          <t>Totals</t>
+          <t>Variable line suggestions</t>
         </is>
       </c>
       <c r="E147" s="32" t="inlineStr">
         <is>
-          <t>Budget and Report</t>
+          <t>Looking for savings</t>
         </is>
       </c>
       <c r="F147" s="32" t="inlineStr">
         <is>
-          <t>Show fixed total and variable total side by side, with % of take-home each</t>
+          <t>Offer: set a lower target or a cap (easy to lower, hard to eliminate)</t>
         </is>
       </c>
       <c r="G147" s="32" t="n"/>
       <c r="H147" s="32" t="n"/>
       <c r="I147" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (Oct 28 reasoning)</t>
         </is>
       </c>
       <c r="J147" s="32" t="n"/>
@@ -21964,24 +21964,24 @@
       </c>
       <c r="D148" s="32" t="inlineStr">
         <is>
-          <t>Fixed cost floor</t>
+          <t>Focus</t>
         </is>
       </c>
       <c r="E148" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Estimate vs actual at month end</t>
         </is>
       </c>
       <c r="F148" s="32" t="inlineStr">
         <is>
-          <t>Fixed total = the monthly floor; feeds runway and Lean FI checks</t>
+          <t>Variable lines get more attention: their misses are listed first and they're tracked for how far off they usually are</t>
         </is>
       </c>
       <c r="G148" s="32" t="n"/>
       <c r="H148" s="32" t="n"/>
       <c r="I148" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (Oct 28: variable is higher risk)</t>
         </is>
       </c>
       <c r="J148" s="32" t="n"/>
@@ -22004,35 +22004,35 @@
       </c>
       <c r="C149" s="32" t="inlineStr">
         <is>
-          <t>Data and timing</t>
+          <t>Fixed vs variable</t>
         </is>
       </c>
       <c r="D149" s="32" t="inlineStr">
         <is>
-          <t>DRAFTT</t>
+          <t>Totals</t>
         </is>
       </c>
       <c r="E149" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Budget and Report</t>
         </is>
       </c>
       <c r="F149" s="32" t="inlineStr">
         <is>
-          <t>Budget lines are plain categories; each carries a DRAFTT tag (from its category, editable). DRAFTT is a view built from the tags, so graceful degradation and DRAFTT shares can be measured</t>
+          <t>Show fixed total and variable total side by side, with % of take-home each</t>
         </is>
       </c>
       <c r="G149" s="32" t="n"/>
       <c r="H149" s="32" t="n"/>
       <c r="I149" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 28)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J149" s="32" t="n"/>
       <c r="K149" s="33" t="inlineStr">
         <is>
-          <t>1-6</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -22049,12 +22049,12 @@
       </c>
       <c r="C150" s="32" t="inlineStr">
         <is>
-          <t>Data and timing</t>
+          <t>Fixed vs variable</t>
         </is>
       </c>
       <c r="D150" s="32" t="inlineStr">
         <is>
-          <t>Guess vs Roughly</t>
+          <t>Fixed cost floor</t>
         </is>
       </c>
       <c r="E150" s="32" t="inlineStr">
@@ -22064,20 +22064,20 @@
       </c>
       <c r="F150" s="32" t="inlineStr">
         <is>
-          <t>Kept separate: Roughly = client's ballpark, Guess = app's typical number</t>
+          <t>Fixed total = the monthly floor; feeds runway and Lean FI checks</t>
         </is>
       </c>
       <c r="G150" s="32" t="n"/>
       <c r="H150" s="32" t="n"/>
       <c r="I150" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 28)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J150" s="32" t="n"/>
       <c r="K150" s="33" t="inlineStr">
         <is>
-          <t>1-6</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="D151" s="32" t="inlineStr">
         <is>
-          <t>Tab names</t>
+          <t>DRAFTT</t>
         </is>
       </c>
       <c r="E151" s="32" t="inlineStr">
@@ -22109,14 +22109,14 @@
       </c>
       <c r="F151" s="32" t="inlineStr">
         <is>
-          <t>Home, My Money, Spending, Plan, Report</t>
+          <t>Budget lines are plain categories; each carries a DRAFTT tag (from its category, editable). DRAFTT is a view built from the tags, so graceful degradation and DRAFTT shares can be measured</t>
         </is>
       </c>
       <c r="G151" s="32" t="n"/>
       <c r="H151" s="32" t="n"/>
       <c r="I151" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 28: rename Numbers and Results)</t>
+          <t>Decided (Oct 28)</t>
         </is>
       </c>
       <c r="J151" s="32" t="n"/>
@@ -22144,24 +22144,24 @@
       </c>
       <c r="D152" s="32" t="inlineStr">
         <is>
-          <t>Backups</t>
+          <t>Guess vs Roughly</t>
         </is>
       </c>
       <c r="E152" s="32" t="inlineStr">
         <is>
-          <t>Last export older than 7 days, or End session</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F152" s="32" t="inlineStr">
         <is>
-          <t>Show 'Last backup 9 days ago' with 'Back up now'; End session downloads a backup file automatically</t>
+          <t>Kept separate: Roughly = client's ballpark, Guess = app's typical number</t>
         </is>
       </c>
       <c r="G152" s="32" t="n"/>
       <c r="H152" s="32" t="n"/>
       <c r="I152" s="32" t="inlineStr">
         <is>
-          <t>Decided (audit: browser storage can be wiped)</t>
+          <t>Decided (Oct 28)</t>
         </is>
       </c>
       <c r="J152" s="32" t="n"/>
@@ -22189,24 +22189,24 @@
       </c>
       <c r="D153" s="32" t="inlineStr">
         <is>
-          <t>Rule conflicts</t>
+          <t>Tab names</t>
         </is>
       </c>
       <c r="E153" s="32" t="inlineStr">
         <is>
-          <t>Two rules disagree</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F153" s="32" t="inlineStr">
         <is>
-          <t>The rule with the later date wins; log the conflict in QUESTIONS.md</t>
+          <t>Home, My Money, Spending, Plan, Report</t>
         </is>
       </c>
       <c r="G153" s="32" t="n"/>
       <c r="H153" s="32" t="n"/>
       <c r="I153" s="32" t="inlineStr">
         <is>
-          <t>Decided (audit)</t>
+          <t>Decided (Oct 28: rename Numbers and Results)</t>
         </is>
       </c>
       <c r="J153" s="32" t="n"/>
@@ -22234,24 +22234,24 @@
       </c>
       <c r="D154" s="32" t="inlineStr">
         <is>
-          <t>Old data</t>
+          <t>Backups</t>
         </is>
       </c>
       <c r="E154" s="32" t="inlineStr">
         <is>
-          <t>Moving from the old SLAM</t>
+          <t>Last export older than 7 days, or End session</t>
         </is>
       </c>
       <c r="F154" s="32" t="inlineStr">
         <is>
-          <t>No import from the old app. Your numbers come from the private Test client file</t>
+          <t>Show 'Last backup 9 days ago' with 'Back up now'; End session downloads a backup file automatically</t>
         </is>
       </c>
       <c r="G154" s="32" t="n"/>
       <c r="H154" s="32" t="n"/>
       <c r="I154" s="32" t="inlineStr">
         <is>
-          <t>Decided (audit: no baggage)</t>
+          <t>Decided (audit: browser storage can be wiped)</t>
         </is>
       </c>
       <c r="J154" s="32" t="n"/>
@@ -22274,39 +22274,35 @@
       </c>
       <c r="C155" s="32" t="inlineStr">
         <is>
-          <t>Time view</t>
+          <t>Data and timing</t>
         </is>
       </c>
       <c r="D155" s="32" t="inlineStr">
         <is>
-          <t>Every money number</t>
+          <t>Rule conflicts</t>
         </is>
       </c>
       <c r="E155" s="32" t="inlineStr">
         <is>
-          <t>Toggle set to Hours of work or FI days</t>
+          <t>Two rules disagree</t>
         </is>
       </c>
       <c r="F155" s="32" t="inlineStr">
         <is>
-          <t>Every amount converts: hours = amount / real hourly wage; FI days = amount / (annual spending / 365)</t>
-        </is>
-      </c>
-      <c r="G155" s="32" t="inlineStr">
-        <is>
-          <t>Missing hourly wage: toggle explains what's needed</t>
-        </is>
-      </c>
+          <t>The rule with the later date wins; log the conflict in QUESTIONS.md</t>
+        </is>
+      </c>
+      <c r="G155" s="32" t="n"/>
       <c r="H155" s="32" t="n"/>
       <c r="I155" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 28: everything converts to time)</t>
+          <t>Decided (audit)</t>
         </is>
       </c>
       <c r="J155" s="32" t="n"/>
       <c r="K155" s="33" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>1-6</t>
         </is>
       </c>
     </row>
@@ -22323,35 +22319,35 @@
       </c>
       <c r="C156" s="32" t="inlineStr">
         <is>
-          <t>Time view</t>
+          <t>Data and timing</t>
         </is>
       </c>
       <c r="D156" s="32" t="inlineStr">
         <is>
-          <t>No hours entered yet</t>
+          <t>Old data</t>
         </is>
       </c>
       <c r="E156" s="32" t="inlineStr">
         <is>
-          <t>Real hourly wage missing</t>
+          <t>Moving from the old SLAM</t>
         </is>
       </c>
       <c r="F156" s="32" t="inlineStr">
         <is>
-          <t>Use take-home / 173 hours (40 a week) labeled Guess, so the toggle works from day one; real hours replace it once entered</t>
+          <t>No import from the old app. Your numbers come from the private Test client file</t>
         </is>
       </c>
       <c r="G156" s="32" t="n"/>
       <c r="H156" s="32" t="n"/>
       <c r="I156" s="32" t="inlineStr">
         <is>
-          <t>Decided (audit: otherwise the toggle does nothing)</t>
+          <t>Decided (audit: no baggage)</t>
         </is>
       </c>
       <c r="J156" s="32" t="n"/>
       <c r="K156" s="33" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>1-6</t>
         </is>
       </c>
     </row>
@@ -22373,24 +22369,28 @@
       </c>
       <c r="D157" s="32" t="inlineStr">
         <is>
-          <t>Toggle</t>
+          <t>Every money number</t>
         </is>
       </c>
       <c r="E157" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Toggle set to Hours of work or FI days</t>
         </is>
       </c>
       <c r="F157" s="32" t="inlineStr">
         <is>
-          <t>One global toggle in the top bar: $ | Hours | FI days; remembered per client</t>
-        </is>
-      </c>
-      <c r="G157" s="32" t="n"/>
+          <t>Every amount converts: hours = amount / real hourly wage; FI days = amount / (annual spending / 365)</t>
+        </is>
+      </c>
+      <c r="G157" s="32" t="inlineStr">
+        <is>
+          <t>Missing hourly wage: toggle explains what's needed</t>
+        </is>
+      </c>
       <c r="H157" s="32" t="n"/>
       <c r="I157" s="32" t="inlineStr">
         <is>
-          <t>Decided</t>
+          <t>Decided (Oct 28: everything converts to time)</t>
         </is>
       </c>
       <c r="J157" s="32" t="n"/>
@@ -22418,24 +22418,24 @@
       </c>
       <c r="D158" s="32" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>No hours entered yet</t>
         </is>
       </c>
       <c r="E158" s="32" t="inlineStr">
         <is>
-          <t>Toggle on $</t>
+          <t>Real hourly wage missing</t>
         </is>
       </c>
       <c r="F158" s="32" t="inlineStr">
         <is>
-          <t>Big amounts (over $50) still show a small grey hours chip</t>
+          <t>Use take-home / 173 hours (40 a week) labeled Guess, so the toggle works from day one; real hours replace it once entered</t>
         </is>
       </c>
       <c r="G158" s="32" t="n"/>
       <c r="H158" s="32" t="n"/>
       <c r="I158" s="32" t="inlineStr">
         <is>
-          <t>Decided</t>
+          <t>Decided (audit: otherwise the toggle does nothing)</t>
         </is>
       </c>
       <c r="J158" s="32" t="n"/>
@@ -22458,12 +22458,12 @@
       </c>
       <c r="C159" s="32" t="inlineStr">
         <is>
-          <t>Polish (v4 preview)</t>
+          <t>Time view</t>
         </is>
       </c>
       <c r="D159" s="32" t="inlineStr">
         <is>
-          <t>Icons</t>
+          <t>Toggle</t>
         </is>
       </c>
       <c r="E159" s="32" t="inlineStr">
@@ -22473,20 +22473,20 @@
       </c>
       <c r="F159" s="32" t="inlineStr">
         <is>
-          <t>Matching line icons (Lucide style, 2.25 stroke, 18px) for duplicate, reset, delete, undo, redo, find, parking lot, client view, gear, add, close. Never emoji or text symbols</t>
+          <t>One global toggle in the top bar: $ | Hours | FI days; remembered per client</t>
         </is>
       </c>
       <c r="G159" s="32" t="n"/>
       <c r="H159" s="32" t="n"/>
       <c r="I159" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 28)</t>
+          <t>Decided</t>
         </is>
       </c>
       <c r="J159" s="32" t="n"/>
       <c r="K159" s="33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2-3</t>
         </is>
       </c>
     </row>
@@ -22503,35 +22503,35 @@
       </c>
       <c r="C160" s="32" t="inlineStr">
         <is>
-          <t>Polish (v4 preview)</t>
+          <t>Time view</t>
         </is>
       </c>
       <c r="D160" s="32" t="inlineStr">
         <is>
-          <t>Every list screen</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E160" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Toggle on $</t>
         </is>
       </c>
       <c r="F160" s="32" t="inlineStr">
         <is>
-          <t>Summary strip above the list: the 3 to 4 numbers that answer 'so what' (Debt: total, monthly payments, debt-free date, interest left)</t>
+          <t>Big amounts (over $50) still show a small grey hours chip</t>
         </is>
       </c>
       <c r="G160" s="32" t="n"/>
       <c r="H160" s="32" t="n"/>
       <c r="I160" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 28)</t>
+          <t>Decided</t>
         </is>
       </c>
       <c r="J160" s="32" t="n"/>
       <c r="K160" s="33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2-3</t>
         </is>
       </c>
     </row>
@@ -22553,7 +22553,7 @@
       </c>
       <c r="D161" s="32" t="inlineStr">
         <is>
-          <t>Numbers in tables</t>
+          <t>Icons</t>
         </is>
       </c>
       <c r="E161" s="32" t="inlineStr">
@@ -22563,7 +22563,7 @@
       </c>
       <c r="F161" s="32" t="inlineStr">
         <is>
-          <t>Money and percent right-aligned; text left-aligned</t>
+          <t>Matching line icons (Lucide style, 2.25 stroke, 18px) for duplicate, reset, delete, undo, redo, find, parking lot, client view, gear, add, close. Never emoji or text symbols</t>
         </is>
       </c>
       <c r="G161" s="32" t="n"/>
@@ -22598,24 +22598,20 @@
       </c>
       <c r="D162" s="32" t="inlineStr">
         <is>
-          <t>Debt rows</t>
+          <t>Every list screen</t>
         </is>
       </c>
       <c r="E162" s="32" t="inlineStr">
         <is>
-          <t>Payoff known</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F162" s="32" t="inlineStr">
         <is>
-          <t>Small bar under the payoff date in the area color; longest payoff = full width</t>
-        </is>
-      </c>
-      <c r="G162" s="32" t="inlineStr">
-        <is>
-          <t>Payoff unknown: empty bar and 'Needs APR'</t>
-        </is>
-      </c>
+          <t>Summary strip above the list: the 3 to 4 numbers that answer 'so what' (Debt: total, monthly payments, debt-free date, interest left)</t>
+        </is>
+      </c>
+      <c r="G162" s="32" t="n"/>
       <c r="H162" s="32" t="n"/>
       <c r="I162" s="32" t="inlineStr">
         <is>
@@ -22647,7 +22643,7 @@
       </c>
       <c r="D163" s="32" t="inlineStr">
         <is>
-          <t>Status tags</t>
+          <t>Numbers in tables</t>
         </is>
       </c>
       <c r="E163" s="32" t="inlineStr">
@@ -22657,7 +22653,7 @@
       </c>
       <c r="F163" s="32" t="inlineStr">
         <is>
-          <t>Each tag carries a symbol as well as a color: ≈ Roughly, ? Guess, ⚠ warning</t>
+          <t>Money and percent right-aligned; text left-aligned</t>
         </is>
       </c>
       <c r="G163" s="32" t="n"/>
@@ -22692,20 +22688,24 @@
       </c>
       <c r="D164" s="32" t="inlineStr">
         <is>
-          <t>Area color</t>
+          <t>Debt rows</t>
         </is>
       </c>
       <c r="E164" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Payoff known</t>
         </is>
       </c>
       <c r="F164" s="32" t="inlineStr">
         <is>
-          <t>Each area's color shows as a dot on its sub-tab, a 6px stripe on its section title, and in its charts</t>
-        </is>
-      </c>
-      <c r="G164" s="32" t="n"/>
+          <t>Small bar under the payoff date in the area color; longest payoff = full width</t>
+        </is>
+      </c>
+      <c r="G164" s="32" t="inlineStr">
+        <is>
+          <t>Payoff unknown: empty bar and 'Needs APR'</t>
+        </is>
+      </c>
       <c r="H164" s="32" t="n"/>
       <c r="I164" s="32" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
       </c>
       <c r="D165" s="32" t="inlineStr">
         <is>
-          <t>Sub-tab progress</t>
+          <t>Status tags</t>
         </is>
       </c>
       <c r="E165" s="32" t="inlineStr">
@@ -22747,7 +22747,7 @@
       </c>
       <c r="F165" s="32" t="inlineStr">
         <is>
-          <t>Each sub-tab shows a small count (3/4) or ✓ when core is done</t>
+          <t>Each tag carries a symbol as well as a color: ≈ Roughly, ? Guess, ⚠ warning</t>
         </is>
       </c>
       <c r="G165" s="32" t="n"/>
@@ -22782,28 +22782,24 @@
       </c>
       <c r="D166" s="32" t="inlineStr">
         <is>
-          <t>Input borders</t>
+          <t>Area color</t>
         </is>
       </c>
       <c r="E166" s="32" t="inlineStr">
         <is>
-          <t>Box has a value</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F166" s="32" t="inlineStr">
         <is>
-          <t>Softer border (#8FA2C6)</t>
-        </is>
-      </c>
-      <c r="G166" s="32" t="inlineStr">
-        <is>
-          <t>Empty: strong 2px border with a hint like 'Add APR'</t>
-        </is>
-      </c>
+          <t>Each area's color shows as a dot on its sub-tab, a 6px stripe on its section title, and in its charts</t>
+        </is>
+      </c>
+      <c r="G166" s="32" t="n"/>
       <c r="H166" s="32" t="n"/>
       <c r="I166" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 28: you said add them all)</t>
+          <t>Decided (Oct 28)</t>
         </is>
       </c>
       <c r="J166" s="32" t="n"/>
@@ -22831,17 +22827,17 @@
       </c>
       <c r="D167" s="32" t="inlineStr">
         <is>
-          <t>Saved moment</t>
+          <t>Sub-tab progress</t>
         </is>
       </c>
       <c r="E167" s="32" t="inlineStr">
         <is>
-          <t>A value changes</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F167" s="32" t="inlineStr">
         <is>
-          <t>Row flashes soft green for under a second and '✓ Saved' shows near the main button</t>
+          <t>Each sub-tab shows a small count (3/4) or ✓ when core is done</t>
         </is>
       </c>
       <c r="G167" s="32" t="n"/>
@@ -22876,24 +22872,28 @@
       </c>
       <c r="D168" s="32" t="inlineStr">
         <is>
-          <t>Sticky</t>
+          <t>Input borders</t>
         </is>
       </c>
       <c r="E168" s="32" t="inlineStr">
         <is>
-          <t>Scrolling</t>
+          <t>Box has a value</t>
         </is>
       </c>
       <c r="F168" s="32" t="inlineStr">
         <is>
-          <t>Top bar stays at the top of the page; column names and the totals row stay inside long lists</t>
-        </is>
-      </c>
-      <c r="G168" s="32" t="n"/>
+          <t>Softer border (#8FA2C6)</t>
+        </is>
+      </c>
+      <c r="G168" s="32" t="inlineStr">
+        <is>
+          <t>Empty: strong 2px border with a hint like 'Add APR'</t>
+        </is>
+      </c>
       <c r="H168" s="32" t="n"/>
       <c r="I168" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 28)</t>
+          <t>Decided (Oct 28: you said add them all)</t>
         </is>
       </c>
       <c r="J168" s="32" t="n"/>
@@ -22921,17 +22921,17 @@
       </c>
       <c r="D169" s="32" t="inlineStr">
         <is>
-          <t>Show the math</t>
+          <t>Saved moment</t>
         </is>
       </c>
       <c r="E169" s="32" t="inlineStr">
         <is>
-          <t>Click any computed number</t>
+          <t>A value changes</t>
         </is>
       </c>
       <c r="F169" s="32" t="inlineStr">
         <is>
-          <t>Small panel with the formula filled in with the client's numbers, in plain words</t>
+          <t>Row flashes soft green for under a second and '✓ Saved' shows near the main button</t>
         </is>
       </c>
       <c r="G169" s="32" t="n"/>
@@ -22966,24 +22966,20 @@
       </c>
       <c r="D170" s="32" t="inlineStr">
         <is>
-          <t>Change since last session</t>
+          <t>Sticky</t>
         </is>
       </c>
       <c r="E170" s="32" t="inlineStr">
         <is>
-          <t>A snapshot exists</t>
+          <t>Scrolling</t>
         </is>
       </c>
       <c r="F170" s="32" t="inlineStr">
         <is>
-          <t>▲ or ▼ with the difference under key numbers (summary strips, net worth, savings rate)</t>
-        </is>
-      </c>
-      <c r="G170" s="32" t="inlineStr">
-        <is>
-          <t>No snapshot: nothing shown</t>
-        </is>
-      </c>
+          <t>Top bar stays at the top of the page; column names and the totals row stay inside long lists</t>
+        </is>
+      </c>
+      <c r="G170" s="32" t="n"/>
       <c r="H170" s="32" t="n"/>
       <c r="I170" s="32" t="inlineStr">
         <is>
@@ -23015,17 +23011,17 @@
       </c>
       <c r="D171" s="32" t="inlineStr">
         <is>
-          <t>Keyboard</t>
+          <t>Show the math</t>
         </is>
       </c>
       <c r="E171" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Click any computed number</t>
         </is>
       </c>
       <c r="F171" s="32" t="inlineStr">
         <is>
-          <t>Tab = next box, Enter in a row = new row below, Ctrl+Z = undo, Ctrl+Shift+Z = redo, / = Find. Shown as a small hint line under each list</t>
+          <t>Small panel with the formula filled in with the client's numbers, in plain words</t>
         </is>
       </c>
       <c r="G171" s="32" t="n"/>
@@ -23060,20 +23056,24 @@
       </c>
       <c r="D172" s="32" t="inlineStr">
         <is>
-          <t>Density</t>
+          <t>Change since last session</t>
         </is>
       </c>
       <c r="E172" s="32" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>A snapshot exists</t>
         </is>
       </c>
       <c r="F172" s="32" t="inlineStr">
         <is>
-          <t>Compact (36px rows) or Comfortable (44px, default); remembered</t>
-        </is>
-      </c>
-      <c r="G172" s="32" t="n"/>
+          <t>▲ or ▼ with the difference under key numbers (summary strips, net worth, savings rate)</t>
+        </is>
+      </c>
+      <c r="G172" s="32" t="inlineStr">
+        <is>
+          <t>No snapshot: nothing shown</t>
+        </is>
+      </c>
       <c r="H172" s="32" t="n"/>
       <c r="I172" s="32" t="inlineStr">
         <is>
@@ -23105,17 +23105,17 @@
       </c>
       <c r="D173" s="32" t="inlineStr">
         <is>
-          <t>Client view</t>
+          <t>Keyboard</t>
         </is>
       </c>
       <c r="E173" s="32" t="inlineStr">
         <is>
-          <t>On</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F173" s="32" t="inlineStr">
         <is>
-          <t>Text 15% bigger, plus the hiding rules already in Visibility</t>
+          <t>Tab = next box, Enter in a row = new row below, Ctrl+Z = undo, Ctrl+Shift+Z = redo, / = Find. Shown as a small hint line under each list</t>
         </is>
       </c>
       <c r="G173" s="32" t="n"/>
@@ -23150,17 +23150,17 @@
       </c>
       <c r="D174" s="32" t="inlineStr">
         <is>
-          <t>Long lists</t>
+          <t>Density</t>
         </is>
       </c>
       <c r="E174" s="32" t="inlineStr">
         <is>
-          <t>More than one type in a list</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="F174" s="32" t="inlineStr">
         <is>
-          <t>Group headers (Credit cards, Loans, Other) with subtotals; click to fold</t>
+          <t>Compact (36px rows) or Comfortable (44px, default); remembered</t>
         </is>
       </c>
       <c r="G174" s="32" t="n"/>
@@ -23195,17 +23195,17 @@
       </c>
       <c r="D175" s="32" t="inlineStr">
         <is>
-          <t>Totals row</t>
+          <t>Client view</t>
         </is>
       </c>
       <c r="E175" s="32" t="inlineStr">
         <is>
-          <t>Every list</t>
+          <t>On</t>
         </is>
       </c>
       <c r="F175" s="32" t="inlineStr">
         <is>
-          <t>Pinned at the bottom: count, total balance, total monthly</t>
+          <t>Text 15% bigger, plus the hiding rules already in Visibility</t>
         </is>
       </c>
       <c r="G175" s="32" t="n"/>
@@ -23240,17 +23240,17 @@
       </c>
       <c r="D176" s="32" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Long lists</t>
         </is>
       </c>
       <c r="E176" s="32" t="inlineStr">
         <is>
-          <t>One-pager or any screen printed or saved as PDF</t>
+          <t>More than one type in a list</t>
         </is>
       </c>
       <c r="F176" s="32" t="inlineStr">
         <is>
-          <t>No buttons, no dark backgrounds, solid lines, black text</t>
+          <t>Group headers (Credit cards, Loans, Other) with subtotals; click to fold</t>
         </is>
       </c>
       <c r="G176" s="32" t="n"/>
@@ -23285,17 +23285,17 @@
       </c>
       <c r="D177" s="32" t="inlineStr">
         <is>
-          <t>Reference look</t>
+          <t>Totals row</t>
         </is>
       </c>
       <c r="E177" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Every list</t>
         </is>
       </c>
       <c r="F177" s="32" t="inlineStr">
         <is>
-          <t>spec/SLAM Look Preview.html is the visual reference; match it</t>
+          <t>Pinned at the bottom: count, total balance, total monthly</t>
         </is>
       </c>
       <c r="G177" s="32" t="n"/>
@@ -23325,35 +23325,35 @@
       </c>
       <c r="C178" s="32" t="inlineStr">
         <is>
-          <t>Couples</t>
+          <t>Polish (v4 preview)</t>
         </is>
       </c>
       <c r="D178" s="32" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="E178" s="32" t="inlineStr">
         <is>
-          <t>Couple</t>
+          <t>One-pager or any screen printed or saved as PDF</t>
         </is>
       </c>
       <c r="F178" s="32" t="inlineStr">
         <is>
-          <t>Every row has Owner: me, partner, joint; joint counts for both</t>
+          <t>No buttons, no dark backgrounds, solid lines, black text</t>
         </is>
       </c>
       <c r="G178" s="32" t="n"/>
       <c r="H178" s="32" t="n"/>
       <c r="I178" s="32" t="inlineStr">
         <is>
-          <t>Decided</t>
+          <t>Decided (Oct 28)</t>
         </is>
       </c>
       <c r="J178" s="32" t="n"/>
       <c r="K178" s="33" t="inlineStr">
         <is>
-          <t>1-5</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -23370,35 +23370,35 @@
       </c>
       <c r="C179" s="32" t="inlineStr">
         <is>
-          <t>Couples</t>
+          <t>Polish (v4 preview)</t>
         </is>
       </c>
       <c r="D179" s="32" t="inlineStr">
         <is>
-          <t>Totals</t>
+          <t>Reference look</t>
         </is>
       </c>
       <c r="E179" s="32" t="inlineStr">
         <is>
-          <t>Couple</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F179" s="32" t="inlineStr">
         <is>
-          <t>Household totals by default; 'Me | Partner | Household' toggle on totals</t>
+          <t>spec/SLAM Look Preview.html is the visual reference; match it</t>
         </is>
       </c>
       <c r="G179" s="32" t="n"/>
       <c r="H179" s="32" t="n"/>
       <c r="I179" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided (Oct 28)</t>
         </is>
       </c>
       <c r="J179" s="32" t="n"/>
       <c r="K179" s="33" t="inlineStr">
         <is>
-          <t>1-5</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -23420,24 +23420,24 @@
       </c>
       <c r="D180" s="32" t="inlineStr">
         <is>
-          <t>Split</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="E180" s="32" t="inlineStr">
         <is>
-          <t>Joint | Separate | Mix</t>
+          <t>Couple</t>
         </is>
       </c>
       <c r="F180" s="32" t="inlineStr">
         <is>
-          <t>Separate: each person's Needs share comes from the split table</t>
+          <t>Every row has Owner: me, partner, joint; joint counts for both</t>
         </is>
       </c>
       <c r="G180" s="32" t="n"/>
       <c r="H180" s="32" t="n"/>
       <c r="I180" s="32" t="inlineStr">
         <is>
-          <t>Decided (accepted Oct 28; was proposed)</t>
+          <t>Decided</t>
         </is>
       </c>
       <c r="J180" s="32" t="n"/>
@@ -23460,35 +23460,35 @@
       </c>
       <c r="C181" s="32" t="inlineStr">
         <is>
-          <t>Session flow</t>
+          <t>Couples</t>
         </is>
       </c>
       <c r="D181" s="32" t="inlineStr">
         <is>
-          <t>Discovery table</t>
+          <t>Totals</t>
         </is>
       </c>
       <c r="E181" s="32" t="inlineStr">
         <is>
-          <t>Send to client file</t>
+          <t>Couple</t>
         </is>
       </c>
       <c r="F181" s="32" t="inlineStr">
         <is>
-          <t>Creates the client; each number fills its field with status Roughly</t>
+          <t>Household totals by default; 'Me | Partner | Household' toggle on totals</t>
         </is>
       </c>
       <c r="G181" s="32" t="n"/>
       <c r="H181" s="32" t="n"/>
       <c r="I181" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 7)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J181" s="32" t="n"/>
       <c r="K181" s="33" t="inlineStr">
         <is>
-          <t>9-10</t>
+          <t>1-5</t>
         </is>
       </c>
     </row>
@@ -23505,22 +23505,22 @@
       </c>
       <c r="C182" s="32" t="inlineStr">
         <is>
-          <t>Session flow</t>
+          <t>Couples</t>
         </is>
       </c>
       <c r="D182" s="32" t="inlineStr">
         <is>
-          <t>Session end</t>
+          <t>Split</t>
         </is>
       </c>
       <c r="E182" s="32" t="inlineStr">
         <is>
-          <t>End session clicked</t>
+          <t>Joint | Separate | Mix</t>
         </is>
       </c>
       <c r="F182" s="32" t="inlineStr">
         <is>
-          <t>Snapshot saved, one-pager filled, homework list built from Will email</t>
+          <t>Separate: each person's Needs share comes from the split table</t>
         </is>
       </c>
       <c r="G182" s="32" t="n"/>
@@ -23533,7 +23533,7 @@
       <c r="J182" s="32" t="n"/>
       <c r="K182" s="33" t="inlineStr">
         <is>
-          <t>9-10</t>
+          <t>1-5</t>
         </is>
       </c>
     </row>
@@ -23555,24 +23555,24 @@
       </c>
       <c r="D183" s="32" t="inlineStr">
         <is>
-          <t>One-pager</t>
+          <t>Discovery table</t>
         </is>
       </c>
       <c r="E183" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Send to client file</t>
         </is>
       </c>
       <c r="F183" s="32" t="inlineStr">
         <is>
-          <t>Includes the disclaimer line</t>
+          <t>Creates the client; each number fills its field with status Roughly</t>
         </is>
       </c>
       <c r="G183" s="32" t="n"/>
       <c r="H183" s="32" t="n"/>
       <c r="I183" s="32" t="inlineStr">
         <is>
-          <t>Decided (session gaps)</t>
+          <t>Decided (Oct 7)</t>
         </is>
       </c>
       <c r="J183" s="32" t="n"/>
@@ -23600,24 +23600,24 @@
       </c>
       <c r="D184" s="32" t="inlineStr">
         <is>
-          <t>Prep view</t>
+          <t>Session end</t>
         </is>
       </c>
       <c r="E184" s="32" t="inlineStr">
         <is>
-          <t>Next session opened</t>
+          <t>End session clicked</t>
         </is>
       </c>
       <c r="F184" s="32" t="inlineStr">
         <is>
-          <t>Shows changes since last snapshot, open homework, numbers due for a check</t>
+          <t>Snapshot saved, one-pager filled, homework list built from Will email</t>
         </is>
       </c>
       <c r="G184" s="32" t="n"/>
       <c r="H184" s="32" t="n"/>
       <c r="I184" s="32" t="inlineStr">
         <is>
-          <t>Decided (session gaps)</t>
+          <t>Decided (accepted Oct 28; was proposed)</t>
         </is>
       </c>
       <c r="J184" s="32" t="n"/>
@@ -23640,12 +23640,12 @@
       </c>
       <c r="C185" s="32" t="inlineStr">
         <is>
-          <t>Copy and look</t>
+          <t>Session flow</t>
         </is>
       </c>
       <c r="D185" s="32" t="inlineStr">
         <is>
-          <t>All on-screen text</t>
+          <t>One-pager</t>
         </is>
       </c>
       <c r="E185" s="32" t="inlineStr">
@@ -23655,20 +23655,20 @@
       </c>
       <c r="F185" s="32" t="inlineStr">
         <is>
-          <t>Written from the user's side: what it means and what to do, never how the app works</t>
+          <t>Includes the disclaimer line</t>
         </is>
       </c>
       <c r="G185" s="32" t="n"/>
       <c r="H185" s="32" t="n"/>
       <c r="I185" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct 25)</t>
+          <t>Decided (session gaps)</t>
         </is>
       </c>
       <c r="J185" s="32" t="n"/>
       <c r="K185" s="33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9-10</t>
         </is>
       </c>
     </row>
@@ -23685,35 +23685,35 @@
       </c>
       <c r="C186" s="32" t="inlineStr">
         <is>
-          <t>Copy and look</t>
+          <t>Session flow</t>
         </is>
       </c>
       <c r="D186" s="32" t="inlineStr">
         <is>
-          <t>Clickable things</t>
+          <t>Prep view</t>
         </is>
       </c>
       <c r="E186" s="32" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Next session opened</t>
         </is>
       </c>
       <c r="F186" s="32" t="inlineStr">
         <is>
-          <t>Buttons look like buttons, inputs have visible borders, small lift on hover</t>
+          <t>Shows changes since last snapshot, open homework, numbers due for a check</t>
         </is>
       </c>
       <c r="G186" s="32" t="n"/>
       <c r="H186" s="32" t="n"/>
       <c r="I186" s="32" t="inlineStr">
         <is>
-          <t>Decided (Oct)</t>
+          <t>Decided (session gaps)</t>
         </is>
       </c>
       <c r="J186" s="32" t="n"/>
       <c r="K186" s="33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9-10</t>
         </is>
       </c>
     </row>
@@ -23735,7 +23735,7 @@
       </c>
       <c r="D187" s="32" t="inlineStr">
         <is>
-          <t>Row actions</t>
+          <t>All on-screen text</t>
         </is>
       </c>
       <c r="E187" s="32" t="inlineStr">
@@ -23745,14 +23745,14 @@
       </c>
       <c r="F187" s="32" t="inlineStr">
         <is>
-          <t>Small icons: ⧉ duplicate, ↺ reset, 🗑 delete, with tooltips, then one 'More ▸' text button. No ⋯ menu</t>
+          <t>Written from the user's side: what it means and what to do, never how the app works</t>
         </is>
       </c>
       <c r="G187" s="32" t="n"/>
       <c r="H187" s="32" t="n"/>
       <c r="I187" s="32" t="inlineStr">
         <is>
-          <t>Decided (your comments)</t>
+          <t>Decided (Oct 25)</t>
         </is>
       </c>
       <c r="J187" s="32" t="n"/>
@@ -23780,24 +23780,24 @@
       </c>
       <c r="D188" s="32" t="inlineStr">
         <is>
-          <t>Durations</t>
+          <t>Clickable things</t>
         </is>
       </c>
       <c r="E188" s="32" t="inlineStr">
         <is>
-          <t>Any payoff or time-to-goal</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F188" s="32" t="inlineStr">
         <is>
-          <t>Shown in months and a date, never rounded to years</t>
+          <t>Buttons look like buttons, inputs have visible borders, small lift on hover</t>
         </is>
       </c>
       <c r="G188" s="32" t="n"/>
       <c r="H188" s="32" t="n"/>
       <c r="I188" s="32" t="inlineStr">
         <is>
-          <t>Decided (screen review)</t>
+          <t>Decided (Oct)</t>
         </is>
       </c>
       <c r="J188" s="32" t="n"/>
@@ -23807,14 +23807,104 @@
         </is>
       </c>
     </row>
+    <row r="189">
+      <c r="A189" s="32" t="inlineStr">
+        <is>
+          <t>R186</t>
+        </is>
+      </c>
+      <c r="B189" s="32" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="C189" s="32" t="inlineStr">
+        <is>
+          <t>Copy and look</t>
+        </is>
+      </c>
+      <c r="D189" s="32" t="inlineStr">
+        <is>
+          <t>Row actions</t>
+        </is>
+      </c>
+      <c r="E189" s="32" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="F189" s="32" t="inlineStr">
+        <is>
+          <t>Small icons: ⧉ duplicate, ↺ reset, 🗑 delete, with tooltips, then one 'More ▸' text button. No ⋯ menu</t>
+        </is>
+      </c>
+      <c r="G189" s="32" t="n"/>
+      <c r="H189" s="32" t="n"/>
+      <c r="I189" s="32" t="inlineStr">
+        <is>
+          <t>Decided (your comments)</t>
+        </is>
+      </c>
+      <c r="J189" s="32" t="n"/>
+      <c r="K189" s="33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="32" t="inlineStr">
+        <is>
+          <t>R187</t>
+        </is>
+      </c>
+      <c r="B190" s="32" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="C190" s="32" t="inlineStr">
+        <is>
+          <t>Copy and look</t>
+        </is>
+      </c>
+      <c r="D190" s="32" t="inlineStr">
+        <is>
+          <t>Durations</t>
+        </is>
+      </c>
+      <c r="E190" s="32" t="inlineStr">
+        <is>
+          <t>Any payoff or time-to-goal</t>
+        </is>
+      </c>
+      <c r="F190" s="32" t="inlineStr">
+        <is>
+          <t>Shown in months and a date, never rounded to years</t>
+        </is>
+      </c>
+      <c r="G190" s="32" t="n"/>
+      <c r="H190" s="32" t="n"/>
+      <c r="I190" s="32" t="inlineStr">
+        <is>
+          <t>Decided (screen review)</t>
+        </is>
+      </c>
+      <c r="J190" s="32" t="n"/>
+      <c r="K190" s="33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K188"/>
+  <autoFilter ref="A3:K190"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B4:B188" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B4:B190" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not started,Spec'd,Built,Tested"</formula1>
     </dataValidation>
   </dataValidations>
@@ -24963,7 +25053,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>n (unrounded) × P − B, or a month-by-month simulation</t>
+          <t>n (unrounded) × P − B</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -24974,7 +25064,7 @@
       <c r="E32" s="4" t="inlineStr"/>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Simulation is the source of truth</t>
+          <t>This formula is the source of truth for one debt. The month-by-month simulation (M34) is only for payoff order with extra payments; it may differ by a few dollars from rounding</t>
         </is>
       </c>
     </row>
@@ -25379,7 +25469,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Coast number at age a = FI number / (1 + real return)^(retire age − a); reached when invested ≥ it</t>
+          <t>Coast number at age a = FI number / (1 + real return)^(retire age − a); reached when invested ≥ it. Retire age = FI target age, else 60</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -26335,7 +26425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V265"/>
+  <dimension ref="A1:V267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -46429,12 +46519,12 @@
       </c>
       <c r="E217" s="32" t="inlineStr">
         <is>
-          <t>Assumptions</t>
+          <t>FI target</t>
         </is>
       </c>
       <c r="F217" s="32" t="inlineStr">
         <is>
-          <t>Return (real)</t>
+          <t>Retire by (age)</t>
         </is>
       </c>
       <c r="G217" s="32" t="inlineStr">
@@ -46444,18 +46534,18 @@
       </c>
       <c r="H217" s="32" t="inlineStr">
         <is>
-          <t>Percent, default 8%</t>
+          <t>Age box, default 60</t>
         </is>
       </c>
       <c r="I217" s="32" t="inlineStr">
         <is>
-          <t>Projection engine</t>
+          <t>Coast FI and the timeline when no FI age is set</t>
         </is>
       </c>
       <c r="J217" s="32" t="n"/>
       <c r="K217" s="32" t="inlineStr">
         <is>
-          <t>Coach guesstimate</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="L217" s="32" t="n"/>
@@ -46466,7 +46556,7 @@
       </c>
       <c r="N217" s="32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O217" s="32" t="n"/>
@@ -46477,7 +46567,7 @@
       </c>
       <c r="Q217" s="32" t="inlineStr">
         <is>
-          <t>Oct 28 default</t>
+          <t>Added from Claude Code's question</t>
         </is>
       </c>
       <c r="S217" s="10" t="inlineStr">
@@ -46487,7 +46577,7 @@
       </c>
       <c r="T217" s="10" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>text</t>
         </is>
       </c>
       <c r="U217" s="10" t="inlineStr"/>
@@ -46525,7 +46615,7 @@
       </c>
       <c r="F218" s="32" t="inlineStr">
         <is>
-          <t>Withdrawal rate</t>
+          <t>Return (after inflation)</t>
         </is>
       </c>
       <c r="G218" s="32" t="inlineStr">
@@ -46535,12 +46625,12 @@
       </c>
       <c r="H218" s="32" t="inlineStr">
         <is>
-          <t>Pick: 3%, 4% (default), 4.7%, 5.2%</t>
+          <t>Pick: 6%, 7% (default), 8%, 12% hopeful</t>
         </is>
       </c>
       <c r="I218" s="32" t="inlineStr">
         <is>
-          <t>FI number</t>
+          <t>Projection engine</t>
         </is>
       </c>
       <c r="J218" s="32" t="n"/>
@@ -46566,7 +46656,11 @@
           <t>Now</t>
         </is>
       </c>
-      <c r="Q218" s="32" t="n"/>
+      <c r="Q218" s="32" t="inlineStr">
+        <is>
+          <t>Oct 28 answers</t>
+        </is>
+      </c>
       <c r="S218" s="10" t="inlineStr">
         <is>
           <t>Plan › Goals</t>
@@ -46579,7 +46673,7 @@
       </c>
       <c r="U218" s="10" t="inlineStr">
         <is>
-          <t>3%, 4% (default), 4.7%, 5.2%</t>
+          <t>6%, 7% (default), 8%, 12% hopeful</t>
         </is>
       </c>
       <c r="V218" s="33" t="inlineStr">
@@ -46616,7 +46710,7 @@
       </c>
       <c r="F219" s="32" t="inlineStr">
         <is>
-          <t>Pace (optimistic, likely, pessimistic)</t>
+          <t>Inflation</t>
         </is>
       </c>
       <c r="G219" s="32" t="inlineStr">
@@ -46626,12 +46720,12 @@
       </c>
       <c r="H219" s="32" t="inlineStr">
         <is>
-          <t>Three-way toggle</t>
+          <t>Pick: 2% (default), 3%</t>
         </is>
       </c>
       <c r="I219" s="32" t="inlineStr">
         <is>
-          <t>Triple D plan</t>
+          <t>Nominal display, Social Security, debt in today's dollars</t>
         </is>
       </c>
       <c r="J219" s="32" t="n"/>
@@ -46648,7 +46742,7 @@
       </c>
       <c r="N219" s="32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O219" s="32" t="n"/>
@@ -46659,7 +46753,7 @@
       </c>
       <c r="Q219" s="32" t="inlineStr">
         <is>
-          <t>Default Likely</t>
+          <t>Returns are already after inflation</t>
         </is>
       </c>
       <c r="S219" s="10" t="inlineStr">
@@ -46672,7 +46766,11 @@
           <t>choice</t>
         </is>
       </c>
-      <c r="U219" s="10" t="inlineStr"/>
+      <c r="U219" s="10" t="inlineStr">
+        <is>
+          <t>2% (default), 3%</t>
+        </is>
+      </c>
       <c r="V219" s="33" t="inlineStr">
         <is>
           <t>7</t>
@@ -46692,7 +46790,7 @@
       </c>
       <c r="C220" s="32" t="inlineStr">
         <is>
-          <t>Session 2+</t>
+          <t>Session 1</t>
         </is>
       </c>
       <c r="D220" s="32" t="inlineStr">
@@ -46707,22 +46805,22 @@
       </c>
       <c r="F220" s="32" t="inlineStr">
         <is>
-          <t>Real or nominal dollars</t>
+          <t>Withdrawal rate</t>
         </is>
       </c>
       <c r="G220" s="32" t="inlineStr">
         <is>
-          <t>Tertiary</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="H220" s="32" t="inlineStr">
         <is>
-          <t>Toggle with plain definition</t>
+          <t>Pick: 3%, 4% (default), 4.7%, 5.2%</t>
         </is>
       </c>
       <c r="I220" s="32" t="inlineStr">
         <is>
-          <t>Engine default real</t>
+          <t>FI number</t>
         </is>
       </c>
       <c r="J220" s="32" t="n"/>
@@ -46739,7 +46837,7 @@
       </c>
       <c r="N220" s="32" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O220" s="32" t="n"/>
@@ -46759,7 +46857,11 @@
           <t>choice</t>
         </is>
       </c>
-      <c r="U220" s="10" t="inlineStr"/>
+      <c r="U220" s="10" t="inlineStr">
+        <is>
+          <t>3%, 4% (default), 4.7%, 5.2%</t>
+        </is>
+      </c>
       <c r="V220" s="33" t="inlineStr">
         <is>
           <t>7</t>
@@ -46779,7 +46881,7 @@
       </c>
       <c r="C221" s="32" t="inlineStr">
         <is>
-          <t>Session 2+</t>
+          <t>Session 1</t>
         </is>
       </c>
       <c r="D221" s="32" t="inlineStr">
@@ -46794,22 +46896,22 @@
       </c>
       <c r="F221" s="32" t="inlineStr">
         <is>
-          <t>Life expectancy</t>
+          <t>Pace (optimistic, likely, pessimistic)</t>
         </is>
       </c>
       <c r="G221" s="32" t="inlineStr">
         <is>
-          <t>Tertiary</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="H221" s="32" t="inlineStr">
         <is>
-          <t>Age, default 90</t>
+          <t>Three-way toggle</t>
         </is>
       </c>
       <c r="I221" s="32" t="inlineStr">
         <is>
-          <t>Decumulation length</t>
+          <t>Triple D plan: 8%, 7%, 6%</t>
         </is>
       </c>
       <c r="J221" s="32" t="n"/>
@@ -46837,7 +46939,7 @@
       </c>
       <c r="Q221" s="32" t="inlineStr">
         <is>
-          <t>ProjectionLab default 85</t>
+          <t>Default Likely</t>
         </is>
       </c>
       <c r="S221" s="10" t="inlineStr">
@@ -46847,7 +46949,7 @@
       </c>
       <c r="T221" s="10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>choice</t>
         </is>
       </c>
       <c r="U221" s="10" t="inlineStr"/>
@@ -46885,7 +46987,7 @@
       </c>
       <c r="F222" s="32" t="inlineStr">
         <is>
-          <t>Social Security</t>
+          <t>Real or nominal dollars</t>
         </is>
       </c>
       <c r="G222" s="32" t="inlineStr">
@@ -46895,12 +46997,12 @@
       </c>
       <c r="H222" s="32" t="inlineStr">
         <is>
-          <t>Pick: full scheduled (likely), reduced %, none</t>
+          <t>Toggle with plain definition</t>
         </is>
       </c>
       <c r="I222" s="32" t="inlineStr">
         <is>
-          <t>Income floor. Never dismissed by default</t>
+          <t>Engine default real</t>
         </is>
       </c>
       <c r="J222" s="32" t="n"/>
@@ -46917,7 +47019,7 @@
       </c>
       <c r="N222" s="32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O222" s="32" t="n"/>
@@ -46937,11 +47039,7 @@
           <t>choice</t>
         </is>
       </c>
-      <c r="U222" s="10" t="inlineStr">
-        <is>
-          <t>full scheduled (likely), reduced %, none</t>
-        </is>
-      </c>
+      <c r="U222" s="10" t="inlineStr"/>
       <c r="V222" s="33" t="inlineStr">
         <is>
           <t>7</t>
@@ -46971,33 +47069,33 @@
       </c>
       <c r="E223" s="32" t="inlineStr">
         <is>
-          <t>Retirement spending</t>
+          <t>Assumptions</t>
         </is>
       </c>
       <c r="F223" s="32" t="inlineStr">
         <is>
-          <t>Spending in retirement</t>
+          <t>Life expectancy</t>
         </is>
       </c>
       <c r="G223" s="32" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Tertiary</t>
         </is>
       </c>
       <c r="H223" s="32" t="inlineStr">
         <is>
-          <t>Amount, defaults to current spending</t>
+          <t>Age, default 90</t>
         </is>
       </c>
       <c r="I223" s="32" t="inlineStr">
         <is>
-          <t>FI number</t>
+          <t>Decumulation length</t>
         </is>
       </c>
       <c r="J223" s="32" t="n"/>
       <c r="K223" s="32" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>Coach guesstimate</t>
         </is>
       </c>
       <c r="L223" s="32" t="n"/>
@@ -47008,7 +47106,7 @@
       </c>
       <c r="N223" s="32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O223" s="32" t="n"/>
@@ -47017,7 +47115,11 @@
           <t>Now</t>
         </is>
       </c>
-      <c r="Q223" s="32" t="n"/>
+      <c r="Q223" s="32" t="inlineStr">
+        <is>
+          <t>ProjectionLab default 85</t>
+        </is>
+      </c>
       <c r="S223" s="10" t="inlineStr">
         <is>
           <t>Plan › Goals</t>
@@ -47025,7 +47127,7 @@
       </c>
       <c r="T223" s="10" t="inlineStr">
         <is>
-          <t>money</t>
+          <t>text</t>
         </is>
       </c>
       <c r="U223" s="10" t="inlineStr"/>
@@ -47048,7 +47150,7 @@
       </c>
       <c r="C224" s="32" t="inlineStr">
         <is>
-          <t>Later</t>
+          <t>Session 2+</t>
         </is>
       </c>
       <c r="D224" s="32" t="inlineStr">
@@ -47058,12 +47160,12 @@
       </c>
       <c r="E224" s="32" t="inlineStr">
         <is>
-          <t>Retirement spending</t>
+          <t>Assumptions</t>
         </is>
       </c>
       <c r="F224" s="32" t="inlineStr">
         <is>
-          <t>Go-go, slow-go, no-go phases</t>
+          <t>Social Security</t>
         </is>
       </c>
       <c r="G224" s="32" t="inlineStr">
@@ -47073,18 +47175,18 @@
       </c>
       <c r="H224" s="32" t="inlineStr">
         <is>
-          <t>Three amounts with ages</t>
+          <t>Pick: full scheduled (likely), reduced %, none</t>
         </is>
       </c>
       <c r="I224" s="32" t="inlineStr">
         <is>
-          <t>Realistic drawdown</t>
+          <t>Income floor. Never dismissed by default</t>
         </is>
       </c>
       <c r="J224" s="32" t="n"/>
       <c r="K224" s="32" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>Coach guesstimate</t>
         </is>
       </c>
       <c r="L224" s="32" t="n"/>
@@ -47101,7 +47203,7 @@
       <c r="O224" s="32" t="n"/>
       <c r="P224" s="32" t="inlineStr">
         <is>
-          <t>Later</t>
+          <t>Now</t>
         </is>
       </c>
       <c r="Q224" s="32" t="n"/>
@@ -47112,10 +47214,14 @@
       </c>
       <c r="T224" s="10" t="inlineStr">
         <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="U224" s="10" t="inlineStr"/>
+          <t>choice</t>
+        </is>
+      </c>
+      <c r="U224" s="10" t="inlineStr">
+        <is>
+          <t>full scheduled (likely), reduced %, none</t>
+        </is>
+      </c>
       <c r="V224" s="33" t="inlineStr">
         <is>
           <t>7</t>
@@ -47135,7 +47241,7 @@
       </c>
       <c r="C225" s="32" t="inlineStr">
         <is>
-          <t>Session 1</t>
+          <t>Session 2+</t>
         </is>
       </c>
       <c r="D225" s="32" t="inlineStr">
@@ -47145,12 +47251,12 @@
       </c>
       <c r="E225" s="32" t="inlineStr">
         <is>
-          <t>Milestones</t>
+          <t>Retirement spending</t>
         </is>
       </c>
       <c r="F225" s="32" t="inlineStr">
         <is>
-          <t>Lean FI (FAT costs only)</t>
+          <t>Spending in retirement</t>
         </is>
       </c>
       <c r="G225" s="32" t="inlineStr">
@@ -47160,24 +47266,24 @@
       </c>
       <c r="H225" s="32" t="inlineStr">
         <is>
-          <t>Computed with date</t>
+          <t>Amount, defaults to current spending</t>
         </is>
       </c>
       <c r="I225" s="32" t="inlineStr">
         <is>
-          <t>Milestone ladder</t>
+          <t>FI number</t>
         </is>
       </c>
       <c r="J225" s="32" t="n"/>
       <c r="K225" s="32" t="inlineStr">
         <is>
-          <t>Computed</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="L225" s="32" t="n"/>
       <c r="M225" s="32" t="inlineStr">
         <is>
-          <t>Computed</t>
+          <t>All</t>
         </is>
       </c>
       <c r="N225" s="32" t="inlineStr">
@@ -47191,11 +47297,7 @@
           <t>Now</t>
         </is>
       </c>
-      <c r="Q225" s="32" t="inlineStr">
-        <is>
-          <t>Your definition</t>
-        </is>
-      </c>
+      <c r="Q225" s="32" t="n"/>
       <c r="S225" s="10" t="inlineStr">
         <is>
           <t>Plan › Goals</t>
@@ -47203,7 +47305,7 @@
       </c>
       <c r="T225" s="10" t="inlineStr">
         <is>
-          <t>computed</t>
+          <t>money</t>
         </is>
       </c>
       <c r="U225" s="10" t="inlineStr"/>
@@ -47226,7 +47328,7 @@
       </c>
       <c r="C226" s="32" t="inlineStr">
         <is>
-          <t>Session 1</t>
+          <t>Later</t>
         </is>
       </c>
       <c r="D226" s="32" t="inlineStr">
@@ -47236,57 +47338,53 @@
       </c>
       <c r="E226" s="32" t="inlineStr">
         <is>
-          <t>Milestones</t>
+          <t>Retirement spending</t>
         </is>
       </c>
       <c r="F226" s="32" t="inlineStr">
         <is>
-          <t>Coast FI</t>
+          <t>Go-go, slow-go, no-go phases</t>
         </is>
       </c>
       <c r="G226" s="32" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Tertiary</t>
         </is>
       </c>
       <c r="H226" s="32" t="inlineStr">
         <is>
-          <t>Computed from age, retirement age, return</t>
+          <t>Three amounts with ages</t>
         </is>
       </c>
       <c r="I226" s="32" t="inlineStr">
         <is>
-          <t>Computed properly, not a fixed multiple</t>
+          <t>Realistic drawdown</t>
         </is>
       </c>
       <c r="J226" s="32" t="n"/>
       <c r="K226" s="32" t="inlineStr">
         <is>
-          <t>Computed</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="L226" s="32" t="n"/>
       <c r="M226" s="32" t="inlineStr">
         <is>
-          <t>Computed</t>
+          <t>All</t>
         </is>
       </c>
       <c r="N226" s="32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O226" s="32" t="n"/>
       <c r="P226" s="32" t="inlineStr">
         <is>
-          <t>Now</t>
-        </is>
-      </c>
-      <c r="Q226" s="32" t="inlineStr">
-        <is>
-          <t>ProjectionLab uses 15x spending</t>
-        </is>
-      </c>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="Q226" s="32" t="n"/>
       <c r="S226" s="10" t="inlineStr">
         <is>
           <t>Plan › Goals</t>
@@ -47294,7 +47392,7 @@
       </c>
       <c r="T226" s="10" t="inlineStr">
         <is>
-          <t>computed</t>
+          <t>money</t>
         </is>
       </c>
       <c r="U226" s="10" t="inlineStr"/>
@@ -47332,7 +47430,7 @@
       </c>
       <c r="F227" s="32" t="inlineStr">
         <is>
-          <t>Barista FI</t>
+          <t>Lean FI (FAT costs only)</t>
         </is>
       </c>
       <c r="G227" s="32" t="inlineStr">
@@ -47342,29 +47440,29 @@
       </c>
       <c r="H227" s="32" t="inlineStr">
         <is>
-          <t>Part-time income field plus computed date</t>
+          <t>Computed with date</t>
         </is>
       </c>
       <c r="I227" s="32" t="inlineStr">
         <is>
-          <t>$100/mo = $30k rule</t>
+          <t>Milestone ladder</t>
         </is>
       </c>
       <c r="J227" s="32" t="n"/>
       <c r="K227" s="32" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>Computed</t>
         </is>
       </c>
       <c r="L227" s="32" t="n"/>
       <c r="M227" s="32" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Computed</t>
         </is>
       </c>
       <c r="N227" s="32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O227" s="32" t="n"/>
@@ -47373,7 +47471,11 @@
           <t>Now</t>
         </is>
       </c>
-      <c r="Q227" s="32" t="n"/>
+      <c r="Q227" s="32" t="inlineStr">
+        <is>
+          <t>Your definition</t>
+        </is>
+      </c>
       <c r="S227" s="10" t="inlineStr">
         <is>
           <t>Plan › Goals</t>
@@ -47381,7 +47483,7 @@
       </c>
       <c r="T227" s="10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>computed</t>
         </is>
       </c>
       <c r="U227" s="10" t="inlineStr"/>
@@ -47419,22 +47521,22 @@
       </c>
       <c r="F228" s="32" t="inlineStr">
         <is>
-          <t>Regular FI</t>
+          <t>Coast FI</t>
         </is>
       </c>
       <c r="G228" s="32" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="H228" s="32" t="inlineStr">
         <is>
-          <t>Computed date</t>
+          <t>Computed from age, retirement age, return</t>
         </is>
       </c>
       <c r="I228" s="32" t="inlineStr">
         <is>
-          <t>Headline result</t>
+          <t>Computed properly, not a fixed multiple</t>
         </is>
       </c>
       <c r="J228" s="32" t="n"/>
@@ -47460,7 +47562,11 @@
           <t>Now</t>
         </is>
       </c>
-      <c r="Q228" s="32" t="n"/>
+      <c r="Q228" s="32" t="inlineStr">
+        <is>
+          <t>ProjectionLab uses 15x spending</t>
+        </is>
+      </c>
       <c r="S228" s="10" t="inlineStr">
         <is>
           <t>Plan › Goals</t>
@@ -47491,7 +47597,7 @@
       </c>
       <c r="C229" s="32" t="inlineStr">
         <is>
-          <t>Later</t>
+          <t>Session 1</t>
         </is>
       </c>
       <c r="D229" s="32" t="inlineStr">
@@ -47506,7 +47612,7 @@
       </c>
       <c r="F229" s="32" t="inlineStr">
         <is>
-          <t>True FI (after tax)</t>
+          <t>Barista FI</t>
         </is>
       </c>
       <c r="G229" s="32" t="inlineStr">
@@ -47516,35 +47622,35 @@
       </c>
       <c r="H229" s="32" t="inlineStr">
         <is>
-          <t>Computed, unlockable</t>
+          <t>Part-time income field plus computed date</t>
         </is>
       </c>
       <c r="I229" s="32" t="inlineStr">
         <is>
-          <t>Dramatic unlock after decumulation</t>
+          <t>$100/mo = $30k rule</t>
         </is>
       </c>
       <c r="J229" s="32" t="n"/>
       <c r="K229" s="32" t="inlineStr">
         <is>
-          <t>Computed</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="L229" s="32" t="n"/>
       <c r="M229" s="32" t="inlineStr">
         <is>
-          <t>Computed</t>
+          <t>All</t>
         </is>
       </c>
       <c r="N229" s="32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O229" s="32" t="n"/>
       <c r="P229" s="32" t="inlineStr">
         <is>
-          <t>Later</t>
+          <t>Now</t>
         </is>
       </c>
       <c r="Q229" s="32" t="n"/>
@@ -47555,7 +47661,7 @@
       </c>
       <c r="T229" s="10" t="inlineStr">
         <is>
-          <t>computed</t>
+          <t>date</t>
         </is>
       </c>
       <c r="U229" s="10" t="inlineStr"/>
@@ -47593,12 +47699,12 @@
       </c>
       <c r="F230" s="32" t="inlineStr">
         <is>
-          <t>Debt free date</t>
+          <t>Regular FI</t>
         </is>
       </c>
       <c r="G230" s="32" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="H230" s="32" t="inlineStr">
@@ -47608,7 +47714,7 @@
       </c>
       <c r="I230" s="32" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Headline result</t>
         </is>
       </c>
       <c r="J230" s="32" t="n"/>
@@ -47625,7 +47731,7 @@
       </c>
       <c r="N230" s="32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O230" s="32" t="n"/>
@@ -47665,7 +47771,7 @@
       </c>
       <c r="C231" s="32" t="inlineStr">
         <is>
-          <t>Session 2+</t>
+          <t>Later</t>
         </is>
       </c>
       <c r="D231" s="32" t="inlineStr">
@@ -47680,52 +47786,48 @@
       </c>
       <c r="F231" s="32" t="inlineStr">
         <is>
-          <t>Custom milestone (at a date or when a condition is true)</t>
+          <t>True FI (after tax)</t>
         </is>
       </c>
       <c r="G231" s="32" t="inlineStr">
         <is>
-          <t>Tertiary</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="H231" s="32" t="inlineStr">
         <is>
-          <t>Name plus date or condition</t>
+          <t>Computed, unlockable</t>
         </is>
       </c>
       <c r="I231" s="32" t="inlineStr">
         <is>
-          <t>Bind events to the timeline</t>
+          <t>Dramatic unlock after decumulation</t>
         </is>
       </c>
       <c r="J231" s="32" t="n"/>
       <c r="K231" s="32" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>Computed</t>
         </is>
       </c>
       <c r="L231" s="32" t="n"/>
       <c r="M231" s="32" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Computed</t>
         </is>
       </c>
       <c r="N231" s="32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O231" s="32" t="n"/>
       <c r="P231" s="32" t="inlineStr">
         <is>
-          <t>Now</t>
-        </is>
-      </c>
-      <c r="Q231" s="32" t="inlineStr">
-        <is>
-          <t>ProjectionLab pattern</t>
-        </is>
-      </c>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="Q231" s="32" t="n"/>
       <c r="S231" s="10" t="inlineStr">
         <is>
           <t>Plan › Goals</t>
@@ -47733,7 +47835,7 @@
       </c>
       <c r="T231" s="10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>computed</t>
         </is>
       </c>
       <c r="U231" s="10" t="inlineStr"/>
@@ -47766,12 +47868,12 @@
       </c>
       <c r="E232" s="32" t="inlineStr">
         <is>
-          <t>Emergency fund</t>
+          <t>Milestones</t>
         </is>
       </c>
       <c r="F232" s="32" t="inlineStr">
         <is>
-          <t>Rule of 5 target (age / 5 months)</t>
+          <t>Debt free date</t>
         </is>
       </c>
       <c r="G232" s="32" t="inlineStr">
@@ -47781,12 +47883,12 @@
       </c>
       <c r="H232" s="32" t="inlineStr">
         <is>
-          <t>Computed with monthly add</t>
+          <t>Computed date</t>
         </is>
       </c>
       <c r="I232" s="32" t="inlineStr">
         <is>
-          <t>Exactly how much to add each month</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="J232" s="32" t="n"/>
@@ -47803,7 +47905,7 @@
       </c>
       <c r="N232" s="32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O232" s="32" t="n"/>
@@ -47812,11 +47914,7 @@
           <t>Now</t>
         </is>
       </c>
-      <c r="Q232" s="32" t="inlineStr">
-        <is>
-          <t>Adjusted by income stability</t>
-        </is>
-      </c>
+      <c r="Q232" s="32" t="n"/>
       <c r="S232" s="10" t="inlineStr">
         <is>
           <t>Plan › Goals</t>
@@ -47847,7 +47945,7 @@
       </c>
       <c r="C233" s="32" t="inlineStr">
         <is>
-          <t>Later</t>
+          <t>Session 2+</t>
         </is>
       </c>
       <c r="D233" s="32" t="inlineStr">
@@ -47857,12 +47955,12 @@
       </c>
       <c r="E233" s="32" t="inlineStr">
         <is>
-          <t>Life events</t>
+          <t>Milestones</t>
         </is>
       </c>
       <c r="F233" s="32" t="inlineStr">
         <is>
-          <t>Scenario blocks (home, car, kid, job change, sabbatical, move, marriage, side hustle, inheritance)</t>
+          <t>Custom milestone (at a date or when a condition is true)</t>
         </is>
       </c>
       <c r="G233" s="32" t="inlineStr">
@@ -47872,12 +47970,12 @@
       </c>
       <c r="H233" s="32" t="inlineStr">
         <is>
-          <t>Event picker grid</t>
+          <t>Name plus date or condition</t>
         </is>
       </c>
       <c r="I233" s="32" t="inlineStr">
         <is>
-          <t>Life simulator. Drag to reorder and see FI date move</t>
+          <t>Bind events to the timeline</t>
         </is>
       </c>
       <c r="J233" s="32" t="n"/>
@@ -47894,18 +47992,18 @@
       </c>
       <c r="N233" s="32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O233" s="32" t="n"/>
       <c r="P233" s="32" t="inlineStr">
         <is>
-          <t>Later</t>
+          <t>Now</t>
         </is>
       </c>
       <c r="Q233" s="32" t="inlineStr">
         <is>
-          <t>ProjectionLab milestone grid</t>
+          <t>ProjectionLab pattern</t>
         </is>
       </c>
       <c r="S233" s="10" t="inlineStr">
@@ -47915,7 +48013,7 @@
       </c>
       <c r="T233" s="10" t="inlineStr">
         <is>
-          <t>choice</t>
+          <t>date</t>
         </is>
       </c>
       <c r="U233" s="10" t="inlineStr"/>
@@ -47938,7 +48036,7 @@
       </c>
       <c r="C234" s="32" t="inlineStr">
         <is>
-          <t>Later</t>
+          <t>Session 1</t>
         </is>
       </c>
       <c r="D234" s="32" t="inlineStr">
@@ -47948,53 +48046,57 @@
       </c>
       <c r="E234" s="32" t="inlineStr">
         <is>
-          <t>What Matters</t>
+          <t>Emergency fund</t>
         </is>
       </c>
       <c r="F234" s="32" t="inlineStr">
         <is>
-          <t>Ranked priorities (fund and remove)</t>
+          <t>Rule of 5 target (age / 5 months)</t>
         </is>
       </c>
       <c r="G234" s="32" t="inlineStr">
         <is>
-          <t>Tertiary</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="H234" s="32" t="inlineStr">
         <is>
-          <t>Two ranked lists</t>
+          <t>Computed with monthly add</t>
         </is>
       </c>
       <c r="I234" s="32" t="inlineStr">
         <is>
-          <t>Spending vs priorities</t>
+          <t>Exactly how much to add each month</t>
         </is>
       </c>
       <c r="J234" s="32" t="n"/>
       <c r="K234" s="32" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>Computed</t>
         </is>
       </c>
       <c r="L234" s="32" t="n"/>
       <c r="M234" s="32" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Computed</t>
         </is>
       </c>
       <c r="N234" s="32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O234" s="32" t="n"/>
       <c r="P234" s="32" t="inlineStr">
         <is>
-          <t>Later</t>
-        </is>
-      </c>
-      <c r="Q234" s="32" t="n"/>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="Q234" s="32" t="inlineStr">
+        <is>
+          <t>Adjusted by income stability</t>
+        </is>
+      </c>
       <c r="S234" s="10" t="inlineStr">
         <is>
           <t>Plan › Goals</t>
@@ -48002,7 +48104,7 @@
       </c>
       <c r="T234" s="10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>computed</t>
         </is>
       </c>
       <c r="U234" s="10" t="inlineStr"/>
@@ -48025,7 +48127,7 @@
       </c>
       <c r="C235" s="32" t="inlineStr">
         <is>
-          <t>Parked</t>
+          <t>Later</t>
         </is>
       </c>
       <c r="D235" s="32" t="inlineStr">
@@ -48035,12 +48137,12 @@
       </c>
       <c r="E235" s="32" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Life events</t>
         </is>
       </c>
       <c r="F235" s="32" t="inlineStr">
         <is>
-          <t>Best case / dream life</t>
+          <t>Scenario blocks (home, car, kid, job change, sabbatical, move, marriage, side hustle, inheritance)</t>
         </is>
       </c>
       <c r="G235" s="32" t="inlineStr">
@@ -48050,12 +48152,12 @@
       </c>
       <c r="H235" s="32" t="inlineStr">
         <is>
-          <t>Free text plus cost</t>
+          <t>Event picker grid</t>
         </is>
       </c>
       <c r="I235" s="32" t="inlineStr">
         <is>
-          <t>Eras intro</t>
+          <t>Life simulator. Drag to reorder and see FI date move</t>
         </is>
       </c>
       <c r="J235" s="32" t="n"/>
@@ -48072,18 +48174,18 @@
       </c>
       <c r="N235" s="32" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O235" s="32" t="n"/>
       <c r="P235" s="32" t="inlineStr">
         <is>
-          <t>Parked</t>
+          <t>Later</t>
         </is>
       </c>
       <c r="Q235" s="32" t="inlineStr">
         <is>
-          <t>Parked Oct 18</t>
+          <t>ProjectionLab milestone grid</t>
         </is>
       </c>
       <c r="S235" s="10" t="inlineStr">
@@ -48093,7 +48195,7 @@
       </c>
       <c r="T235" s="10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>choice</t>
         </is>
       </c>
       <c r="U235" s="10" t="inlineStr"/>
@@ -48116,49 +48218,49 @@
       </c>
       <c r="C236" s="32" t="inlineStr">
         <is>
-          <t>Discovery</t>
+          <t>Later</t>
         </is>
       </c>
       <c r="D236" s="32" t="inlineStr">
         <is>
-          <t>Coaching</t>
+          <t>Goals</t>
         </is>
       </c>
       <c r="E236" s="32" t="inlineStr">
         <is>
-          <t>Discovery call</t>
+          <t>What Matters</t>
         </is>
       </c>
       <c r="F236" s="32" t="inlineStr">
         <is>
-          <t>Discovery table numbers</t>
+          <t>Ranked priorities (fund and remove)</t>
         </is>
       </c>
       <c r="G236" s="32" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Tertiary</t>
         </is>
       </c>
       <c r="H236" s="32" t="inlineStr">
         <is>
-          <t>Quick table, populates the map</t>
+          <t>Two ranked lists</t>
         </is>
       </c>
       <c r="I236" s="32" t="inlineStr">
         <is>
-          <t>Not starting blind in session 1</t>
+          <t>Spending vs priorities</t>
         </is>
       </c>
       <c r="J236" s="32" t="n"/>
       <c r="K236" s="32" t="inlineStr">
         <is>
-          <t>Coach</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="L236" s="32" t="n"/>
       <c r="M236" s="32" t="inlineStr">
         <is>
-          <t>Know it</t>
+          <t>All</t>
         </is>
       </c>
       <c r="N236" s="32" t="inlineStr">
@@ -48169,13 +48271,13 @@
       <c r="O236" s="32" t="n"/>
       <c r="P236" s="32" t="inlineStr">
         <is>
-          <t>Now</t>
+          <t>Later</t>
         </is>
       </c>
       <c r="Q236" s="32" t="n"/>
       <c r="S236" s="10" t="inlineStr">
         <is>
-          <t>Home / ⚙ Coach tools</t>
+          <t>Plan › Goals</t>
         </is>
       </c>
       <c r="T236" s="10" t="inlineStr">
@@ -48186,7 +48288,7 @@
       <c r="U236" s="10" t="inlineStr"/>
       <c r="V236" s="33" t="inlineStr">
         <is>
-          <t>9-10</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -48203,66 +48305,70 @@
       </c>
       <c r="C237" s="32" t="inlineStr">
         <is>
-          <t>Session 1</t>
+          <t>Parked</t>
         </is>
       </c>
       <c r="D237" s="32" t="inlineStr">
         <is>
-          <t>Coaching</t>
+          <t>Goals</t>
         </is>
       </c>
       <c r="E237" s="32" t="inlineStr">
         <is>
-          <t>Session</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="F237" s="32" t="inlineStr">
         <is>
-          <t>Session date and agenda</t>
+          <t>Best case / dream life</t>
         </is>
       </c>
       <c r="G237" s="32" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Tertiary</t>
         </is>
       </c>
       <c r="H237" s="32" t="inlineStr">
         <is>
-          <t>Agenda on Home</t>
+          <t>Free text plus cost</t>
         </is>
       </c>
       <c r="I237" s="32" t="inlineStr">
         <is>
-          <t>Guide me path</t>
+          <t>Eras intro</t>
         </is>
       </c>
       <c r="J237" s="32" t="n"/>
       <c r="K237" s="32" t="inlineStr">
         <is>
-          <t>Coach</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="L237" s="32" t="n"/>
       <c r="M237" s="32" t="inlineStr">
         <is>
-          <t>Know it</t>
+          <t>All</t>
         </is>
       </c>
       <c r="N237" s="32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O237" s="32" t="n"/>
       <c r="P237" s="32" t="inlineStr">
         <is>
-          <t>Now</t>
-        </is>
-      </c>
-      <c r="Q237" s="32" t="n"/>
+          <t>Parked</t>
+        </is>
+      </c>
+      <c r="Q237" s="32" t="inlineStr">
+        <is>
+          <t>Parked Oct 18</t>
+        </is>
+      </c>
       <c r="S237" s="10" t="inlineStr">
         <is>
-          <t>Home / ⚙ Coach tools</t>
+          <t>Plan › Goals</t>
         </is>
       </c>
       <c r="T237" s="10" t="inlineStr">
@@ -48273,7 +48379,7 @@
       <c r="U237" s="10" t="inlineStr"/>
       <c r="V237" s="33" t="inlineStr">
         <is>
-          <t>9-10</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -48290,7 +48396,7 @@
       </c>
       <c r="C238" s="32" t="inlineStr">
         <is>
-          <t>Session 1</t>
+          <t>Discovery</t>
         </is>
       </c>
       <c r="D238" s="32" t="inlineStr">
@@ -48300,12 +48406,12 @@
       </c>
       <c r="E238" s="32" t="inlineStr">
         <is>
-          <t>Session</t>
+          <t>Discovery call</t>
         </is>
       </c>
       <c r="F238" s="32" t="inlineStr">
         <is>
-          <t>Session notes</t>
+          <t>Discovery table numbers</t>
         </is>
       </c>
       <c r="G238" s="32" t="inlineStr">
@@ -48315,12 +48421,12 @@
       </c>
       <c r="H238" s="32" t="inlineStr">
         <is>
-          <t>Collapsed notes box</t>
+          <t>Quick table, populates the map</t>
         </is>
       </c>
       <c r="I238" s="32" t="inlineStr">
         <is>
-          <t>Coach only</t>
+          <t>Not starting blind in session 1</t>
         </is>
       </c>
       <c r="J238" s="32" t="n"/>
@@ -48387,12 +48493,12 @@
       </c>
       <c r="E239" s="32" t="inlineStr">
         <is>
-          <t>Homework</t>
+          <t>Session</t>
         </is>
       </c>
       <c r="F239" s="32" t="inlineStr">
         <is>
-          <t>Homework list (auto from fields marked 'will email')</t>
+          <t>Session date and agenda</t>
         </is>
       </c>
       <c r="G239" s="32" t="inlineStr">
@@ -48402,12 +48508,12 @@
       </c>
       <c r="H239" s="32" t="inlineStr">
         <is>
-          <t>Checklist with due date</t>
+          <t>Agenda on Home</t>
         </is>
       </c>
       <c r="I239" s="32" t="inlineStr">
         <is>
-          <t>Client to-dos</t>
+          <t>Guide me path</t>
         </is>
       </c>
       <c r="J239" s="32" t="n"/>
@@ -48441,7 +48547,7 @@
       </c>
       <c r="T239" s="10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="U239" s="10" t="inlineStr"/>
@@ -48474,12 +48580,12 @@
       </c>
       <c r="E240" s="32" t="inlineStr">
         <is>
-          <t>One-pager</t>
+          <t>Session</t>
         </is>
       </c>
       <c r="F240" s="32" t="inlineStr">
         <is>
-          <t>Key stats, things to know, to-dos, goals</t>
+          <t>Session notes</t>
         </is>
       </c>
       <c r="G240" s="32" t="inlineStr">
@@ -48489,12 +48595,12 @@
       </c>
       <c r="H240" s="32" t="inlineStr">
         <is>
-          <t>Auto-filled, editable</t>
+          <t>Collapsed notes box</t>
         </is>
       </c>
       <c r="I240" s="32" t="inlineStr">
         <is>
-          <t>End-of-session one-pager</t>
+          <t>Coach only</t>
         </is>
       </c>
       <c r="J240" s="32" t="n"/>
@@ -48561,12 +48667,12 @@
       </c>
       <c r="E241" s="32" t="inlineStr">
         <is>
-          <t>One-pager</t>
+          <t>Homework</t>
         </is>
       </c>
       <c r="F241" s="32" t="inlineStr">
         <is>
-          <t>Strengths, struggles, do more of, do less of</t>
+          <t>Homework list (auto from fields marked 'will email')</t>
         </is>
       </c>
       <c r="G241" s="32" t="inlineStr">
@@ -48576,12 +48682,12 @@
       </c>
       <c r="H241" s="32" t="inlineStr">
         <is>
-          <t>Four short boxes</t>
+          <t>Checklist with due date</t>
         </is>
       </c>
       <c r="I241" s="32" t="inlineStr">
         <is>
-          <t>Coaching summary</t>
+          <t>Client to-dos</t>
         </is>
       </c>
       <c r="J241" s="32" t="n"/>
@@ -48615,7 +48721,7 @@
       </c>
       <c r="T241" s="10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="U241" s="10" t="inlineStr"/>
@@ -48638,7 +48744,7 @@
       </c>
       <c r="C242" s="32" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Session 1</t>
         </is>
       </c>
       <c r="D242" s="32" t="inlineStr">
@@ -48648,12 +48754,12 @@
       </c>
       <c r="E242" s="32" t="inlineStr">
         <is>
-          <t>Money date</t>
+          <t>One-pager</t>
         </is>
       </c>
       <c r="F242" s="32" t="inlineStr">
         <is>
-          <t>Monthly check-in notes and next check date</t>
+          <t>Key stats, things to know, to-dos, goals</t>
         </is>
       </c>
       <c r="G242" s="32" t="inlineStr">
@@ -48663,12 +48769,12 @@
       </c>
       <c r="H242" s="32" t="inlineStr">
         <is>
-          <t>Date plus notes</t>
+          <t>Auto-filled, editable</t>
         </is>
       </c>
       <c r="I242" s="32" t="inlineStr">
         <is>
-          <t>Maintenance tier</t>
+          <t>End-of-session one-pager</t>
         </is>
       </c>
       <c r="J242" s="32" t="n"/>
@@ -48702,7 +48808,7 @@
       </c>
       <c r="T242" s="10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="U242" s="10" t="inlineStr"/>
@@ -48725,7 +48831,7 @@
       </c>
       <c r="C243" s="32" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Session 1</t>
         </is>
       </c>
       <c r="D243" s="32" t="inlineStr">
@@ -48735,12 +48841,12 @@
       </c>
       <c r="E243" s="32" t="inlineStr">
         <is>
-          <t>Scoreboard</t>
+          <t>One-pager</t>
         </is>
       </c>
       <c r="F243" s="32" t="inlineStr">
         <is>
-          <t>Client satisfaction score</t>
+          <t>Strengths, struggles, do more of, do less of</t>
         </is>
       </c>
       <c r="G243" s="32" t="inlineStr">
@@ -48750,12 +48856,12 @@
       </c>
       <c r="H243" s="32" t="inlineStr">
         <is>
-          <t>1 to 10</t>
+          <t>Four short boxes</t>
         </is>
       </c>
       <c r="I243" s="32" t="inlineStr">
         <is>
-          <t>On the scoreboard (Oct 8)</t>
+          <t>Coaching summary</t>
         </is>
       </c>
       <c r="J243" s="32" t="n"/>
@@ -48812,7 +48918,7 @@
       </c>
       <c r="C244" s="32" t="inlineStr">
         <is>
-          <t>Session 1</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="D244" s="32" t="inlineStr">
@@ -48822,12 +48928,12 @@
       </c>
       <c r="E244" s="32" t="inlineStr">
         <is>
-          <t>Every number</t>
+          <t>Money date</t>
         </is>
       </c>
       <c r="F244" s="32" t="inlineStr">
         <is>
-          <t>Next check date for rough or aged numbers</t>
+          <t>Monthly check-in notes and next check date</t>
         </is>
       </c>
       <c r="G244" s="32" t="inlineStr">
@@ -48837,12 +48943,12 @@
       </c>
       <c r="H244" s="32" t="inlineStr">
         <is>
-          <t>Date (auto from age)</t>
+          <t>Date plus notes</t>
         </is>
       </c>
       <c r="I244" s="32" t="inlineStr">
         <is>
-          <t>Refresh nag</t>
+          <t>Maintenance tier</t>
         </is>
       </c>
       <c r="J244" s="32" t="n"/>
@@ -48899,7 +49005,7 @@
       </c>
       <c r="C245" s="32" t="inlineStr">
         <is>
-          <t>Session 1</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="D245" s="32" t="inlineStr">
@@ -48909,33 +49015,33 @@
       </c>
       <c r="E245" s="32" t="inlineStr">
         <is>
-          <t>Why now</t>
+          <t>Scoreboard</t>
         </is>
       </c>
       <c r="F245" s="32" t="inlineStr">
         <is>
-          <t>What prompted this call</t>
+          <t>Client satisfaction score</t>
         </is>
       </c>
       <c r="G245" s="32" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="H245" s="32" t="inlineStr">
         <is>
-          <t>Text box</t>
+          <t>1 to 10</t>
         </is>
       </c>
       <c r="I245" s="32" t="inlineStr">
         <is>
-          <t>Client's own words; feeds the one-pager</t>
+          <t>On the scoreboard (Oct 8)</t>
         </is>
       </c>
       <c r="J245" s="32" t="n"/>
       <c r="K245" s="32" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>Coach</t>
         </is>
       </c>
       <c r="L245" s="32" t="n"/>
@@ -48946,7 +49052,7 @@
       </c>
       <c r="N245" s="32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O245" s="32" t="n"/>
@@ -48996,33 +49102,33 @@
       </c>
       <c r="E246" s="32" t="inlineStr">
         <is>
-          <t>Why now</t>
+          <t>Every number</t>
         </is>
       </c>
       <c r="F246" s="32" t="inlineStr">
         <is>
-          <t>Biggest worry and goal in their words</t>
+          <t>Next check date for rough or aged numbers</t>
         </is>
       </c>
       <c r="G246" s="32" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="H246" s="32" t="inlineStr">
         <is>
-          <t>Two text boxes</t>
+          <t>Date (auto from age)</t>
         </is>
       </c>
       <c r="I246" s="32" t="inlineStr">
         <is>
-          <t>Sets the session focus</t>
+          <t>Refresh nag</t>
         </is>
       </c>
       <c r="J246" s="32" t="n"/>
       <c r="K246" s="32" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>Coach</t>
         </is>
       </c>
       <c r="L246" s="32" t="n"/>
@@ -49033,7 +49139,7 @@
       </c>
       <c r="N246" s="32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O246" s="32" t="n"/>
@@ -49050,7 +49156,7 @@
       </c>
       <c r="T246" s="10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="U246" s="10" t="inlineStr"/>
@@ -49088,22 +49194,22 @@
       </c>
       <c r="F247" s="32" t="inlineStr">
         <is>
-          <t>Money feeling 1-10</t>
+          <t>What prompted this call</t>
         </is>
       </c>
       <c r="G247" s="32" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="H247" s="32" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Text box</t>
         </is>
       </c>
       <c r="I247" s="32" t="inlineStr">
         <is>
-          <t>Asked every session to show change</t>
+          <t>Client's own words; feeds the one-pager</t>
         </is>
       </c>
       <c r="J247" s="32" t="n"/>
@@ -49120,7 +49226,7 @@
       </c>
       <c r="N247" s="32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O247" s="32" t="n"/>
@@ -49137,7 +49243,7 @@
       </c>
       <c r="T247" s="10" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="U247" s="10" t="inlineStr"/>
@@ -49170,12 +49276,12 @@
       </c>
       <c r="E248" s="32" t="inlineStr">
         <is>
-          <t>Parking lot</t>
+          <t>Why now</t>
         </is>
       </c>
       <c r="F248" s="32" t="inlineStr">
         <is>
-          <t>Quick notes</t>
+          <t>Biggest worry and goal in their words</t>
         </is>
       </c>
       <c r="G248" s="32" t="inlineStr">
@@ -49185,18 +49291,18 @@
       </c>
       <c r="H248" s="32" t="inlineStr">
         <is>
-          <t>Always-visible note box</t>
+          <t>Two text boxes</t>
         </is>
       </c>
       <c r="I248" s="32" t="inlineStr">
         <is>
-          <t>Things the client mentions mid-sentence; convert to fields later</t>
+          <t>Sets the session focus</t>
         </is>
       </c>
       <c r="J248" s="32" t="n"/>
       <c r="K248" s="32" t="inlineStr">
         <is>
-          <t>Coach</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="L248" s="32" t="n"/>
@@ -49207,7 +49313,7 @@
       </c>
       <c r="N248" s="32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O248" s="32" t="n"/>
@@ -49252,17 +49358,17 @@
       </c>
       <c r="D249" s="32" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Coaching</t>
         </is>
       </c>
       <c r="E249" s="32" t="inlineStr">
         <is>
-          <t>Couples split</t>
+          <t>Why now</t>
         </is>
       </c>
       <c r="F249" s="32" t="inlineStr">
         <is>
-          <t>Joint, separate or mix</t>
+          <t>Money feeling 1-10</t>
         </is>
       </c>
       <c r="G249" s="32" t="inlineStr">
@@ -49272,12 +49378,12 @@
       </c>
       <c r="H249" s="32" t="inlineStr">
         <is>
-          <t>Toggle</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="I249" s="32" t="inlineStr">
         <is>
-          <t>How a couple runs money</t>
+          <t>Asked every session to show change</t>
         </is>
       </c>
       <c r="J249" s="32" t="n"/>
@@ -49289,7 +49395,7 @@
       <c r="L249" s="32" t="n"/>
       <c r="M249" s="32" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Know it</t>
         </is>
       </c>
       <c r="N249" s="32" t="inlineStr">
@@ -49306,18 +49412,18 @@
       <c r="Q249" s="32" t="n"/>
       <c r="S249" s="10" t="inlineStr">
         <is>
-          <t>My Money › Profile</t>
+          <t>Home / ⚙ Coach tools</t>
         </is>
       </c>
       <c r="T249" s="10" t="inlineStr">
         <is>
-          <t>choice</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="U249" s="10" t="inlineStr"/>
       <c r="V249" s="33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9-10</t>
         </is>
       </c>
     </row>
@@ -49339,44 +49445,44 @@
       </c>
       <c r="D250" s="32" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Coaching</t>
         </is>
       </c>
       <c r="E250" s="32" t="inlineStr">
         <is>
-          <t>Couples split</t>
+          <t>Parking lot</t>
         </is>
       </c>
       <c r="F250" s="32" t="inlineStr">
         <is>
-          <t>Who pays what (% or fixed)</t>
+          <t>Quick notes</t>
         </is>
       </c>
       <c r="G250" s="32" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="H250" s="32" t="inlineStr">
         <is>
-          <t>Split table</t>
+          <t>Always-visible note box</t>
         </is>
       </c>
       <c r="I250" s="32" t="inlineStr">
         <is>
-          <t>Housing, food, bills</t>
+          <t>Things the client mentions mid-sentence; convert to fields later</t>
         </is>
       </c>
       <c r="J250" s="32" t="n"/>
       <c r="K250" s="32" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>Coach</t>
         </is>
       </c>
       <c r="L250" s="32" t="n"/>
       <c r="M250" s="32" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Know it</t>
         </is>
       </c>
       <c r="N250" s="32" t="inlineStr">
@@ -49393,7 +49499,7 @@
       <c r="Q250" s="32" t="n"/>
       <c r="S250" s="10" t="inlineStr">
         <is>
-          <t>My Money › Profile</t>
+          <t>Home / ⚙ Coach tools</t>
         </is>
       </c>
       <c r="T250" s="10" t="inlineStr">
@@ -49404,7 +49510,7 @@
       <c r="U250" s="10" t="inlineStr"/>
       <c r="V250" s="33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9-10</t>
         </is>
       </c>
     </row>
@@ -49426,32 +49532,32 @@
       </c>
       <c r="D251" s="32" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="E251" s="32" t="inlineStr">
         <is>
-          <t>Variable income</t>
+          <t>Couples split</t>
         </is>
       </c>
       <c r="F251" s="32" t="inlineStr">
         <is>
-          <t>Last 12 months, typical month, lowest month</t>
+          <t>Joint, separate or mix</t>
         </is>
       </c>
       <c r="G251" s="32" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="H251" s="32" t="inlineStr">
         <is>
-          <t>Three amounts</t>
+          <t>Toggle</t>
         </is>
       </c>
       <c r="I251" s="32" t="inlineStr">
         <is>
-          <t>Self-employed, tips, creators. Lowest month drives the safe budget</t>
+          <t>How a couple runs money</t>
         </is>
       </c>
       <c r="J251" s="32" t="n"/>
@@ -49468,7 +49574,7 @@
       </c>
       <c r="N251" s="32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O251" s="32" t="n"/>
@@ -49480,12 +49586,12 @@
       <c r="Q251" s="32" t="n"/>
       <c r="S251" s="10" t="inlineStr">
         <is>
-          <t>My Money › Income</t>
+          <t>My Money › Profile</t>
         </is>
       </c>
       <c r="T251" s="10" t="inlineStr">
         <is>
-          <t>money</t>
+          <t>choice</t>
         </is>
       </c>
       <c r="U251" s="10" t="inlineStr"/>
@@ -49513,32 +49619,32 @@
       </c>
       <c r="D252" s="32" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="E252" s="32" t="inlineStr">
         <is>
-          <t>Variable income</t>
+          <t>Couples split</t>
         </is>
       </c>
       <c r="F252" s="32" t="inlineStr">
         <is>
-          <t>Set aside for taxes %</t>
+          <t>Who pays what (% or fixed)</t>
         </is>
       </c>
       <c r="G252" s="32" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="H252" s="32" t="inlineStr">
         <is>
-          <t>Percent</t>
+          <t>Split table</t>
         </is>
       </c>
       <c r="I252" s="32" t="inlineStr">
         <is>
-          <t>Self-employed only</t>
+          <t>Housing, food, bills</t>
         </is>
       </c>
       <c r="J252" s="32" t="n"/>
@@ -49555,7 +49661,7 @@
       </c>
       <c r="N252" s="32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O252" s="32" t="n"/>
@@ -49567,12 +49673,12 @@
       <c r="Q252" s="32" t="n"/>
       <c r="S252" s="10" t="inlineStr">
         <is>
-          <t>My Money › Income</t>
+          <t>My Money › Profile</t>
         </is>
       </c>
       <c r="T252" s="10" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>text</t>
         </is>
       </c>
       <c r="U252" s="10" t="inlineStr"/>
@@ -49595,7 +49701,7 @@
       </c>
       <c r="C253" s="32" t="inlineStr">
         <is>
-          <t>Session 2+</t>
+          <t>Session 1</t>
         </is>
       </c>
       <c r="D253" s="32" t="inlineStr">
@@ -49610,22 +49716,22 @@
       </c>
       <c r="F253" s="32" t="inlineStr">
         <is>
-          <t>Month by month (12 boxes)</t>
+          <t>Last 12 months, typical month, lowest month</t>
         </is>
       </c>
       <c r="G253" s="32" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="H253" s="32" t="inlineStr">
         <is>
-          <t>Twelve amounts</t>
+          <t>Three amounts</t>
         </is>
       </c>
       <c r="I253" s="32" t="inlineStr">
         <is>
-          <t>Builds the income chart</t>
+          <t>Self-employed, tips, creators. Lowest month drives the safe budget</t>
         </is>
       </c>
       <c r="J253" s="32" t="n"/>
@@ -49634,11 +49740,7 @@
           <t>Client</t>
         </is>
       </c>
-      <c r="L253" s="32" t="inlineStr">
-        <is>
-          <t>Often</t>
-        </is>
-      </c>
+      <c r="L253" s="32" t="n"/>
       <c r="M253" s="32" t="inlineStr">
         <is>
           <t>All</t>
@@ -49646,7 +49748,7 @@
       </c>
       <c r="N253" s="32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O253" s="32" t="n"/>
@@ -49696,27 +49798,27 @@
       </c>
       <c r="E254" s="32" t="inlineStr">
         <is>
-          <t>Other benefits</t>
+          <t>Variable income</t>
         </is>
       </c>
       <c r="F254" s="32" t="inlineStr">
         <is>
-          <t>Benefit name, what it is, how it works, value, using it?</t>
+          <t>Set aside for taxes %</t>
         </is>
       </c>
       <c r="G254" s="32" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="H254" s="32" t="inlineStr">
         <is>
-          <t>Row with five cells</t>
+          <t>Percent</t>
         </is>
       </c>
       <c r="I254" s="32" t="inlineStr">
         <is>
-          <t>Commuter, tuition, student loan help, wellness, phone, childcare FSA, meals, home office, ESPP, sabbatical, legal plan, pet insurance</t>
+          <t>Self-employed only</t>
         </is>
       </c>
       <c r="J254" s="32" t="n"/>
@@ -49725,11 +49827,7 @@
           <t>Client</t>
         </is>
       </c>
-      <c r="L254" s="32" t="inlineStr">
-        <is>
-          <t>Often</t>
-        </is>
-      </c>
+      <c r="L254" s="32" t="n"/>
       <c r="M254" s="32" t="inlineStr">
         <is>
           <t>All</t>
@@ -49737,7 +49835,7 @@
       </c>
       <c r="N254" s="32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O254" s="32" t="n"/>
@@ -49746,11 +49844,7 @@
           <t>Now</t>
         </is>
       </c>
-      <c r="Q254" s="32" t="inlineStr">
-        <is>
-          <t>Your comment: name it, explain it, give nontraditional examples</t>
-        </is>
-      </c>
+      <c r="Q254" s="32" t="n"/>
       <c r="S254" s="10" t="inlineStr">
         <is>
           <t>My Money › Income</t>
@@ -49758,7 +49852,7 @@
       </c>
       <c r="T254" s="10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="U254" s="10" t="inlineStr"/>
@@ -49791,27 +49885,27 @@
       </c>
       <c r="E255" s="32" t="inlineStr">
         <is>
-          <t>Equity pay</t>
+          <t>Variable income</t>
         </is>
       </c>
       <c r="F255" s="32" t="inlineStr">
         <is>
-          <t>ESPP %, discount; RSU grants and vest dates</t>
+          <t>Month by month (12 boxes)</t>
         </is>
       </c>
       <c r="G255" s="32" t="inlineStr">
         <is>
-          <t>Tertiary</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="H255" s="32" t="inlineStr">
         <is>
-          <t>Fields</t>
+          <t>Twelve amounts</t>
         </is>
       </c>
       <c r="I255" s="32" t="inlineStr">
         <is>
-          <t>Only if offered</t>
+          <t>Builds the income chart</t>
         </is>
       </c>
       <c r="J255" s="32" t="n"/>
@@ -49849,7 +49943,7 @@
       </c>
       <c r="T255" s="10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>money</t>
         </is>
       </c>
       <c r="U255" s="10" t="inlineStr"/>
@@ -49877,17 +49971,17 @@
       </c>
       <c r="D256" s="32" t="inlineStr">
         <is>
-          <t>Debt</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="E256" s="32" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Other benefits</t>
         </is>
       </c>
       <c r="F256" s="32" t="inlineStr">
         <is>
-          <t>Credit score, as-of date, source</t>
+          <t>Benefit name, what it is, how it works, value, using it?</t>
         </is>
       </c>
       <c r="G256" s="32" t="inlineStr">
@@ -49897,12 +49991,12 @@
       </c>
       <c r="H256" s="32" t="inlineStr">
         <is>
-          <t>Number plus date</t>
+          <t>Row with five cells</t>
         </is>
       </c>
       <c r="I256" s="32" t="inlineStr">
         <is>
-          <t>Context for refinancing and cards</t>
+          <t>Commuter, tuition, student loan help, wellness, phone, childcare FSA, meals, home office, ESPP, sabbatical, legal plan, pet insurance</t>
         </is>
       </c>
       <c r="J256" s="32" t="n"/>
@@ -49913,7 +50007,7 @@
       </c>
       <c r="L256" s="32" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Often</t>
         </is>
       </c>
       <c r="M256" s="32" t="inlineStr">
@@ -49932,15 +50026,19 @@
           <t>Now</t>
         </is>
       </c>
-      <c r="Q256" s="32" t="n"/>
+      <c r="Q256" s="32" t="inlineStr">
+        <is>
+          <t>Your comment: name it, explain it, give nontraditional examples</t>
+        </is>
+      </c>
       <c r="S256" s="10" t="inlineStr">
         <is>
-          <t>My Money › Debt</t>
+          <t>My Money › Income</t>
         </is>
       </c>
       <c r="T256" s="10" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="U256" s="10" t="inlineStr"/>
@@ -49963,37 +50061,37 @@
       </c>
       <c r="C257" s="32" t="inlineStr">
         <is>
-          <t>Session 1</t>
+          <t>Session 2+</t>
         </is>
       </c>
       <c r="D257" s="32" t="inlineStr">
         <is>
-          <t>Debt</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="E257" s="32" t="inlineStr">
         <is>
-          <t>Credit cards</t>
+          <t>Equity pay</t>
         </is>
       </c>
       <c r="F257" s="32" t="inlineStr">
         <is>
-          <t>Payment choice: minimum, custom, in full</t>
+          <t>ESPP %, discount; RSU grants and vest dates</t>
         </is>
       </c>
       <c r="G257" s="32" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tertiary</t>
         </is>
       </c>
       <c r="H257" s="32" t="inlineStr">
         <is>
-          <t>Toggle plus Pay in full button</t>
+          <t>Fields</t>
         </is>
       </c>
       <c r="I257" s="32" t="inlineStr">
         <is>
-          <t>Your comment: minimum payment computed in Primary, options below</t>
+          <t>Only if offered</t>
         </is>
       </c>
       <c r="J257" s="32" t="n"/>
@@ -50002,7 +50100,11 @@
           <t>Client</t>
         </is>
       </c>
-      <c r="L257" s="32" t="n"/>
+      <c r="L257" s="32" t="inlineStr">
+        <is>
+          <t>Often</t>
+        </is>
+      </c>
       <c r="M257" s="32" t="inlineStr">
         <is>
           <t>All</t>
@@ -50010,7 +50112,7 @@
       </c>
       <c r="N257" s="32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O257" s="32" t="n"/>
@@ -50022,12 +50124,12 @@
       <c r="Q257" s="32" t="n"/>
       <c r="S257" s="10" t="inlineStr">
         <is>
-          <t>My Money › Debt</t>
+          <t>My Money › Income</t>
         </is>
       </c>
       <c r="T257" s="10" t="inlineStr">
         <is>
-          <t>choice</t>
+          <t>text</t>
         </is>
       </c>
       <c r="U257" s="10" t="inlineStr"/>
@@ -50055,32 +50157,32 @@
       </c>
       <c r="D258" s="32" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>Debt</t>
         </is>
       </c>
       <c r="E258" s="32" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="F258" s="32" t="inlineStr">
         <is>
-          <t>Type, have it or not, premium</t>
+          <t>Credit score, as-of date, source</t>
         </is>
       </c>
       <c r="G258" s="32" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="H258" s="32" t="inlineStr">
         <is>
-          <t>Dropdown, toggle, amount</t>
+          <t>Number plus date</t>
         </is>
       </c>
       <c r="I258" s="32" t="inlineStr">
         <is>
-          <t>Health, life, disability, renters or home, car, umbrella</t>
+          <t>Context for refinancing and cards</t>
         </is>
       </c>
       <c r="J258" s="32" t="n"/>
@@ -50089,7 +50191,11 @@
           <t>Client</t>
         </is>
       </c>
-      <c r="L258" s="32" t="n"/>
+      <c r="L258" s="32" t="inlineStr">
+        <is>
+          <t>Sometimes</t>
+        </is>
+      </c>
       <c r="M258" s="32" t="inlineStr">
         <is>
           <t>All</t>
@@ -50109,12 +50215,12 @@
       <c r="Q258" s="32" t="n"/>
       <c r="S258" s="10" t="inlineStr">
         <is>
-          <t>My Money › Protection</t>
+          <t>My Money › Debt</t>
         </is>
       </c>
       <c r="T258" s="10" t="inlineStr">
         <is>
-          <t>money</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="U258" s="10" t="inlineStr"/>
@@ -50137,37 +50243,37 @@
       </c>
       <c r="C259" s="32" t="inlineStr">
         <is>
-          <t>Session 2+</t>
+          <t>Session 1</t>
         </is>
       </c>
       <c r="D259" s="32" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>Debt</t>
         </is>
       </c>
       <c r="E259" s="32" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Credit cards</t>
         </is>
       </c>
       <c r="F259" s="32" t="inlineStr">
         <is>
-          <t>Coverage amount, through employer, deductible / out-of-pocket max</t>
+          <t>Payment choice: minimum, custom, in full</t>
         </is>
       </c>
       <c r="G259" s="32" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="H259" s="32" t="inlineStr">
         <is>
-          <t>Fields</t>
+          <t>Toggle plus Pay in full button</t>
         </is>
       </c>
       <c r="I259" s="32" t="inlineStr">
         <is>
-          <t>Gaps show as to-dos</t>
+          <t>Your comment: minimum payment computed in Primary, options below</t>
         </is>
       </c>
       <c r="J259" s="32" t="n"/>
@@ -50176,11 +50282,7 @@
           <t>Client</t>
         </is>
       </c>
-      <c r="L259" s="32" t="inlineStr">
-        <is>
-          <t>Often</t>
-        </is>
-      </c>
+      <c r="L259" s="32" t="n"/>
       <c r="M259" s="32" t="inlineStr">
         <is>
           <t>All</t>
@@ -50188,7 +50290,7 @@
       </c>
       <c r="N259" s="32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O259" s="32" t="n"/>
@@ -50200,12 +50302,12 @@
       <c r="Q259" s="32" t="n"/>
       <c r="S259" s="10" t="inlineStr">
         <is>
-          <t>My Money › Protection</t>
+          <t>My Money › Debt</t>
         </is>
       </c>
       <c r="T259" s="10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>choice</t>
         </is>
       </c>
       <c r="U259" s="10" t="inlineStr"/>
@@ -50233,17 +50335,17 @@
       </c>
       <c r="D260" s="32" t="inlineStr">
         <is>
-          <t>Needs</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="E260" s="32" t="inlineStr">
         <is>
-          <t>Irregular costs</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="F260" s="32" t="inlineStr">
         <is>
-          <t>Yearly cost and month due (walk-the-list prompt)</t>
+          <t>Type, have it or not, premium</t>
         </is>
       </c>
       <c r="G260" s="32" t="inlineStr">
@@ -50253,12 +50355,12 @@
       </c>
       <c r="H260" s="32" t="inlineStr">
         <is>
-          <t>Amount plus month</t>
+          <t>Dropdown, toggle, amount</t>
         </is>
       </c>
       <c r="I260" s="32" t="inlineStr">
         <is>
-          <t>Registration, holidays, birthdays, renewals, vet, travel, annual subscriptions, tax prep</t>
+          <t>Health, life, disability, renters or home, car, umbrella</t>
         </is>
       </c>
       <c r="J260" s="32" t="n"/>
@@ -50275,7 +50377,7 @@
       </c>
       <c r="N260" s="32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O260" s="32" t="n"/>
@@ -50287,7 +50389,7 @@
       <c r="Q260" s="32" t="n"/>
       <c r="S260" s="10" t="inlineStr">
         <is>
-          <t>Spending › Budget</t>
+          <t>My Money › Protection</t>
         </is>
       </c>
       <c r="T260" s="10" t="inlineStr">
@@ -50298,7 +50400,7 @@
       <c r="U260" s="10" t="inlineStr"/>
       <c r="V260" s="33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -50315,22 +50417,22 @@
       </c>
       <c r="C261" s="32" t="inlineStr">
         <is>
-          <t>Session 1</t>
+          <t>Session 2+</t>
         </is>
       </c>
       <c r="D261" s="32" t="inlineStr">
         <is>
-          <t>Goals</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="E261" s="32" t="inlineStr">
         <is>
-          <t>Next 12 months</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="F261" s="32" t="inlineStr">
         <is>
-          <t>Upcoming event, rough cost, month</t>
+          <t>Coverage amount, through employer, deductible / out-of-pocket max</t>
         </is>
       </c>
       <c r="G261" s="32" t="inlineStr">
@@ -50340,12 +50442,12 @@
       </c>
       <c r="H261" s="32" t="inlineStr">
         <is>
-          <t>Row</t>
+          <t>Fields</t>
         </is>
       </c>
       <c r="I261" s="32" t="inlineStr">
         <is>
-          <t>Wedding, move, trip, big purchase</t>
+          <t>Gaps show as to-dos</t>
         </is>
       </c>
       <c r="J261" s="32" t="n"/>
@@ -50354,7 +50456,11 @@
           <t>Client</t>
         </is>
       </c>
-      <c r="L261" s="32" t="n"/>
+      <c r="L261" s="32" t="inlineStr">
+        <is>
+          <t>Often</t>
+        </is>
+      </c>
       <c r="M261" s="32" t="inlineStr">
         <is>
           <t>All</t>
@@ -50374,7 +50480,7 @@
       <c r="Q261" s="32" t="n"/>
       <c r="S261" s="10" t="inlineStr">
         <is>
-          <t>Plan › Next 12 months</t>
+          <t>My Money › Protection</t>
         </is>
       </c>
       <c r="T261" s="10" t="inlineStr">
@@ -50385,7 +50491,7 @@
       <c r="U261" s="10" t="inlineStr"/>
       <c r="V261" s="33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -50402,7 +50508,7 @@
       </c>
       <c r="C262" s="32" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Session 1</t>
         </is>
       </c>
       <c r="D262" s="32" t="inlineStr">
@@ -50412,27 +50518,27 @@
       </c>
       <c r="E262" s="32" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Irregular costs</t>
         </is>
       </c>
       <c r="F262" s="32" t="inlineStr">
         <is>
-          <t>Maybe money (expected, not certain)</t>
+          <t>Yearly cost and month due (walk-the-list prompt)</t>
         </is>
       </c>
       <c r="G262" s="32" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="H262" s="32" t="inlineStr">
         <is>
-          <t>In / Out / Maybe toggle</t>
+          <t>Amount plus month</t>
         </is>
       </c>
       <c r="I262" s="32" t="inlineStr">
         <is>
-          <t>Your comment: dashed chip, out of the balance unless counted</t>
+          <t>Registration, holidays, birthdays, renewals, vet, travel, annual subscriptions, tax prep</t>
         </is>
       </c>
       <c r="J262" s="32" t="n"/>
@@ -50449,7 +50555,7 @@
       </c>
       <c r="N262" s="32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O262" s="32" t="n"/>
@@ -50461,12 +50567,12 @@
       <c r="Q262" s="32" t="n"/>
       <c r="S262" s="10" t="inlineStr">
         <is>
-          <t>Spending › Cash flow calendar</t>
+          <t>Spending › Budget</t>
         </is>
       </c>
       <c r="T262" s="10" t="inlineStr">
         <is>
-          <t>choice</t>
+          <t>money</t>
         </is>
       </c>
       <c r="U262" s="10" t="inlineStr"/>
@@ -50489,37 +50595,37 @@
       </c>
       <c r="C263" s="32" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Session 1</t>
         </is>
       </c>
       <c r="D263" s="32" t="inlineStr">
         <is>
-          <t>Needs</t>
+          <t>Goals</t>
         </is>
       </c>
       <c r="E263" s="32" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Next 12 months</t>
         </is>
       </c>
       <c r="F263" s="32" t="inlineStr">
         <is>
-          <t>Wins on a date</t>
+          <t>Upcoming event, rough cost, month</t>
         </is>
       </c>
       <c r="G263" s="32" t="inlineStr">
         <is>
-          <t>Tertiary</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="H263" s="32" t="inlineStr">
         <is>
-          <t>Name plus date</t>
+          <t>Row</t>
         </is>
       </c>
       <c r="I263" s="32" t="inlineStr">
         <is>
-          <t>Your comment: dates for good things like milestones</t>
+          <t>Wedding, move, trip, big purchase</t>
         </is>
       </c>
       <c r="J263" s="32" t="n"/>
@@ -50536,7 +50642,7 @@
       </c>
       <c r="N263" s="32" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O263" s="32" t="n"/>
@@ -50548,18 +50654,18 @@
       <c r="Q263" s="32" t="n"/>
       <c r="S263" s="10" t="inlineStr">
         <is>
-          <t>Spending › Cash flow calendar</t>
+          <t>Plan › Next 12 months</t>
         </is>
       </c>
       <c r="T263" s="10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="U263" s="10" t="inlineStr"/>
       <c r="V263" s="33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -50576,22 +50682,22 @@
       </c>
       <c r="C264" s="32" t="inlineStr">
         <is>
-          <t>Session 1</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="D264" s="32" t="inlineStr">
         <is>
-          <t>Coaching</t>
+          <t>Needs</t>
         </is>
       </c>
       <c r="E264" s="32" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="F264" s="32" t="inlineStr">
         <is>
-          <t>Private notes and shared notes</t>
+          <t>Maybe money (expected, not certain)</t>
         </is>
       </c>
       <c r="G264" s="32" t="inlineStr">
@@ -50601,24 +50707,24 @@
       </c>
       <c r="H264" s="32" t="inlineStr">
         <is>
-          <t>Two boxes</t>
+          <t>In / Out / Maybe toggle</t>
         </is>
       </c>
       <c r="I264" s="32" t="inlineStr">
         <is>
-          <t>Private stays with you</t>
+          <t>Your comment: dashed chip, out of the balance unless counted</t>
         </is>
       </c>
       <c r="J264" s="32" t="n"/>
       <c r="K264" s="32" t="inlineStr">
         <is>
-          <t>Coach</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="L264" s="32" t="n"/>
       <c r="M264" s="32" t="inlineStr">
         <is>
-          <t>Know it</t>
+          <t>All</t>
         </is>
       </c>
       <c r="N264" s="32" t="inlineStr">
@@ -50635,18 +50741,18 @@
       <c r="Q264" s="32" t="n"/>
       <c r="S264" s="10" t="inlineStr">
         <is>
-          <t>Home / ⚙ Coach tools</t>
+          <t>Spending › Cash flow calendar</t>
         </is>
       </c>
       <c r="T264" s="10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>choice</t>
         </is>
       </c>
       <c r="U264" s="10" t="inlineStr"/>
       <c r="V264" s="33" t="inlineStr">
         <is>
-          <t>9-10</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -50663,54 +50769,54 @@
       </c>
       <c r="C265" s="32" t="inlineStr">
         <is>
-          <t>Session 1</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="D265" s="32" t="inlineStr">
         <is>
-          <t>Coaching</t>
+          <t>Needs</t>
         </is>
       </c>
       <c r="E265" s="32" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="F265" s="32" t="inlineStr">
         <is>
-          <t>Session number, next date, client status</t>
+          <t>Wins on a date</t>
         </is>
       </c>
       <c r="G265" s="32" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Tertiary</t>
         </is>
       </c>
       <c r="H265" s="32" t="inlineStr">
         <is>
-          <t>Fields</t>
+          <t>Name plus date</t>
         </is>
       </c>
       <c r="I265" s="32" t="inlineStr">
         <is>
-          <t>Session 2 of 6; active, maintenance, paused</t>
+          <t>Your comment: dates for good things like milestones</t>
         </is>
       </c>
       <c r="J265" s="32" t="n"/>
       <c r="K265" s="32" t="inlineStr">
         <is>
-          <t>Coach</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="L265" s="32" t="n"/>
       <c r="M265" s="32" t="inlineStr">
         <is>
-          <t>Know it</t>
+          <t>All</t>
         </is>
       </c>
       <c r="N265" s="32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O265" s="32" t="n"/>
@@ -50722,23 +50828,197 @@
       <c r="Q265" s="32" t="n"/>
       <c r="S265" s="10" t="inlineStr">
         <is>
-          <t>Home / ⚙ Coach tools</t>
+          <t>Spending › Cash flow calendar</t>
         </is>
       </c>
       <c r="T265" s="10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="U265" s="10" t="inlineStr"/>
       <c r="V265" s="33" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="32" t="inlineStr">
+        <is>
+          <t>F264</t>
+        </is>
+      </c>
+      <c r="B266" s="32" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="C266" s="32" t="inlineStr">
+        <is>
+          <t>Session 1</t>
+        </is>
+      </c>
+      <c r="D266" s="32" t="inlineStr">
+        <is>
+          <t>Coaching</t>
+        </is>
+      </c>
+      <c r="E266" s="32" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="F266" s="32" t="inlineStr">
+        <is>
+          <t>Private notes and shared notes</t>
+        </is>
+      </c>
+      <c r="G266" s="32" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="H266" s="32" t="inlineStr">
+        <is>
+          <t>Two boxes</t>
+        </is>
+      </c>
+      <c r="I266" s="32" t="inlineStr">
+        <is>
+          <t>Private stays with you</t>
+        </is>
+      </c>
+      <c r="J266" s="32" t="n"/>
+      <c r="K266" s="32" t="inlineStr">
+        <is>
+          <t>Coach</t>
+        </is>
+      </c>
+      <c r="L266" s="32" t="n"/>
+      <c r="M266" s="32" t="inlineStr">
+        <is>
+          <t>Know it</t>
+        </is>
+      </c>
+      <c r="N266" s="32" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O266" s="32" t="n"/>
+      <c r="P266" s="32" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="Q266" s="32" t="n"/>
+      <c r="S266" s="10" t="inlineStr">
+        <is>
+          <t>Home / ⚙ Coach tools</t>
+        </is>
+      </c>
+      <c r="T266" s="10" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="U266" s="10" t="inlineStr"/>
+      <c r="V266" s="33" t="inlineStr">
+        <is>
           <t>9-10</t>
         </is>
       </c>
     </row>
+    <row r="267">
+      <c r="A267" s="32" t="inlineStr">
+        <is>
+          <t>F265</t>
+        </is>
+      </c>
+      <c r="B267" s="32" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="C267" s="32" t="inlineStr">
+        <is>
+          <t>Session 1</t>
+        </is>
+      </c>
+      <c r="D267" s="32" t="inlineStr">
+        <is>
+          <t>Coaching</t>
+        </is>
+      </c>
+      <c r="E267" s="32" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="F267" s="32" t="inlineStr">
+        <is>
+          <t>Session number, next date, client status</t>
+        </is>
+      </c>
+      <c r="G267" s="32" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="H267" s="32" t="inlineStr">
+        <is>
+          <t>Fields</t>
+        </is>
+      </c>
+      <c r="I267" s="32" t="inlineStr">
+        <is>
+          <t>Session 2 of 6; active, maintenance, paused</t>
+        </is>
+      </c>
+      <c r="J267" s="32" t="n"/>
+      <c r="K267" s="32" t="inlineStr">
+        <is>
+          <t>Coach</t>
+        </is>
+      </c>
+      <c r="L267" s="32" t="n"/>
+      <c r="M267" s="32" t="inlineStr">
+        <is>
+          <t>Know it</t>
+        </is>
+      </c>
+      <c r="N267" s="32" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O267" s="32" t="n"/>
+      <c r="P267" s="32" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="Q267" s="32" t="n"/>
+      <c r="S267" s="10" t="inlineStr">
+        <is>
+          <t>Home / ⚙ Coach tools</t>
+        </is>
+      </c>
+      <c r="T267" s="10" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="U267" s="10" t="inlineStr"/>
+      <c r="V267" s="33" t="inlineStr">
+        <is>
+          <t>9-10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:V265"/>
+  <autoFilter ref="A2:V267"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
@@ -64830,7 +65110,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Top bar: left = where am I, middle = 5 tabs, right = 7 tools. Sub-tabs always directly under the main tabs</t>
+          <t>Top bar: left = where am I, middle = 5 tabs, right = 8 tools. Sub-tabs always directly under the main tabs</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
